--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26F984D-EB36-41C6-8E08-2F5CF76D31C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F2585-5F49-43EC-9A20-6E65BFA61FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="774" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,23 +514,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,24 +554,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -1615,78 +1615,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="2" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="30"/>
+      <c r="AF1" s="30"/>
+      <c r="AG1" s="30"/>
     </row>
     <row r="2" spans="1:33" s="2" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="43" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
     </row>
     <row r="3" spans="1:33" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="7"/>
@@ -1724,49 +1724,49 @@
       <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="36"/>
-      <c r="AE4" s="36"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="39"/>
     </row>
     <row r="5" spans="1:33" s="1" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="4">
         <v>1</v>
       </c>
@@ -2488,139 +2488,139 @@
     <row r="22" spans="1:33" ht="22.5" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="8"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="28"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
       <c r="X22" s="33"/>
       <c r="Y22" s="33"/>
-      <c r="Z22" s="28"/>
+      <c r="Z22" s="31"/>
       <c r="AA22" s="33"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="28"/>
-      <c r="AG22" s="28"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
     </row>
     <row r="23" spans="1:33" ht="22.5" customHeight="1">
       <c r="B23" s="9"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="28"/>
     </row>
     <row r="24" spans="1:33" ht="22.5" customHeight="1">
       <c r="B24" s="9"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="26"/>
-      <c r="Q24" s="26"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="26"/>
-      <c r="X24" s="44"/>
-      <c r="Y24" s="44"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="26"/>
-      <c r="AD24" s="26"/>
-      <c r="AE24" s="26"/>
-      <c r="AF24" s="26"/>
-      <c r="AG24" s="26"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="27"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="27"/>
+      <c r="AC24" s="27"/>
+      <c r="AD24" s="27"/>
+      <c r="AE24" s="27"/>
+      <c r="AF24" s="27"/>
+      <c r="AG24" s="27"/>
     </row>
     <row r="25" spans="1:33" ht="22.5" customHeight="1">
       <c r="B25" s="9"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="27"/>
-      <c r="AC25" s="27"/>
-      <c r="AD25" s="27"/>
-      <c r="AE25" s="27"/>
-      <c r="AF25" s="27"/>
-      <c r="AG25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="28"/>
+      <c r="AE25" s="28"/>
+      <c r="AF25" s="28"/>
+      <c r="AG25" s="28"/>
     </row>
     <row r="26" spans="1:33" ht="12" customHeight="1"/>
     <row r="27" spans="1:33" ht="19.5" customHeight="1">
@@ -2631,26 +2631,26 @@
       <c r="Y27" s="21"/>
     </row>
     <row r="28" spans="1:33" ht="173.25" customHeight="1">
-      <c r="B28" s="45"/>
+      <c r="B28" s="26"/>
     </row>
     <row r="29" spans="1:33" ht="21" customHeight="1">
       <c r="AA29" s="19"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
+      <c r="AB29" s="44"/>
+      <c r="AC29" s="45"/>
+      <c r="AD29" s="45"/>
+      <c r="AE29" s="45"/>
+      <c r="AF29" s="45"/>
+      <c r="AG29" s="45"/>
     </row>
     <row r="30" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AB30" s="29" t="s">
+      <c r="AB30" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
+      <c r="AC30" s="43"/>
+      <c r="AD30" s="43"/>
+      <c r="AE30" s="43"/>
+      <c r="AF30" s="43"/>
+      <c r="AG30" s="43"/>
     </row>
     <row r="31" spans="1:33" ht="7.5" customHeight="1">
       <c r="D31" s="17"/>
@@ -2663,6 +2663,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="H24:H25"/>
     <mergeCell ref="AC24:AC25"/>
     <mergeCell ref="R24:R25"/>
     <mergeCell ref="D24:D25"/>
@@ -2679,60 +2733,6 @@
     <mergeCell ref="AG22:AG23"/>
     <mergeCell ref="P22:P23"/>
     <mergeCell ref="AB22:AB23"/>
-    <mergeCell ref="O24:O25"/>
-    <mergeCell ref="AF24:AF25"/>
-    <mergeCell ref="V24:V25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="AE24:AE25"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="AG24:AG25"/>
-    <mergeCell ref="P24:P25"/>
-    <mergeCell ref="A1:Z2"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="W24:W25"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="T22:T23"/>
-    <mergeCell ref="X22:X23"/>
-    <mergeCell ref="AF22:AF23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="W22:W23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="AE22:AE23"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="V22:V23"/>
-    <mergeCell ref="AB30:AG30"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="AB24:AB25"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="AD24:AD25"/>
-    <mergeCell ref="AB29:AG29"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="T24:T25"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="J24:J25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F2585-5F49-43EC-9A20-6E65BFA61FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C95E556-0718-4159-88D3-1E0A8FBFC363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="774" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,33 +514,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -554,14 +544,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -1615,78 +1615,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="2" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="41"/>
+      <c r="AC1" s="41"/>
+      <c r="AD1" s="41"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="41"/>
+      <c r="AG1" s="41"/>
     </row>
     <row r="2" spans="1:33" s="2" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="29" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
     </row>
     <row r="3" spans="1:33" s="2" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="7"/>
@@ -1724,49 +1724,49 @@
       <c r="AG3" s="16"/>
     </row>
     <row r="4" spans="1:33" s="1" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="39"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
     </row>
     <row r="5" spans="1:33" s="1" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="4">
         <v>1</v>
       </c>
@@ -2488,139 +2488,139 @@
     <row r="22" spans="1:33" ht="22.5" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="8"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
       <c r="X22" s="33"/>
       <c r="Y22" s="33"/>
-      <c r="Z22" s="31"/>
+      <c r="Z22" s="28"/>
       <c r="AA22" s="33"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
+      <c r="AB22" s="28"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="28"/>
+      <c r="AE22" s="28"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="28"/>
     </row>
     <row r="23" spans="1:33" ht="22.5" customHeight="1">
       <c r="B23" s="9"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="29"/>
+      <c r="AF23" s="29"/>
+      <c r="AG23" s="29"/>
     </row>
     <row r="24" spans="1:33" ht="22.5" customHeight="1">
       <c r="B24" s="9"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="27"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="27"/>
-      <c r="AC24" s="27"/>
-      <c r="AD24" s="27"/>
-      <c r="AE24" s="27"/>
-      <c r="AF24" s="27"/>
-      <c r="AG24" s="27"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="44"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="44"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
     </row>
     <row r="25" spans="1:33" ht="22.5" customHeight="1">
       <c r="B25" s="9"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="28"/>
-      <c r="AE25" s="28"/>
-      <c r="AF25" s="28"/>
-      <c r="AG25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29"/>
+      <c r="AC25" s="29"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
+      <c r="AF25" s="29"/>
+      <c r="AG25" s="29"/>
     </row>
     <row r="26" spans="1:33" ht="12" customHeight="1"/>
     <row r="27" spans="1:33" ht="19.5" customHeight="1">
@@ -2631,26 +2631,57 @@
       <c r="Y27" s="21"/>
     </row>
     <row r="28" spans="1:33" ht="173.25" customHeight="1">
-      <c r="B28" s="26"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="45"/>
+      <c r="AB28" s="45"/>
+      <c r="AC28" s="45"/>
+      <c r="AD28" s="45"/>
+      <c r="AE28" s="45"/>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="45"/>
     </row>
     <row r="29" spans="1:33" ht="21" customHeight="1">
       <c r="AA29" s="19"/>
-      <c r="AB29" s="44"/>
-      <c r="AC29" s="45"/>
-      <c r="AD29" s="45"/>
-      <c r="AE29" s="45"/>
-      <c r="AF29" s="45"/>
-      <c r="AG29" s="45"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32"/>
     </row>
     <row r="30" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AB30" s="42" t="s">
+      <c r="AB30" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="43"/>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="43"/>
-      <c r="AG30" s="43"/>
+      <c r="AC30" s="27"/>
+      <c r="AD30" s="27"/>
+      <c r="AE30" s="27"/>
+      <c r="AF30" s="27"/>
+      <c r="AG30" s="27"/>
     </row>
     <row r="31" spans="1:33" ht="7.5" customHeight="1">
       <c r="D31" s="17"/>
@@ -2662,21 +2693,46 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="AB30:AG30"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="AB24:AB25"/>
-    <mergeCell ref="AD22:AD23"/>
-    <mergeCell ref="AD24:AD25"/>
-    <mergeCell ref="AB29:AG29"/>
-    <mergeCell ref="S22:S23"/>
-    <mergeCell ref="U22:U23"/>
-    <mergeCell ref="AA22:AA23"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="T24:T25"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="J24:J25"/>
+  <mergeCells count="71">
+    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="W24:W25"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="T22:T23"/>
     <mergeCell ref="X22:X23"/>
@@ -2693,46 +2749,22 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="AE22:AE23"/>
     <mergeCell ref="V22:V23"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="R22:R23"/>
-    <mergeCell ref="AC22:AC23"/>
-    <mergeCell ref="AE24:AE25"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="AG24:AG25"/>
-    <mergeCell ref="P24:P25"/>
-    <mergeCell ref="A1:Z2"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="J24:J25"/>
     <mergeCell ref="O24:O25"/>
     <mergeCell ref="AF24:AF25"/>
-    <mergeCell ref="V24:V25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="AC24:AC25"/>
-    <mergeCell ref="R24:R25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="U24:U25"/>
-    <mergeCell ref="AA2:AG2"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="Z22:Z23"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="Y22:Y23"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="AG22:AG23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="AB22:AB23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -382,7 +382,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -494,6 +494,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -1829,8 +1832,16 @@
       <c r="AB6" s="22" t="n"/>
       <c r="AC6" s="22" t="n"/>
       <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="22" t="n"/>
-      <c r="AF6" s="22" t="n"/>
+      <c r="AE6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="22" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1870,8 +1881,16 @@
       <c r="AB7" s="22" t="n"/>
       <c r="AC7" s="22" t="n"/>
       <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
+      <c r="AE7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="22" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1911,8 +1930,16 @@
       <c r="AB8" s="22" t="n"/>
       <c r="AC8" s="22" t="n"/>
       <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
+      <c r="AE8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="22" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1952,8 +1979,16 @@
       <c r="AB9" s="22" t="n"/>
       <c r="AC9" s="22" t="n"/>
       <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="22" t="n"/>
-      <c r="AF9" s="22" t="n"/>
+      <c r="AE9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="22" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1993,8 +2028,16 @@
       <c r="AB10" s="22" t="n"/>
       <c r="AC10" s="22" t="n"/>
       <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="n"/>
-      <c r="AF10" s="22" t="n"/>
+      <c r="AE10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="22" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2034,8 +2077,16 @@
       <c r="AB11" s="22" t="n"/>
       <c r="AC11" s="22" t="n"/>
       <c r="AD11" s="22" t="n"/>
-      <c r="AE11" s="22" t="n"/>
-      <c r="AF11" s="22" t="n"/>
+      <c r="AE11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AG11" s="22" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2075,8 +2126,16 @@
       <c r="AB12" s="22" t="n"/>
       <c r="AC12" s="22" t="n"/>
       <c r="AD12" s="22" t="n"/>
-      <c r="AE12" s="22" t="n"/>
-      <c r="AF12" s="22" t="n"/>
+      <c r="AE12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG12" s="22" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2116,8 +2175,16 @@
       <c r="AB13" s="22" t="n"/>
       <c r="AC13" s="22" t="n"/>
       <c r="AD13" s="22" t="n"/>
-      <c r="AE13" s="22" t="n"/>
-      <c r="AF13" s="22" t="n"/>
+      <c r="AE13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG13" s="22" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2157,8 +2224,16 @@
       <c r="AB14" s="22" t="n"/>
       <c r="AC14" s="22" t="n"/>
       <c r="AD14" s="22" t="n"/>
-      <c r="AE14" s="22" t="n"/>
-      <c r="AF14" s="22" t="n"/>
+      <c r="AE14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AG14" s="22" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2198,8 +2273,16 @@
       <c r="AB15" s="22" t="n"/>
       <c r="AC15" s="22" t="n"/>
       <c r="AD15" s="22" t="n"/>
-      <c r="AE15" s="22" t="n"/>
-      <c r="AF15" s="22" t="n"/>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG15" s="22" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2239,8 +2322,16 @@
       <c r="AB16" s="22" t="n"/>
       <c r="AC16" s="22" t="n"/>
       <c r="AD16" s="22" t="n"/>
-      <c r="AE16" s="22" t="n"/>
-      <c r="AF16" s="22" t="n"/>
+      <c r="AE16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AG16" s="22" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2280,8 +2371,16 @@
       <c r="AB17" s="22" t="n"/>
       <c r="AC17" s="22" t="n"/>
       <c r="AD17" s="22" t="n"/>
-      <c r="AE17" s="22" t="n"/>
-      <c r="AF17" s="22" t="n"/>
+      <c r="AE17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AG17" s="22" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2321,8 +2420,16 @@
       <c r="AB18" s="22" t="n"/>
       <c r="AC18" s="22" t="n"/>
       <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="22" t="n"/>
-      <c r="AF18" s="22" t="n"/>
+      <c r="AE18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG18" s="22" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2362,8 +2469,16 @@
       <c r="AB19" s="22" t="n"/>
       <c r="AC19" s="22" t="n"/>
       <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="22" t="n"/>
-      <c r="AF19" s="22" t="n"/>
+      <c r="AE19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG19" s="22" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2403,8 +2518,16 @@
       <c r="AB20" s="22" t="n"/>
       <c r="AC20" s="22" t="n"/>
       <c r="AD20" s="22" t="n"/>
-      <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="22" t="n"/>
+      <c r="AE20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG20" s="22" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2444,8 +2567,16 @@
       <c r="AB21" s="22" t="n"/>
       <c r="AC21" s="22" t="n"/>
       <c r="AD21" s="22" t="n"/>
-      <c r="AE21" s="22" t="n"/>
-      <c r="AF21" s="22" t="n"/>
+      <c r="AE21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG21" s="22" t="n"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
@@ -2479,8 +2610,16 @@
       <c r="AB22" s="28" t="n"/>
       <c r="AC22" s="28" t="n"/>
       <c r="AD22" s="28" t="n"/>
-      <c r="AE22" s="28" t="n"/>
-      <c r="AF22" s="28" t="n"/>
+      <c r="AE22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AF22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
       <c r="AG22" s="28" t="n"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
@@ -2596,7 +2735,11 @@
       <c r="Y27" s="21" t="n"/>
     </row>
     <row r="28" ht="173.25" customHeight="1">
-      <c r="B28" s="45" t="n"/>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="AA29" s="19" t="n"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -1842,7 +1842,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG6" s="22" t="n"/>
+      <c r="AG6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="14" t="n">
@@ -1891,7 +1895,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG7" s="22" t="n"/>
+      <c r="AG7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="n">
@@ -1940,7 +1948,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG8" s="22" t="n"/>
+      <c r="AG8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="14" t="n">
@@ -1989,7 +2001,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG9" s="22" t="n"/>
+      <c r="AG9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="n">
@@ -2038,7 +2054,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG10" s="22" t="n"/>
+      <c r="AG10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="14" t="n">
@@ -2087,7 +2107,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AG11" s="22" t="n"/>
+      <c r="AG11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="n">
@@ -2136,7 +2160,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG12" s="22" t="n"/>
+      <c r="AG12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="n">
@@ -2185,7 +2213,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG13" s="22" t="n"/>
+      <c r="AG13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="n">
@@ -2234,7 +2266,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG14" s="22" t="n"/>
+      <c r="AG14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="14" t="n">
@@ -2283,7 +2319,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG15" s="22" t="n"/>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="n">
@@ -2332,7 +2372,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG16" s="22" t="n"/>
+      <c r="AG16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="14" t="n">
@@ -2381,7 +2425,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="AG17" s="22" t="n"/>
+      <c r="AG17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="14" t="n">
@@ -2430,7 +2478,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG18" s="22" t="n"/>
+      <c r="AG18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="14" t="n">
@@ -2479,7 +2531,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG19" s="22" t="n"/>
+      <c r="AG19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="14" t="n">
@@ -2528,7 +2584,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG20" s="22" t="n"/>
+      <c r="AG20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="n">
@@ -2577,7 +2637,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="AG21" s="22" t="n"/>
+      <c r="AG21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="n"/>
@@ -2620,7 +2684,11 @@
           <t>พงศกร มลวัง</t>
         </is>
       </c>
-      <c r="AG22" s="28" t="n"/>
+      <c r="AG22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="B23" s="9" t="n"/>
@@ -2737,7 +2805,7 @@
     <row r="28" ht="173.25" customHeight="1">
       <c r="B28" s="46" t="inlineStr">
         <is>
-          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -954,4 +954,1965 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <cols>
+    <col width="4.875" customWidth="1" style="27" min="1" max="1"/>
+    <col width="58.5" customWidth="1" style="27" min="2" max="2"/>
+    <col width="3.375" customWidth="1" style="27" min="3" max="33"/>
+    <col width="9.125" customWidth="1" style="27" min="34" max="245"/>
+    <col width="7" customWidth="1" style="27" min="246" max="246"/>
+    <col width="14.75" customWidth="1" style="27" min="247" max="247"/>
+    <col width="13.375" customWidth="1" style="27" min="248" max="248"/>
+    <col width="9.875" customWidth="1" style="27" min="249" max="252"/>
+    <col width="10.75" customWidth="1" style="27" min="253" max="253"/>
+    <col width="9.875" customWidth="1" style="27" min="254" max="255"/>
+    <col width="14.875" customWidth="1" style="27" min="256" max="256"/>
+    <col width="23.875" customWidth="1" style="27" min="257" max="257"/>
+    <col width="13.25" customWidth="1" style="27" min="258" max="258"/>
+    <col width="9.125" customWidth="1" style="27" min="259" max="501"/>
+    <col width="7" customWidth="1" style="27" min="502" max="502"/>
+    <col width="14.75" customWidth="1" style="27" min="503" max="503"/>
+    <col width="13.375" customWidth="1" style="27" min="504" max="504"/>
+    <col width="9.875" customWidth="1" style="27" min="505" max="508"/>
+    <col width="10.75" customWidth="1" style="27" min="509" max="509"/>
+    <col width="9.875" customWidth="1" style="27" min="510" max="511"/>
+    <col width="14.875" customWidth="1" style="27" min="512" max="512"/>
+    <col width="23.875" customWidth="1" style="27" min="513" max="513"/>
+    <col width="13.25" customWidth="1" style="27" min="514" max="514"/>
+    <col width="9.125" customWidth="1" style="27" min="515" max="757"/>
+    <col width="7" customWidth="1" style="27" min="758" max="758"/>
+    <col width="14.75" customWidth="1" style="27" min="759" max="759"/>
+    <col width="13.375" customWidth="1" style="27" min="760" max="760"/>
+    <col width="9.875" customWidth="1" style="27" min="761" max="764"/>
+    <col width="10.75" customWidth="1" style="27" min="765" max="765"/>
+    <col width="9.875" customWidth="1" style="27" min="766" max="767"/>
+    <col width="14.875" customWidth="1" style="27" min="768" max="768"/>
+    <col width="23.875" customWidth="1" style="27" min="769" max="769"/>
+    <col width="13.25" customWidth="1" style="27" min="770" max="770"/>
+    <col width="9.125" customWidth="1" style="27" min="771" max="1013"/>
+    <col width="7" customWidth="1" style="27" min="1014" max="1014"/>
+    <col width="14.75" customWidth="1" style="27" min="1015" max="1015"/>
+    <col width="13.375" customWidth="1" style="27" min="1016" max="1016"/>
+    <col width="9.875" customWidth="1" style="27" min="1017" max="1020"/>
+    <col width="10.75" customWidth="1" style="27" min="1021" max="1021"/>
+    <col width="9.875" customWidth="1" style="27" min="1022" max="1023"/>
+    <col width="14.875" customWidth="1" style="27" min="1024" max="1024"/>
+    <col width="23.875" customWidth="1" style="27" min="1025" max="1025"/>
+    <col width="13.25" customWidth="1" style="27" min="1026" max="1026"/>
+    <col width="9.125" customWidth="1" style="27" min="1027" max="1269"/>
+    <col width="7" customWidth="1" style="27" min="1270" max="1270"/>
+    <col width="14.75" customWidth="1" style="27" min="1271" max="1271"/>
+    <col width="13.375" customWidth="1" style="27" min="1272" max="1272"/>
+    <col width="9.875" customWidth="1" style="27" min="1273" max="1276"/>
+    <col width="10.75" customWidth="1" style="27" min="1277" max="1277"/>
+    <col width="9.875" customWidth="1" style="27" min="1278" max="1279"/>
+    <col width="14.875" customWidth="1" style="27" min="1280" max="1280"/>
+    <col width="23.875" customWidth="1" style="27" min="1281" max="1281"/>
+    <col width="13.25" customWidth="1" style="27" min="1282" max="1282"/>
+    <col width="9.125" customWidth="1" style="27" min="1283" max="1525"/>
+    <col width="7" customWidth="1" style="27" min="1526" max="1526"/>
+    <col width="14.75" customWidth="1" style="27" min="1527" max="1527"/>
+    <col width="13.375" customWidth="1" style="27" min="1528" max="1528"/>
+    <col width="9.875" customWidth="1" style="27" min="1529" max="1532"/>
+    <col width="10.75" customWidth="1" style="27" min="1533" max="1533"/>
+    <col width="9.875" customWidth="1" style="27" min="1534" max="1535"/>
+    <col width="14.875" customWidth="1" style="27" min="1536" max="1536"/>
+    <col width="23.875" customWidth="1" style="27" min="1537" max="1537"/>
+    <col width="13.25" customWidth="1" style="27" min="1538" max="1538"/>
+    <col width="9.125" customWidth="1" style="27" min="1539" max="1781"/>
+    <col width="7" customWidth="1" style="27" min="1782" max="1782"/>
+    <col width="14.75" customWidth="1" style="27" min="1783" max="1783"/>
+    <col width="13.375" customWidth="1" style="27" min="1784" max="1784"/>
+    <col width="9.875" customWidth="1" style="27" min="1785" max="1788"/>
+    <col width="10.75" customWidth="1" style="27" min="1789" max="1789"/>
+    <col width="9.875" customWidth="1" style="27" min="1790" max="1791"/>
+    <col width="14.875" customWidth="1" style="27" min="1792" max="1792"/>
+    <col width="23.875" customWidth="1" style="27" min="1793" max="1793"/>
+    <col width="13.25" customWidth="1" style="27" min="1794" max="1794"/>
+    <col width="9.125" customWidth="1" style="27" min="1795" max="2037"/>
+    <col width="7" customWidth="1" style="27" min="2038" max="2038"/>
+    <col width="14.75" customWidth="1" style="27" min="2039" max="2039"/>
+    <col width="13.375" customWidth="1" style="27" min="2040" max="2040"/>
+    <col width="9.875" customWidth="1" style="27" min="2041" max="2044"/>
+    <col width="10.75" customWidth="1" style="27" min="2045" max="2045"/>
+    <col width="9.875" customWidth="1" style="27" min="2046" max="2047"/>
+    <col width="14.875" customWidth="1" style="27" min="2048" max="2048"/>
+    <col width="23.875" customWidth="1" style="27" min="2049" max="2049"/>
+    <col width="13.25" customWidth="1" style="27" min="2050" max="2050"/>
+    <col width="9.125" customWidth="1" style="27" min="2051" max="2293"/>
+    <col width="7" customWidth="1" style="27" min="2294" max="2294"/>
+    <col width="14.75" customWidth="1" style="27" min="2295" max="2295"/>
+    <col width="13.375" customWidth="1" style="27" min="2296" max="2296"/>
+    <col width="9.875" customWidth="1" style="27" min="2297" max="2300"/>
+    <col width="10.75" customWidth="1" style="27" min="2301" max="2301"/>
+    <col width="9.875" customWidth="1" style="27" min="2302" max="2303"/>
+    <col width="14.875" customWidth="1" style="27" min="2304" max="2304"/>
+    <col width="23.875" customWidth="1" style="27" min="2305" max="2305"/>
+    <col width="13.25" customWidth="1" style="27" min="2306" max="2306"/>
+    <col width="9.125" customWidth="1" style="27" min="2307" max="2549"/>
+    <col width="7" customWidth="1" style="27" min="2550" max="2550"/>
+    <col width="14.75" customWidth="1" style="27" min="2551" max="2551"/>
+    <col width="13.375" customWidth="1" style="27" min="2552" max="2552"/>
+    <col width="9.875" customWidth="1" style="27" min="2553" max="2556"/>
+    <col width="10.75" customWidth="1" style="27" min="2557" max="2557"/>
+    <col width="9.875" customWidth="1" style="27" min="2558" max="2559"/>
+    <col width="14.875" customWidth="1" style="27" min="2560" max="2560"/>
+    <col width="23.875" customWidth="1" style="27" min="2561" max="2561"/>
+    <col width="13.25" customWidth="1" style="27" min="2562" max="2562"/>
+    <col width="9.125" customWidth="1" style="27" min="2563" max="2805"/>
+    <col width="7" customWidth="1" style="27" min="2806" max="2806"/>
+    <col width="14.75" customWidth="1" style="27" min="2807" max="2807"/>
+    <col width="13.375" customWidth="1" style="27" min="2808" max="2808"/>
+    <col width="9.875" customWidth="1" style="27" min="2809" max="2812"/>
+    <col width="10.75" customWidth="1" style="27" min="2813" max="2813"/>
+    <col width="9.875" customWidth="1" style="27" min="2814" max="2815"/>
+    <col width="14.875" customWidth="1" style="27" min="2816" max="2816"/>
+    <col width="23.875" customWidth="1" style="27" min="2817" max="2817"/>
+    <col width="13.25" customWidth="1" style="27" min="2818" max="2818"/>
+    <col width="9.125" customWidth="1" style="27" min="2819" max="3061"/>
+    <col width="7" customWidth="1" style="27" min="3062" max="3062"/>
+    <col width="14.75" customWidth="1" style="27" min="3063" max="3063"/>
+    <col width="13.375" customWidth="1" style="27" min="3064" max="3064"/>
+    <col width="9.875" customWidth="1" style="27" min="3065" max="3068"/>
+    <col width="10.75" customWidth="1" style="27" min="3069" max="3069"/>
+    <col width="9.875" customWidth="1" style="27" min="3070" max="3071"/>
+    <col width="14.875" customWidth="1" style="27" min="3072" max="3072"/>
+    <col width="23.875" customWidth="1" style="27" min="3073" max="3073"/>
+    <col width="13.25" customWidth="1" style="27" min="3074" max="3074"/>
+    <col width="9.125" customWidth="1" style="27" min="3075" max="3317"/>
+    <col width="7" customWidth="1" style="27" min="3318" max="3318"/>
+    <col width="14.75" customWidth="1" style="27" min="3319" max="3319"/>
+    <col width="13.375" customWidth="1" style="27" min="3320" max="3320"/>
+    <col width="9.875" customWidth="1" style="27" min="3321" max="3324"/>
+    <col width="10.75" customWidth="1" style="27" min="3325" max="3325"/>
+    <col width="9.875" customWidth="1" style="27" min="3326" max="3327"/>
+    <col width="14.875" customWidth="1" style="27" min="3328" max="3328"/>
+    <col width="23.875" customWidth="1" style="27" min="3329" max="3329"/>
+    <col width="13.25" customWidth="1" style="27" min="3330" max="3330"/>
+    <col width="9.125" customWidth="1" style="27" min="3331" max="3573"/>
+    <col width="7" customWidth="1" style="27" min="3574" max="3574"/>
+    <col width="14.75" customWidth="1" style="27" min="3575" max="3575"/>
+    <col width="13.375" customWidth="1" style="27" min="3576" max="3576"/>
+    <col width="9.875" customWidth="1" style="27" min="3577" max="3580"/>
+    <col width="10.75" customWidth="1" style="27" min="3581" max="3581"/>
+    <col width="9.875" customWidth="1" style="27" min="3582" max="3583"/>
+    <col width="14.875" customWidth="1" style="27" min="3584" max="3584"/>
+    <col width="23.875" customWidth="1" style="27" min="3585" max="3585"/>
+    <col width="13.25" customWidth="1" style="27" min="3586" max="3586"/>
+    <col width="9.125" customWidth="1" style="27" min="3587" max="3829"/>
+    <col width="7" customWidth="1" style="27" min="3830" max="3830"/>
+    <col width="14.75" customWidth="1" style="27" min="3831" max="3831"/>
+    <col width="13.375" customWidth="1" style="27" min="3832" max="3832"/>
+    <col width="9.875" customWidth="1" style="27" min="3833" max="3836"/>
+    <col width="10.75" customWidth="1" style="27" min="3837" max="3837"/>
+    <col width="9.875" customWidth="1" style="27" min="3838" max="3839"/>
+    <col width="14.875" customWidth="1" style="27" min="3840" max="3840"/>
+    <col width="23.875" customWidth="1" style="27" min="3841" max="3841"/>
+    <col width="13.25" customWidth="1" style="27" min="3842" max="3842"/>
+    <col width="9.125" customWidth="1" style="27" min="3843" max="4085"/>
+    <col width="7" customWidth="1" style="27" min="4086" max="4086"/>
+    <col width="14.75" customWidth="1" style="27" min="4087" max="4087"/>
+    <col width="13.375" customWidth="1" style="27" min="4088" max="4088"/>
+    <col width="9.875" customWidth="1" style="27" min="4089" max="4092"/>
+    <col width="10.75" customWidth="1" style="27" min="4093" max="4093"/>
+    <col width="9.875" customWidth="1" style="27" min="4094" max="4095"/>
+    <col width="14.875" customWidth="1" style="27" min="4096" max="4096"/>
+    <col width="23.875" customWidth="1" style="27" min="4097" max="4097"/>
+    <col width="13.25" customWidth="1" style="27" min="4098" max="4098"/>
+    <col width="9.125" customWidth="1" style="27" min="4099" max="4341"/>
+    <col width="7" customWidth="1" style="27" min="4342" max="4342"/>
+    <col width="14.75" customWidth="1" style="27" min="4343" max="4343"/>
+    <col width="13.375" customWidth="1" style="27" min="4344" max="4344"/>
+    <col width="9.875" customWidth="1" style="27" min="4345" max="4348"/>
+    <col width="10.75" customWidth="1" style="27" min="4349" max="4349"/>
+    <col width="9.875" customWidth="1" style="27" min="4350" max="4351"/>
+    <col width="14.875" customWidth="1" style="27" min="4352" max="4352"/>
+    <col width="23.875" customWidth="1" style="27" min="4353" max="4353"/>
+    <col width="13.25" customWidth="1" style="27" min="4354" max="4354"/>
+    <col width="9.125" customWidth="1" style="27" min="4355" max="4597"/>
+    <col width="7" customWidth="1" style="27" min="4598" max="4598"/>
+    <col width="14.75" customWidth="1" style="27" min="4599" max="4599"/>
+    <col width="13.375" customWidth="1" style="27" min="4600" max="4600"/>
+    <col width="9.875" customWidth="1" style="27" min="4601" max="4604"/>
+    <col width="10.75" customWidth="1" style="27" min="4605" max="4605"/>
+    <col width="9.875" customWidth="1" style="27" min="4606" max="4607"/>
+    <col width="14.875" customWidth="1" style="27" min="4608" max="4608"/>
+    <col width="23.875" customWidth="1" style="27" min="4609" max="4609"/>
+    <col width="13.25" customWidth="1" style="27" min="4610" max="4610"/>
+    <col width="9.125" customWidth="1" style="27" min="4611" max="4853"/>
+    <col width="7" customWidth="1" style="27" min="4854" max="4854"/>
+    <col width="14.75" customWidth="1" style="27" min="4855" max="4855"/>
+    <col width="13.375" customWidth="1" style="27" min="4856" max="4856"/>
+    <col width="9.875" customWidth="1" style="27" min="4857" max="4860"/>
+    <col width="10.75" customWidth="1" style="27" min="4861" max="4861"/>
+    <col width="9.875" customWidth="1" style="27" min="4862" max="4863"/>
+    <col width="14.875" customWidth="1" style="27" min="4864" max="4864"/>
+    <col width="23.875" customWidth="1" style="27" min="4865" max="4865"/>
+    <col width="13.25" customWidth="1" style="27" min="4866" max="4866"/>
+    <col width="9.125" customWidth="1" style="27" min="4867" max="5109"/>
+    <col width="7" customWidth="1" style="27" min="5110" max="5110"/>
+    <col width="14.75" customWidth="1" style="27" min="5111" max="5111"/>
+    <col width="13.375" customWidth="1" style="27" min="5112" max="5112"/>
+    <col width="9.875" customWidth="1" style="27" min="5113" max="5116"/>
+    <col width="10.75" customWidth="1" style="27" min="5117" max="5117"/>
+    <col width="9.875" customWidth="1" style="27" min="5118" max="5119"/>
+    <col width="14.875" customWidth="1" style="27" min="5120" max="5120"/>
+    <col width="23.875" customWidth="1" style="27" min="5121" max="5121"/>
+    <col width="13.25" customWidth="1" style="27" min="5122" max="5122"/>
+    <col width="9.125" customWidth="1" style="27" min="5123" max="5365"/>
+    <col width="7" customWidth="1" style="27" min="5366" max="5366"/>
+    <col width="14.75" customWidth="1" style="27" min="5367" max="5367"/>
+    <col width="13.375" customWidth="1" style="27" min="5368" max="5368"/>
+    <col width="9.875" customWidth="1" style="27" min="5369" max="5372"/>
+    <col width="10.75" customWidth="1" style="27" min="5373" max="5373"/>
+    <col width="9.875" customWidth="1" style="27" min="5374" max="5375"/>
+    <col width="14.875" customWidth="1" style="27" min="5376" max="5376"/>
+    <col width="23.875" customWidth="1" style="27" min="5377" max="5377"/>
+    <col width="13.25" customWidth="1" style="27" min="5378" max="5378"/>
+    <col width="9.125" customWidth="1" style="27" min="5379" max="5621"/>
+    <col width="7" customWidth="1" style="27" min="5622" max="5622"/>
+    <col width="14.75" customWidth="1" style="27" min="5623" max="5623"/>
+    <col width="13.375" customWidth="1" style="27" min="5624" max="5624"/>
+    <col width="9.875" customWidth="1" style="27" min="5625" max="5628"/>
+    <col width="10.75" customWidth="1" style="27" min="5629" max="5629"/>
+    <col width="9.875" customWidth="1" style="27" min="5630" max="5631"/>
+    <col width="14.875" customWidth="1" style="27" min="5632" max="5632"/>
+    <col width="23.875" customWidth="1" style="27" min="5633" max="5633"/>
+    <col width="13.25" customWidth="1" style="27" min="5634" max="5634"/>
+    <col width="9.125" customWidth="1" style="27" min="5635" max="5877"/>
+    <col width="7" customWidth="1" style="27" min="5878" max="5878"/>
+    <col width="14.75" customWidth="1" style="27" min="5879" max="5879"/>
+    <col width="13.375" customWidth="1" style="27" min="5880" max="5880"/>
+    <col width="9.875" customWidth="1" style="27" min="5881" max="5884"/>
+    <col width="10.75" customWidth="1" style="27" min="5885" max="5885"/>
+    <col width="9.875" customWidth="1" style="27" min="5886" max="5887"/>
+    <col width="14.875" customWidth="1" style="27" min="5888" max="5888"/>
+    <col width="23.875" customWidth="1" style="27" min="5889" max="5889"/>
+    <col width="13.25" customWidth="1" style="27" min="5890" max="5890"/>
+    <col width="9.125" customWidth="1" style="27" min="5891" max="6133"/>
+    <col width="7" customWidth="1" style="27" min="6134" max="6134"/>
+    <col width="14.75" customWidth="1" style="27" min="6135" max="6135"/>
+    <col width="13.375" customWidth="1" style="27" min="6136" max="6136"/>
+    <col width="9.875" customWidth="1" style="27" min="6137" max="6140"/>
+    <col width="10.75" customWidth="1" style="27" min="6141" max="6141"/>
+    <col width="9.875" customWidth="1" style="27" min="6142" max="6143"/>
+    <col width="14.875" customWidth="1" style="27" min="6144" max="6144"/>
+    <col width="23.875" customWidth="1" style="27" min="6145" max="6145"/>
+    <col width="13.25" customWidth="1" style="27" min="6146" max="6146"/>
+    <col width="9.125" customWidth="1" style="27" min="6147" max="6389"/>
+    <col width="7" customWidth="1" style="27" min="6390" max="6390"/>
+    <col width="14.75" customWidth="1" style="27" min="6391" max="6391"/>
+    <col width="13.375" customWidth="1" style="27" min="6392" max="6392"/>
+    <col width="9.875" customWidth="1" style="27" min="6393" max="6396"/>
+    <col width="10.75" customWidth="1" style="27" min="6397" max="6397"/>
+    <col width="9.875" customWidth="1" style="27" min="6398" max="6399"/>
+    <col width="14.875" customWidth="1" style="27" min="6400" max="6400"/>
+    <col width="23.875" customWidth="1" style="27" min="6401" max="6401"/>
+    <col width="13.25" customWidth="1" style="27" min="6402" max="6402"/>
+    <col width="9.125" customWidth="1" style="27" min="6403" max="6645"/>
+    <col width="7" customWidth="1" style="27" min="6646" max="6646"/>
+    <col width="14.75" customWidth="1" style="27" min="6647" max="6647"/>
+    <col width="13.375" customWidth="1" style="27" min="6648" max="6648"/>
+    <col width="9.875" customWidth="1" style="27" min="6649" max="6652"/>
+    <col width="10.75" customWidth="1" style="27" min="6653" max="6653"/>
+    <col width="9.875" customWidth="1" style="27" min="6654" max="6655"/>
+    <col width="14.875" customWidth="1" style="27" min="6656" max="6656"/>
+    <col width="23.875" customWidth="1" style="27" min="6657" max="6657"/>
+    <col width="13.25" customWidth="1" style="27" min="6658" max="6658"/>
+    <col width="9.125" customWidth="1" style="27" min="6659" max="6901"/>
+    <col width="7" customWidth="1" style="27" min="6902" max="6902"/>
+    <col width="14.75" customWidth="1" style="27" min="6903" max="6903"/>
+    <col width="13.375" customWidth="1" style="27" min="6904" max="6904"/>
+    <col width="9.875" customWidth="1" style="27" min="6905" max="6908"/>
+    <col width="10.75" customWidth="1" style="27" min="6909" max="6909"/>
+    <col width="9.875" customWidth="1" style="27" min="6910" max="6911"/>
+    <col width="14.875" customWidth="1" style="27" min="6912" max="6912"/>
+    <col width="23.875" customWidth="1" style="27" min="6913" max="6913"/>
+    <col width="13.25" customWidth="1" style="27" min="6914" max="6914"/>
+    <col width="9.125" customWidth="1" style="27" min="6915" max="7157"/>
+    <col width="7" customWidth="1" style="27" min="7158" max="7158"/>
+    <col width="14.75" customWidth="1" style="27" min="7159" max="7159"/>
+    <col width="13.375" customWidth="1" style="27" min="7160" max="7160"/>
+    <col width="9.875" customWidth="1" style="27" min="7161" max="7164"/>
+    <col width="10.75" customWidth="1" style="27" min="7165" max="7165"/>
+    <col width="9.875" customWidth="1" style="27" min="7166" max="7167"/>
+    <col width="14.875" customWidth="1" style="27" min="7168" max="7168"/>
+    <col width="23.875" customWidth="1" style="27" min="7169" max="7169"/>
+    <col width="13.25" customWidth="1" style="27" min="7170" max="7170"/>
+    <col width="9.125" customWidth="1" style="27" min="7171" max="7413"/>
+    <col width="7" customWidth="1" style="27" min="7414" max="7414"/>
+    <col width="14.75" customWidth="1" style="27" min="7415" max="7415"/>
+    <col width="13.375" customWidth="1" style="27" min="7416" max="7416"/>
+    <col width="9.875" customWidth="1" style="27" min="7417" max="7420"/>
+    <col width="10.75" customWidth="1" style="27" min="7421" max="7421"/>
+    <col width="9.875" customWidth="1" style="27" min="7422" max="7423"/>
+    <col width="14.875" customWidth="1" style="27" min="7424" max="7424"/>
+    <col width="23.875" customWidth="1" style="27" min="7425" max="7425"/>
+    <col width="13.25" customWidth="1" style="27" min="7426" max="7426"/>
+    <col width="9.125" customWidth="1" style="27" min="7427" max="7669"/>
+    <col width="7" customWidth="1" style="27" min="7670" max="7670"/>
+    <col width="14.75" customWidth="1" style="27" min="7671" max="7671"/>
+    <col width="13.375" customWidth="1" style="27" min="7672" max="7672"/>
+    <col width="9.875" customWidth="1" style="27" min="7673" max="7676"/>
+    <col width="10.75" customWidth="1" style="27" min="7677" max="7677"/>
+    <col width="9.875" customWidth="1" style="27" min="7678" max="7679"/>
+    <col width="14.875" customWidth="1" style="27" min="7680" max="7680"/>
+    <col width="23.875" customWidth="1" style="27" min="7681" max="7681"/>
+    <col width="13.25" customWidth="1" style="27" min="7682" max="7682"/>
+    <col width="9.125" customWidth="1" style="27" min="7683" max="7925"/>
+    <col width="7" customWidth="1" style="27" min="7926" max="7926"/>
+    <col width="14.75" customWidth="1" style="27" min="7927" max="7927"/>
+    <col width="13.375" customWidth="1" style="27" min="7928" max="7928"/>
+    <col width="9.875" customWidth="1" style="27" min="7929" max="7932"/>
+    <col width="10.75" customWidth="1" style="27" min="7933" max="7933"/>
+    <col width="9.875" customWidth="1" style="27" min="7934" max="7935"/>
+    <col width="14.875" customWidth="1" style="27" min="7936" max="7936"/>
+    <col width="23.875" customWidth="1" style="27" min="7937" max="7937"/>
+    <col width="13.25" customWidth="1" style="27" min="7938" max="7938"/>
+    <col width="9.125" customWidth="1" style="27" min="7939" max="8181"/>
+    <col width="7" customWidth="1" style="27" min="8182" max="8182"/>
+    <col width="14.75" customWidth="1" style="27" min="8183" max="8183"/>
+    <col width="13.375" customWidth="1" style="27" min="8184" max="8184"/>
+    <col width="9.875" customWidth="1" style="27" min="8185" max="8188"/>
+    <col width="10.75" customWidth="1" style="27" min="8189" max="8189"/>
+    <col width="9.875" customWidth="1" style="27" min="8190" max="8191"/>
+    <col width="14.875" customWidth="1" style="27" min="8192" max="8192"/>
+    <col width="23.875" customWidth="1" style="27" min="8193" max="8193"/>
+    <col width="13.25" customWidth="1" style="27" min="8194" max="8194"/>
+    <col width="9.125" customWidth="1" style="27" min="8195" max="8437"/>
+    <col width="7" customWidth="1" style="27" min="8438" max="8438"/>
+    <col width="14.75" customWidth="1" style="27" min="8439" max="8439"/>
+    <col width="13.375" customWidth="1" style="27" min="8440" max="8440"/>
+    <col width="9.875" customWidth="1" style="27" min="8441" max="8444"/>
+    <col width="10.75" customWidth="1" style="27" min="8445" max="8445"/>
+    <col width="9.875" customWidth="1" style="27" min="8446" max="8447"/>
+    <col width="14.875" customWidth="1" style="27" min="8448" max="8448"/>
+    <col width="23.875" customWidth="1" style="27" min="8449" max="8449"/>
+    <col width="13.25" customWidth="1" style="27" min="8450" max="8450"/>
+    <col width="9.125" customWidth="1" style="27" min="8451" max="8693"/>
+    <col width="7" customWidth="1" style="27" min="8694" max="8694"/>
+    <col width="14.75" customWidth="1" style="27" min="8695" max="8695"/>
+    <col width="13.375" customWidth="1" style="27" min="8696" max="8696"/>
+    <col width="9.875" customWidth="1" style="27" min="8697" max="8700"/>
+    <col width="10.75" customWidth="1" style="27" min="8701" max="8701"/>
+    <col width="9.875" customWidth="1" style="27" min="8702" max="8703"/>
+    <col width="14.875" customWidth="1" style="27" min="8704" max="8704"/>
+    <col width="23.875" customWidth="1" style="27" min="8705" max="8705"/>
+    <col width="13.25" customWidth="1" style="27" min="8706" max="8706"/>
+    <col width="9.125" customWidth="1" style="27" min="8707" max="8949"/>
+    <col width="7" customWidth="1" style="27" min="8950" max="8950"/>
+    <col width="14.75" customWidth="1" style="27" min="8951" max="8951"/>
+    <col width="13.375" customWidth="1" style="27" min="8952" max="8952"/>
+    <col width="9.875" customWidth="1" style="27" min="8953" max="8956"/>
+    <col width="10.75" customWidth="1" style="27" min="8957" max="8957"/>
+    <col width="9.875" customWidth="1" style="27" min="8958" max="8959"/>
+    <col width="14.875" customWidth="1" style="27" min="8960" max="8960"/>
+    <col width="23.875" customWidth="1" style="27" min="8961" max="8961"/>
+    <col width="13.25" customWidth="1" style="27" min="8962" max="8962"/>
+    <col width="9.125" customWidth="1" style="27" min="8963" max="9205"/>
+    <col width="7" customWidth="1" style="27" min="9206" max="9206"/>
+    <col width="14.75" customWidth="1" style="27" min="9207" max="9207"/>
+    <col width="13.375" customWidth="1" style="27" min="9208" max="9208"/>
+    <col width="9.875" customWidth="1" style="27" min="9209" max="9212"/>
+    <col width="10.75" customWidth="1" style="27" min="9213" max="9213"/>
+    <col width="9.875" customWidth="1" style="27" min="9214" max="9215"/>
+    <col width="14.875" customWidth="1" style="27" min="9216" max="9216"/>
+    <col width="23.875" customWidth="1" style="27" min="9217" max="9217"/>
+    <col width="13.25" customWidth="1" style="27" min="9218" max="9218"/>
+    <col width="9.125" customWidth="1" style="27" min="9219" max="9461"/>
+    <col width="7" customWidth="1" style="27" min="9462" max="9462"/>
+    <col width="14.75" customWidth="1" style="27" min="9463" max="9463"/>
+    <col width="13.375" customWidth="1" style="27" min="9464" max="9464"/>
+    <col width="9.875" customWidth="1" style="27" min="9465" max="9468"/>
+    <col width="10.75" customWidth="1" style="27" min="9469" max="9469"/>
+    <col width="9.875" customWidth="1" style="27" min="9470" max="9471"/>
+    <col width="14.875" customWidth="1" style="27" min="9472" max="9472"/>
+    <col width="23.875" customWidth="1" style="27" min="9473" max="9473"/>
+    <col width="13.25" customWidth="1" style="27" min="9474" max="9474"/>
+    <col width="9.125" customWidth="1" style="27" min="9475" max="9717"/>
+    <col width="7" customWidth="1" style="27" min="9718" max="9718"/>
+    <col width="14.75" customWidth="1" style="27" min="9719" max="9719"/>
+    <col width="13.375" customWidth="1" style="27" min="9720" max="9720"/>
+    <col width="9.875" customWidth="1" style="27" min="9721" max="9724"/>
+    <col width="10.75" customWidth="1" style="27" min="9725" max="9725"/>
+    <col width="9.875" customWidth="1" style="27" min="9726" max="9727"/>
+    <col width="14.875" customWidth="1" style="27" min="9728" max="9728"/>
+    <col width="23.875" customWidth="1" style="27" min="9729" max="9729"/>
+    <col width="13.25" customWidth="1" style="27" min="9730" max="9730"/>
+    <col width="9.125" customWidth="1" style="27" min="9731" max="9973"/>
+    <col width="7" customWidth="1" style="27" min="9974" max="9974"/>
+    <col width="14.75" customWidth="1" style="27" min="9975" max="9975"/>
+    <col width="13.375" customWidth="1" style="27" min="9976" max="9976"/>
+    <col width="9.875" customWidth="1" style="27" min="9977" max="9980"/>
+    <col width="10.75" customWidth="1" style="27" min="9981" max="9981"/>
+    <col width="9.875" customWidth="1" style="27" min="9982" max="9983"/>
+    <col width="14.875" customWidth="1" style="27" min="9984" max="9984"/>
+    <col width="23.875" customWidth="1" style="27" min="9985" max="9985"/>
+    <col width="13.25" customWidth="1" style="27" min="9986" max="9986"/>
+    <col width="9.125" customWidth="1" style="27" min="9987" max="10229"/>
+    <col width="7" customWidth="1" style="27" min="10230" max="10230"/>
+    <col width="14.75" customWidth="1" style="27" min="10231" max="10231"/>
+    <col width="13.375" customWidth="1" style="27" min="10232" max="10232"/>
+    <col width="9.875" customWidth="1" style="27" min="10233" max="10236"/>
+    <col width="10.75" customWidth="1" style="27" min="10237" max="10237"/>
+    <col width="9.875" customWidth="1" style="27" min="10238" max="10239"/>
+    <col width="14.875" customWidth="1" style="27" min="10240" max="10240"/>
+    <col width="23.875" customWidth="1" style="27" min="10241" max="10241"/>
+    <col width="13.25" customWidth="1" style="27" min="10242" max="10242"/>
+    <col width="9.125" customWidth="1" style="27" min="10243" max="10485"/>
+    <col width="7" customWidth="1" style="27" min="10486" max="10486"/>
+    <col width="14.75" customWidth="1" style="27" min="10487" max="10487"/>
+    <col width="13.375" customWidth="1" style="27" min="10488" max="10488"/>
+    <col width="9.875" customWidth="1" style="27" min="10489" max="10492"/>
+    <col width="10.75" customWidth="1" style="27" min="10493" max="10493"/>
+    <col width="9.875" customWidth="1" style="27" min="10494" max="10495"/>
+    <col width="14.875" customWidth="1" style="27" min="10496" max="10496"/>
+    <col width="23.875" customWidth="1" style="27" min="10497" max="10497"/>
+    <col width="13.25" customWidth="1" style="27" min="10498" max="10498"/>
+    <col width="9.125" customWidth="1" style="27" min="10499" max="10741"/>
+    <col width="7" customWidth="1" style="27" min="10742" max="10742"/>
+    <col width="14.75" customWidth="1" style="27" min="10743" max="10743"/>
+    <col width="13.375" customWidth="1" style="27" min="10744" max="10744"/>
+    <col width="9.875" customWidth="1" style="27" min="10745" max="10748"/>
+    <col width="10.75" customWidth="1" style="27" min="10749" max="10749"/>
+    <col width="9.875" customWidth="1" style="27" min="10750" max="10751"/>
+    <col width="14.875" customWidth="1" style="27" min="10752" max="10752"/>
+    <col width="23.875" customWidth="1" style="27" min="10753" max="10753"/>
+    <col width="13.25" customWidth="1" style="27" min="10754" max="10754"/>
+    <col width="9.125" customWidth="1" style="27" min="10755" max="10997"/>
+    <col width="7" customWidth="1" style="27" min="10998" max="10998"/>
+    <col width="14.75" customWidth="1" style="27" min="10999" max="10999"/>
+    <col width="13.375" customWidth="1" style="27" min="11000" max="11000"/>
+    <col width="9.875" customWidth="1" style="27" min="11001" max="11004"/>
+    <col width="10.75" customWidth="1" style="27" min="11005" max="11005"/>
+    <col width="9.875" customWidth="1" style="27" min="11006" max="11007"/>
+    <col width="14.875" customWidth="1" style="27" min="11008" max="11008"/>
+    <col width="23.875" customWidth="1" style="27" min="11009" max="11009"/>
+    <col width="13.25" customWidth="1" style="27" min="11010" max="11010"/>
+    <col width="9.125" customWidth="1" style="27" min="11011" max="11253"/>
+    <col width="7" customWidth="1" style="27" min="11254" max="11254"/>
+    <col width="14.75" customWidth="1" style="27" min="11255" max="11255"/>
+    <col width="13.375" customWidth="1" style="27" min="11256" max="11256"/>
+    <col width="9.875" customWidth="1" style="27" min="11257" max="11260"/>
+    <col width="10.75" customWidth="1" style="27" min="11261" max="11261"/>
+    <col width="9.875" customWidth="1" style="27" min="11262" max="11263"/>
+    <col width="14.875" customWidth="1" style="27" min="11264" max="11264"/>
+    <col width="23.875" customWidth="1" style="27" min="11265" max="11265"/>
+    <col width="13.25" customWidth="1" style="27" min="11266" max="11266"/>
+    <col width="9.125" customWidth="1" style="27" min="11267" max="11509"/>
+    <col width="7" customWidth="1" style="27" min="11510" max="11510"/>
+    <col width="14.75" customWidth="1" style="27" min="11511" max="11511"/>
+    <col width="13.375" customWidth="1" style="27" min="11512" max="11512"/>
+    <col width="9.875" customWidth="1" style="27" min="11513" max="11516"/>
+    <col width="10.75" customWidth="1" style="27" min="11517" max="11517"/>
+    <col width="9.875" customWidth="1" style="27" min="11518" max="11519"/>
+    <col width="14.875" customWidth="1" style="27" min="11520" max="11520"/>
+    <col width="23.875" customWidth="1" style="27" min="11521" max="11521"/>
+    <col width="13.25" customWidth="1" style="27" min="11522" max="11522"/>
+    <col width="9.125" customWidth="1" style="27" min="11523" max="11765"/>
+    <col width="7" customWidth="1" style="27" min="11766" max="11766"/>
+    <col width="14.75" customWidth="1" style="27" min="11767" max="11767"/>
+    <col width="13.375" customWidth="1" style="27" min="11768" max="11768"/>
+    <col width="9.875" customWidth="1" style="27" min="11769" max="11772"/>
+    <col width="10.75" customWidth="1" style="27" min="11773" max="11773"/>
+    <col width="9.875" customWidth="1" style="27" min="11774" max="11775"/>
+    <col width="14.875" customWidth="1" style="27" min="11776" max="11776"/>
+    <col width="23.875" customWidth="1" style="27" min="11777" max="11777"/>
+    <col width="13.25" customWidth="1" style="27" min="11778" max="11778"/>
+    <col width="9.125" customWidth="1" style="27" min="11779" max="12021"/>
+    <col width="7" customWidth="1" style="27" min="12022" max="12022"/>
+    <col width="14.75" customWidth="1" style="27" min="12023" max="12023"/>
+    <col width="13.375" customWidth="1" style="27" min="12024" max="12024"/>
+    <col width="9.875" customWidth="1" style="27" min="12025" max="12028"/>
+    <col width="10.75" customWidth="1" style="27" min="12029" max="12029"/>
+    <col width="9.875" customWidth="1" style="27" min="12030" max="12031"/>
+    <col width="14.875" customWidth="1" style="27" min="12032" max="12032"/>
+    <col width="23.875" customWidth="1" style="27" min="12033" max="12033"/>
+    <col width="13.25" customWidth="1" style="27" min="12034" max="12034"/>
+    <col width="9.125" customWidth="1" style="27" min="12035" max="12277"/>
+    <col width="7" customWidth="1" style="27" min="12278" max="12278"/>
+    <col width="14.75" customWidth="1" style="27" min="12279" max="12279"/>
+    <col width="13.375" customWidth="1" style="27" min="12280" max="12280"/>
+    <col width="9.875" customWidth="1" style="27" min="12281" max="12284"/>
+    <col width="10.75" customWidth="1" style="27" min="12285" max="12285"/>
+    <col width="9.875" customWidth="1" style="27" min="12286" max="12287"/>
+    <col width="14.875" customWidth="1" style="27" min="12288" max="12288"/>
+    <col width="23.875" customWidth="1" style="27" min="12289" max="12289"/>
+    <col width="13.25" customWidth="1" style="27" min="12290" max="12290"/>
+    <col width="9.125" customWidth="1" style="27" min="12291" max="12533"/>
+    <col width="7" customWidth="1" style="27" min="12534" max="12534"/>
+    <col width="14.75" customWidth="1" style="27" min="12535" max="12535"/>
+    <col width="13.375" customWidth="1" style="27" min="12536" max="12536"/>
+    <col width="9.875" customWidth="1" style="27" min="12537" max="12540"/>
+    <col width="10.75" customWidth="1" style="27" min="12541" max="12541"/>
+    <col width="9.875" customWidth="1" style="27" min="12542" max="12543"/>
+    <col width="14.875" customWidth="1" style="27" min="12544" max="12544"/>
+    <col width="23.875" customWidth="1" style="27" min="12545" max="12545"/>
+    <col width="13.25" customWidth="1" style="27" min="12546" max="12546"/>
+    <col width="9.125" customWidth="1" style="27" min="12547" max="12789"/>
+    <col width="7" customWidth="1" style="27" min="12790" max="12790"/>
+    <col width="14.75" customWidth="1" style="27" min="12791" max="12791"/>
+    <col width="13.375" customWidth="1" style="27" min="12792" max="12792"/>
+    <col width="9.875" customWidth="1" style="27" min="12793" max="12796"/>
+    <col width="10.75" customWidth="1" style="27" min="12797" max="12797"/>
+    <col width="9.875" customWidth="1" style="27" min="12798" max="12799"/>
+    <col width="14.875" customWidth="1" style="27" min="12800" max="12800"/>
+    <col width="23.875" customWidth="1" style="27" min="12801" max="12801"/>
+    <col width="13.25" customWidth="1" style="27" min="12802" max="12802"/>
+    <col width="9.125" customWidth="1" style="27" min="12803" max="13045"/>
+    <col width="7" customWidth="1" style="27" min="13046" max="13046"/>
+    <col width="14.75" customWidth="1" style="27" min="13047" max="13047"/>
+    <col width="13.375" customWidth="1" style="27" min="13048" max="13048"/>
+    <col width="9.875" customWidth="1" style="27" min="13049" max="13052"/>
+    <col width="10.75" customWidth="1" style="27" min="13053" max="13053"/>
+    <col width="9.875" customWidth="1" style="27" min="13054" max="13055"/>
+    <col width="14.875" customWidth="1" style="27" min="13056" max="13056"/>
+    <col width="23.875" customWidth="1" style="27" min="13057" max="13057"/>
+    <col width="13.25" customWidth="1" style="27" min="13058" max="13058"/>
+    <col width="9.125" customWidth="1" style="27" min="13059" max="13301"/>
+    <col width="7" customWidth="1" style="27" min="13302" max="13302"/>
+    <col width="14.75" customWidth="1" style="27" min="13303" max="13303"/>
+    <col width="13.375" customWidth="1" style="27" min="13304" max="13304"/>
+    <col width="9.875" customWidth="1" style="27" min="13305" max="13308"/>
+    <col width="10.75" customWidth="1" style="27" min="13309" max="13309"/>
+    <col width="9.875" customWidth="1" style="27" min="13310" max="13311"/>
+    <col width="14.875" customWidth="1" style="27" min="13312" max="13312"/>
+    <col width="23.875" customWidth="1" style="27" min="13313" max="13313"/>
+    <col width="13.25" customWidth="1" style="27" min="13314" max="13314"/>
+    <col width="9.125" customWidth="1" style="27" min="13315" max="13557"/>
+    <col width="7" customWidth="1" style="27" min="13558" max="13558"/>
+    <col width="14.75" customWidth="1" style="27" min="13559" max="13559"/>
+    <col width="13.375" customWidth="1" style="27" min="13560" max="13560"/>
+    <col width="9.875" customWidth="1" style="27" min="13561" max="13564"/>
+    <col width="10.75" customWidth="1" style="27" min="13565" max="13565"/>
+    <col width="9.875" customWidth="1" style="27" min="13566" max="13567"/>
+    <col width="14.875" customWidth="1" style="27" min="13568" max="13568"/>
+    <col width="23.875" customWidth="1" style="27" min="13569" max="13569"/>
+    <col width="13.25" customWidth="1" style="27" min="13570" max="13570"/>
+    <col width="9.125" customWidth="1" style="27" min="13571" max="13813"/>
+    <col width="7" customWidth="1" style="27" min="13814" max="13814"/>
+    <col width="14.75" customWidth="1" style="27" min="13815" max="13815"/>
+    <col width="13.375" customWidth="1" style="27" min="13816" max="13816"/>
+    <col width="9.875" customWidth="1" style="27" min="13817" max="13820"/>
+    <col width="10.75" customWidth="1" style="27" min="13821" max="13821"/>
+    <col width="9.875" customWidth="1" style="27" min="13822" max="13823"/>
+    <col width="14.875" customWidth="1" style="27" min="13824" max="13824"/>
+    <col width="23.875" customWidth="1" style="27" min="13825" max="13825"/>
+    <col width="13.25" customWidth="1" style="27" min="13826" max="13826"/>
+    <col width="9.125" customWidth="1" style="27" min="13827" max="14069"/>
+    <col width="7" customWidth="1" style="27" min="14070" max="14070"/>
+    <col width="14.75" customWidth="1" style="27" min="14071" max="14071"/>
+    <col width="13.375" customWidth="1" style="27" min="14072" max="14072"/>
+    <col width="9.875" customWidth="1" style="27" min="14073" max="14076"/>
+    <col width="10.75" customWidth="1" style="27" min="14077" max="14077"/>
+    <col width="9.875" customWidth="1" style="27" min="14078" max="14079"/>
+    <col width="14.875" customWidth="1" style="27" min="14080" max="14080"/>
+    <col width="23.875" customWidth="1" style="27" min="14081" max="14081"/>
+    <col width="13.25" customWidth="1" style="27" min="14082" max="14082"/>
+    <col width="9.125" customWidth="1" style="27" min="14083" max="14325"/>
+    <col width="7" customWidth="1" style="27" min="14326" max="14326"/>
+    <col width="14.75" customWidth="1" style="27" min="14327" max="14327"/>
+    <col width="13.375" customWidth="1" style="27" min="14328" max="14328"/>
+    <col width="9.875" customWidth="1" style="27" min="14329" max="14332"/>
+    <col width="10.75" customWidth="1" style="27" min="14333" max="14333"/>
+    <col width="9.875" customWidth="1" style="27" min="14334" max="14335"/>
+    <col width="14.875" customWidth="1" style="27" min="14336" max="14336"/>
+    <col width="23.875" customWidth="1" style="27" min="14337" max="14337"/>
+    <col width="13.25" customWidth="1" style="27" min="14338" max="14338"/>
+    <col width="9.125" customWidth="1" style="27" min="14339" max="14581"/>
+    <col width="7" customWidth="1" style="27" min="14582" max="14582"/>
+    <col width="14.75" customWidth="1" style="27" min="14583" max="14583"/>
+    <col width="13.375" customWidth="1" style="27" min="14584" max="14584"/>
+    <col width="9.875" customWidth="1" style="27" min="14585" max="14588"/>
+    <col width="10.75" customWidth="1" style="27" min="14589" max="14589"/>
+    <col width="9.875" customWidth="1" style="27" min="14590" max="14591"/>
+    <col width="14.875" customWidth="1" style="27" min="14592" max="14592"/>
+    <col width="23.875" customWidth="1" style="27" min="14593" max="14593"/>
+    <col width="13.25" customWidth="1" style="27" min="14594" max="14594"/>
+    <col width="9.125" customWidth="1" style="27" min="14595" max="14837"/>
+    <col width="7" customWidth="1" style="27" min="14838" max="14838"/>
+    <col width="14.75" customWidth="1" style="27" min="14839" max="14839"/>
+    <col width="13.375" customWidth="1" style="27" min="14840" max="14840"/>
+    <col width="9.875" customWidth="1" style="27" min="14841" max="14844"/>
+    <col width="10.75" customWidth="1" style="27" min="14845" max="14845"/>
+    <col width="9.875" customWidth="1" style="27" min="14846" max="14847"/>
+    <col width="14.875" customWidth="1" style="27" min="14848" max="14848"/>
+    <col width="23.875" customWidth="1" style="27" min="14849" max="14849"/>
+    <col width="13.25" customWidth="1" style="27" min="14850" max="14850"/>
+    <col width="9.125" customWidth="1" style="27" min="14851" max="15093"/>
+    <col width="7" customWidth="1" style="27" min="15094" max="15094"/>
+    <col width="14.75" customWidth="1" style="27" min="15095" max="15095"/>
+    <col width="13.375" customWidth="1" style="27" min="15096" max="15096"/>
+    <col width="9.875" customWidth="1" style="27" min="15097" max="15100"/>
+    <col width="10.75" customWidth="1" style="27" min="15101" max="15101"/>
+    <col width="9.875" customWidth="1" style="27" min="15102" max="15103"/>
+    <col width="14.875" customWidth="1" style="27" min="15104" max="15104"/>
+    <col width="23.875" customWidth="1" style="27" min="15105" max="15105"/>
+    <col width="13.25" customWidth="1" style="27" min="15106" max="15106"/>
+    <col width="9.125" customWidth="1" style="27" min="15107" max="15349"/>
+    <col width="7" customWidth="1" style="27" min="15350" max="15350"/>
+    <col width="14.75" customWidth="1" style="27" min="15351" max="15351"/>
+    <col width="13.375" customWidth="1" style="27" min="15352" max="15352"/>
+    <col width="9.875" customWidth="1" style="27" min="15353" max="15356"/>
+    <col width="10.75" customWidth="1" style="27" min="15357" max="15357"/>
+    <col width="9.875" customWidth="1" style="27" min="15358" max="15359"/>
+    <col width="14.875" customWidth="1" style="27" min="15360" max="15360"/>
+    <col width="23.875" customWidth="1" style="27" min="15361" max="15361"/>
+    <col width="13.25" customWidth="1" style="27" min="15362" max="15362"/>
+    <col width="9.125" customWidth="1" style="27" min="15363" max="15605"/>
+    <col width="7" customWidth="1" style="27" min="15606" max="15606"/>
+    <col width="14.75" customWidth="1" style="27" min="15607" max="15607"/>
+    <col width="13.375" customWidth="1" style="27" min="15608" max="15608"/>
+    <col width="9.875" customWidth="1" style="27" min="15609" max="15612"/>
+    <col width="10.75" customWidth="1" style="27" min="15613" max="15613"/>
+    <col width="9.875" customWidth="1" style="27" min="15614" max="15615"/>
+    <col width="14.875" customWidth="1" style="27" min="15616" max="15616"/>
+    <col width="23.875" customWidth="1" style="27" min="15617" max="15617"/>
+    <col width="13.25" customWidth="1" style="27" min="15618" max="15618"/>
+    <col width="9.125" customWidth="1" style="27" min="15619" max="15861"/>
+    <col width="7" customWidth="1" style="27" min="15862" max="15862"/>
+    <col width="14.75" customWidth="1" style="27" min="15863" max="15863"/>
+    <col width="13.375" customWidth="1" style="27" min="15864" max="15864"/>
+    <col width="9.875" customWidth="1" style="27" min="15865" max="15868"/>
+    <col width="10.75" customWidth="1" style="27" min="15869" max="15869"/>
+    <col width="9.875" customWidth="1" style="27" min="15870" max="15871"/>
+    <col width="14.875" customWidth="1" style="27" min="15872" max="15872"/>
+    <col width="23.875" customWidth="1" style="27" min="15873" max="15873"/>
+    <col width="13.25" customWidth="1" style="27" min="15874" max="15874"/>
+    <col width="9.125" customWidth="1" style="27" min="15875" max="16117"/>
+    <col width="7" customWidth="1" style="27" min="16118" max="16118"/>
+    <col width="14.75" customWidth="1" style="27" min="16119" max="16119"/>
+    <col width="13.375" customWidth="1" style="27" min="16120" max="16120"/>
+    <col width="9.875" customWidth="1" style="27" min="16121" max="16124"/>
+    <col width="10.75" customWidth="1" style="27" min="16125" max="16125"/>
+    <col width="9.875" customWidth="1" style="27" min="16126" max="16127"/>
+    <col width="14.875" customWidth="1" style="27" min="16128" max="16128"/>
+    <col width="23.875" customWidth="1" style="27" min="16129" max="16129"/>
+    <col width="13.25" customWidth="1" style="27" min="16130" max="16130"/>
+    <col width="9.125" customWidth="1" style="27" min="16131" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>ใบตรวจสอบเครื่อง CNC</t>
+        </is>
+      </c>
+      <c r="AA1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="AA2" s="43" t="inlineStr">
+        <is>
+          <t>Machine No. : 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="41">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="16" t="n"/>
+      <c r="W3" s="16" t="n"/>
+      <c r="X3" s="16" t="n"/>
+      <c r="Y3" s="16" t="n"/>
+      <c r="Z3" s="16" t="n"/>
+      <c r="AA3" s="16" t="n"/>
+      <c r="AB3" s="16" t="n"/>
+      <c r="AC3" s="16" t="n"/>
+      <c r="AD3" s="16" t="n"/>
+      <c r="AE3" s="16" t="n"/>
+      <c r="AF3" s="16" t="n"/>
+      <c r="AG3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="18" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>การตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ประจำเดือน  ………………………………..</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+      <c r="K4" s="36" t="n"/>
+      <c r="L4" s="36" t="n"/>
+      <c r="M4" s="36" t="n"/>
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="36" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="36" t="n"/>
+      <c r="S4" s="36" t="n"/>
+      <c r="T4" s="36" t="n"/>
+      <c r="U4" s="36" t="n"/>
+      <c r="V4" s="36" t="n"/>
+      <c r="W4" s="36" t="n"/>
+      <c r="X4" s="36" t="n"/>
+      <c r="Y4" s="36" t="n"/>
+      <c r="Z4" s="36" t="n"/>
+      <c r="AA4" s="36" t="n"/>
+      <c r="AB4" s="36" t="n"/>
+      <c r="AC4" s="36" t="n"/>
+      <c r="AD4" s="36" t="n"/>
+      <c r="AE4" s="36" t="n"/>
+      <c r="AF4" s="36" t="n"/>
+      <c r="AG4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Worm up เครื่องจักร 15 นาที ทุกครั้งที่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="22" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="22" t="n"/>
+      <c r="AA6" s="23" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="22" t="n"/>
+      <c r="AD6" s="22" t="n"/>
+      <c r="AE6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>เช็คระดับนำมันที่ Pump Hydraulic ทุกวัน เติมเมื่อพร่อง</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="23" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>ทำความสะอาด Air filter Mesh ทุกวัน</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="22" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="23" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจเช็คแรงดัน Air Control Unit ปกติเฉลี่ยที่ 0.5 Mpa</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+      <c r="U9" s="22" t="n"/>
+      <c r="V9" s="22" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="22" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="22" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="22" t="n"/>
+      <c r="AC9" s="22" t="n"/>
+      <c r="AD9" s="22" t="n"/>
+      <c r="AE9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>เช็คน้ำมันชุด Gear ของ ATC ทุกวัน(เปลี่ยนถ่ายทุกปี)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="23" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>อัดจารบี Ballscrew และ Linear Guideทุก 1ครั้งต่อเดือน</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="23" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบการเคลื่อนที่ของแกนทุกแกน (X,Y,Z)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="23" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสภาพของน้ำ Coolant ถ่ายรูปค่าที่วัดได้ส่งเข้าระบบ</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="22" t="n"/>
+      <c r="U13" s="22" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Coolant pump</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Unclamp และการเปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="22" t="n"/>
+      <c r="U15" s="22" t="n"/>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="22" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Spindle</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="22" t="n"/>
+      <c r="U16" s="22" t="n"/>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="22" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="22" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+      <c r="AE16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Arm เปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="n"/>
+      <c r="U17" s="22" t="n"/>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="22" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบระดับของน้ำ Coolant เติมเมื่ออยู่ระดับที่ต่ำ</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="22" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ความสะอาดทั่วไปของเครื่องจักรโดยรวม</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="23" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบความพร้อมสภาพโดยรวม(ฟังด้วยหู ดูด้วยตา)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="23" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสายไฮโดรลิกส์ และสายลม</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="22" t="n"/>
+      <c r="AA21" s="23" t="n"/>
+      <c r="AB21" s="22" t="n"/>
+      <c r="AC21" s="22" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n"/>
+      <c r="R22" s="28" t="n"/>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="33" t="n"/>
+      <c r="Y22" s="33" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="33" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="28" t="n"/>
+      <c r="AE22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AF22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AG22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="29" t="n"/>
+      <c r="N23" s="29" t="n"/>
+      <c r="O23" s="29" t="n"/>
+      <c r="P23" s="29" t="n"/>
+      <c r="Q23" s="29" t="n"/>
+      <c r="R23" s="29" t="n"/>
+      <c r="S23" s="29" t="n"/>
+      <c r="T23" s="29" t="n"/>
+      <c r="U23" s="29" t="n"/>
+      <c r="V23" s="29" t="n"/>
+      <c r="W23" s="29" t="n"/>
+      <c r="X23" s="29" t="n"/>
+      <c r="Y23" s="29" t="n"/>
+      <c r="Z23" s="29" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="29" t="n"/>
+      <c r="AC23" s="29" t="n"/>
+      <c r="AD23" s="29" t="n"/>
+      <c r="AE23" s="29" t="n"/>
+      <c r="AF23" s="29" t="n"/>
+      <c r="AG23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
+      <c r="M24" s="30" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="30" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="30" t="n"/>
+      <c r="U24" s="30" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="30" t="n"/>
+      <c r="X24" s="44" t="n"/>
+      <c r="Y24" s="44" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="44" t="n"/>
+      <c r="AB24" s="30" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="30" t="n"/>
+      <c r="AF24" s="30" t="n"/>
+      <c r="AG24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="29" t="n"/>
+      <c r="N25" s="29" t="n"/>
+      <c r="O25" s="29" t="n"/>
+      <c r="P25" s="29" t="n"/>
+      <c r="Q25" s="29" t="n"/>
+      <c r="R25" s="29" t="n"/>
+      <c r="S25" s="29" t="n"/>
+      <c r="T25" s="29" t="n"/>
+      <c r="U25" s="29" t="n"/>
+      <c r="V25" s="29" t="n"/>
+      <c r="W25" s="29" t="n"/>
+      <c r="X25" s="29" t="n"/>
+      <c r="Y25" s="29" t="n"/>
+      <c r="Z25" s="29" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="29" t="n"/>
+      <c r="AC25" s="29" t="n"/>
+      <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
+      <c r="AG25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>บันทึกเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="Y27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="173.25" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="AA29" s="19" t="n"/>
+      <c r="AB29" s="31" t="n"/>
+      <c r="AC29" s="32" t="n"/>
+      <c r="AD29" s="32" t="n"/>
+      <c r="AE29" s="32" t="n"/>
+      <c r="AF29" s="32" t="n"/>
+      <c r="AG29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="29.25" customHeight="1">
+      <c r="AB30" s="26" t="inlineStr">
+        <is>
+          <t>ผู้จัดการแผนกซ่อมบำรุง</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1">
+      <c r="D31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="C32" s="18" t="n"/>
+      <c r="AG32" s="20" t="inlineStr">
+        <is>
+          <t>FM-MN-07 Rev.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="71">
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="77" blackAndWhite="1" horizontalDpi="4294967293" verticalDpi="4294967293"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -581,6 +581,94 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>33618</colOff>
+      <row>0</row>
+      <rowOff>11206</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>672353</colOff>
+      <row>2</row>
+      <rowOff>19163</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Picture 11" descr="LOGO PES.png"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="33618" y="11206"/>
+          <a:ext cx="963706" cy="657898"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>2206621</colOff>
+      <row>21</row>
+      <rowOff>42333</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>4413250</colOff>
+      <row>25</row>
+      <rowOff>31749</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip r:embed="rId2"/>
+        <a:srcRect r="8552"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="2571746" y="4836583"/>
+          <a:ext cx="2206629" cy="1132416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -866,4 +954,1965 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <cols>
+    <col width="4.875" customWidth="1" style="27" min="1" max="1"/>
+    <col width="58.5" customWidth="1" style="27" min="2" max="2"/>
+    <col width="3.375" customWidth="1" style="27" min="3" max="33"/>
+    <col width="9.125" customWidth="1" style="27" min="34" max="245"/>
+    <col width="7" customWidth="1" style="27" min="246" max="246"/>
+    <col width="14.75" customWidth="1" style="27" min="247" max="247"/>
+    <col width="13.375" customWidth="1" style="27" min="248" max="248"/>
+    <col width="9.875" customWidth="1" style="27" min="249" max="252"/>
+    <col width="10.75" customWidth="1" style="27" min="253" max="253"/>
+    <col width="9.875" customWidth="1" style="27" min="254" max="255"/>
+    <col width="14.875" customWidth="1" style="27" min="256" max="256"/>
+    <col width="23.875" customWidth="1" style="27" min="257" max="257"/>
+    <col width="13.25" customWidth="1" style="27" min="258" max="258"/>
+    <col width="9.125" customWidth="1" style="27" min="259" max="501"/>
+    <col width="7" customWidth="1" style="27" min="502" max="502"/>
+    <col width="14.75" customWidth="1" style="27" min="503" max="503"/>
+    <col width="13.375" customWidth="1" style="27" min="504" max="504"/>
+    <col width="9.875" customWidth="1" style="27" min="505" max="508"/>
+    <col width="10.75" customWidth="1" style="27" min="509" max="509"/>
+    <col width="9.875" customWidth="1" style="27" min="510" max="511"/>
+    <col width="14.875" customWidth="1" style="27" min="512" max="512"/>
+    <col width="23.875" customWidth="1" style="27" min="513" max="513"/>
+    <col width="13.25" customWidth="1" style="27" min="514" max="514"/>
+    <col width="9.125" customWidth="1" style="27" min="515" max="757"/>
+    <col width="7" customWidth="1" style="27" min="758" max="758"/>
+    <col width="14.75" customWidth="1" style="27" min="759" max="759"/>
+    <col width="13.375" customWidth="1" style="27" min="760" max="760"/>
+    <col width="9.875" customWidth="1" style="27" min="761" max="764"/>
+    <col width="10.75" customWidth="1" style="27" min="765" max="765"/>
+    <col width="9.875" customWidth="1" style="27" min="766" max="767"/>
+    <col width="14.875" customWidth="1" style="27" min="768" max="768"/>
+    <col width="23.875" customWidth="1" style="27" min="769" max="769"/>
+    <col width="13.25" customWidth="1" style="27" min="770" max="770"/>
+    <col width="9.125" customWidth="1" style="27" min="771" max="1013"/>
+    <col width="7" customWidth="1" style="27" min="1014" max="1014"/>
+    <col width="14.75" customWidth="1" style="27" min="1015" max="1015"/>
+    <col width="13.375" customWidth="1" style="27" min="1016" max="1016"/>
+    <col width="9.875" customWidth="1" style="27" min="1017" max="1020"/>
+    <col width="10.75" customWidth="1" style="27" min="1021" max="1021"/>
+    <col width="9.875" customWidth="1" style="27" min="1022" max="1023"/>
+    <col width="14.875" customWidth="1" style="27" min="1024" max="1024"/>
+    <col width="23.875" customWidth="1" style="27" min="1025" max="1025"/>
+    <col width="13.25" customWidth="1" style="27" min="1026" max="1026"/>
+    <col width="9.125" customWidth="1" style="27" min="1027" max="1269"/>
+    <col width="7" customWidth="1" style="27" min="1270" max="1270"/>
+    <col width="14.75" customWidth="1" style="27" min="1271" max="1271"/>
+    <col width="13.375" customWidth="1" style="27" min="1272" max="1272"/>
+    <col width="9.875" customWidth="1" style="27" min="1273" max="1276"/>
+    <col width="10.75" customWidth="1" style="27" min="1277" max="1277"/>
+    <col width="9.875" customWidth="1" style="27" min="1278" max="1279"/>
+    <col width="14.875" customWidth="1" style="27" min="1280" max="1280"/>
+    <col width="23.875" customWidth="1" style="27" min="1281" max="1281"/>
+    <col width="13.25" customWidth="1" style="27" min="1282" max="1282"/>
+    <col width="9.125" customWidth="1" style="27" min="1283" max="1525"/>
+    <col width="7" customWidth="1" style="27" min="1526" max="1526"/>
+    <col width="14.75" customWidth="1" style="27" min="1527" max="1527"/>
+    <col width="13.375" customWidth="1" style="27" min="1528" max="1528"/>
+    <col width="9.875" customWidth="1" style="27" min="1529" max="1532"/>
+    <col width="10.75" customWidth="1" style="27" min="1533" max="1533"/>
+    <col width="9.875" customWidth="1" style="27" min="1534" max="1535"/>
+    <col width="14.875" customWidth="1" style="27" min="1536" max="1536"/>
+    <col width="23.875" customWidth="1" style="27" min="1537" max="1537"/>
+    <col width="13.25" customWidth="1" style="27" min="1538" max="1538"/>
+    <col width="9.125" customWidth="1" style="27" min="1539" max="1781"/>
+    <col width="7" customWidth="1" style="27" min="1782" max="1782"/>
+    <col width="14.75" customWidth="1" style="27" min="1783" max="1783"/>
+    <col width="13.375" customWidth="1" style="27" min="1784" max="1784"/>
+    <col width="9.875" customWidth="1" style="27" min="1785" max="1788"/>
+    <col width="10.75" customWidth="1" style="27" min="1789" max="1789"/>
+    <col width="9.875" customWidth="1" style="27" min="1790" max="1791"/>
+    <col width="14.875" customWidth="1" style="27" min="1792" max="1792"/>
+    <col width="23.875" customWidth="1" style="27" min="1793" max="1793"/>
+    <col width="13.25" customWidth="1" style="27" min="1794" max="1794"/>
+    <col width="9.125" customWidth="1" style="27" min="1795" max="2037"/>
+    <col width="7" customWidth="1" style="27" min="2038" max="2038"/>
+    <col width="14.75" customWidth="1" style="27" min="2039" max="2039"/>
+    <col width="13.375" customWidth="1" style="27" min="2040" max="2040"/>
+    <col width="9.875" customWidth="1" style="27" min="2041" max="2044"/>
+    <col width="10.75" customWidth="1" style="27" min="2045" max="2045"/>
+    <col width="9.875" customWidth="1" style="27" min="2046" max="2047"/>
+    <col width="14.875" customWidth="1" style="27" min="2048" max="2048"/>
+    <col width="23.875" customWidth="1" style="27" min="2049" max="2049"/>
+    <col width="13.25" customWidth="1" style="27" min="2050" max="2050"/>
+    <col width="9.125" customWidth="1" style="27" min="2051" max="2293"/>
+    <col width="7" customWidth="1" style="27" min="2294" max="2294"/>
+    <col width="14.75" customWidth="1" style="27" min="2295" max="2295"/>
+    <col width="13.375" customWidth="1" style="27" min="2296" max="2296"/>
+    <col width="9.875" customWidth="1" style="27" min="2297" max="2300"/>
+    <col width="10.75" customWidth="1" style="27" min="2301" max="2301"/>
+    <col width="9.875" customWidth="1" style="27" min="2302" max="2303"/>
+    <col width="14.875" customWidth="1" style="27" min="2304" max="2304"/>
+    <col width="23.875" customWidth="1" style="27" min="2305" max="2305"/>
+    <col width="13.25" customWidth="1" style="27" min="2306" max="2306"/>
+    <col width="9.125" customWidth="1" style="27" min="2307" max="2549"/>
+    <col width="7" customWidth="1" style="27" min="2550" max="2550"/>
+    <col width="14.75" customWidth="1" style="27" min="2551" max="2551"/>
+    <col width="13.375" customWidth="1" style="27" min="2552" max="2552"/>
+    <col width="9.875" customWidth="1" style="27" min="2553" max="2556"/>
+    <col width="10.75" customWidth="1" style="27" min="2557" max="2557"/>
+    <col width="9.875" customWidth="1" style="27" min="2558" max="2559"/>
+    <col width="14.875" customWidth="1" style="27" min="2560" max="2560"/>
+    <col width="23.875" customWidth="1" style="27" min="2561" max="2561"/>
+    <col width="13.25" customWidth="1" style="27" min="2562" max="2562"/>
+    <col width="9.125" customWidth="1" style="27" min="2563" max="2805"/>
+    <col width="7" customWidth="1" style="27" min="2806" max="2806"/>
+    <col width="14.75" customWidth="1" style="27" min="2807" max="2807"/>
+    <col width="13.375" customWidth="1" style="27" min="2808" max="2808"/>
+    <col width="9.875" customWidth="1" style="27" min="2809" max="2812"/>
+    <col width="10.75" customWidth="1" style="27" min="2813" max="2813"/>
+    <col width="9.875" customWidth="1" style="27" min="2814" max="2815"/>
+    <col width="14.875" customWidth="1" style="27" min="2816" max="2816"/>
+    <col width="23.875" customWidth="1" style="27" min="2817" max="2817"/>
+    <col width="13.25" customWidth="1" style="27" min="2818" max="2818"/>
+    <col width="9.125" customWidth="1" style="27" min="2819" max="3061"/>
+    <col width="7" customWidth="1" style="27" min="3062" max="3062"/>
+    <col width="14.75" customWidth="1" style="27" min="3063" max="3063"/>
+    <col width="13.375" customWidth="1" style="27" min="3064" max="3064"/>
+    <col width="9.875" customWidth="1" style="27" min="3065" max="3068"/>
+    <col width="10.75" customWidth="1" style="27" min="3069" max="3069"/>
+    <col width="9.875" customWidth="1" style="27" min="3070" max="3071"/>
+    <col width="14.875" customWidth="1" style="27" min="3072" max="3072"/>
+    <col width="23.875" customWidth="1" style="27" min="3073" max="3073"/>
+    <col width="13.25" customWidth="1" style="27" min="3074" max="3074"/>
+    <col width="9.125" customWidth="1" style="27" min="3075" max="3317"/>
+    <col width="7" customWidth="1" style="27" min="3318" max="3318"/>
+    <col width="14.75" customWidth="1" style="27" min="3319" max="3319"/>
+    <col width="13.375" customWidth="1" style="27" min="3320" max="3320"/>
+    <col width="9.875" customWidth="1" style="27" min="3321" max="3324"/>
+    <col width="10.75" customWidth="1" style="27" min="3325" max="3325"/>
+    <col width="9.875" customWidth="1" style="27" min="3326" max="3327"/>
+    <col width="14.875" customWidth="1" style="27" min="3328" max="3328"/>
+    <col width="23.875" customWidth="1" style="27" min="3329" max="3329"/>
+    <col width="13.25" customWidth="1" style="27" min="3330" max="3330"/>
+    <col width="9.125" customWidth="1" style="27" min="3331" max="3573"/>
+    <col width="7" customWidth="1" style="27" min="3574" max="3574"/>
+    <col width="14.75" customWidth="1" style="27" min="3575" max="3575"/>
+    <col width="13.375" customWidth="1" style="27" min="3576" max="3576"/>
+    <col width="9.875" customWidth="1" style="27" min="3577" max="3580"/>
+    <col width="10.75" customWidth="1" style="27" min="3581" max="3581"/>
+    <col width="9.875" customWidth="1" style="27" min="3582" max="3583"/>
+    <col width="14.875" customWidth="1" style="27" min="3584" max="3584"/>
+    <col width="23.875" customWidth="1" style="27" min="3585" max="3585"/>
+    <col width="13.25" customWidth="1" style="27" min="3586" max="3586"/>
+    <col width="9.125" customWidth="1" style="27" min="3587" max="3829"/>
+    <col width="7" customWidth="1" style="27" min="3830" max="3830"/>
+    <col width="14.75" customWidth="1" style="27" min="3831" max="3831"/>
+    <col width="13.375" customWidth="1" style="27" min="3832" max="3832"/>
+    <col width="9.875" customWidth="1" style="27" min="3833" max="3836"/>
+    <col width="10.75" customWidth="1" style="27" min="3837" max="3837"/>
+    <col width="9.875" customWidth="1" style="27" min="3838" max="3839"/>
+    <col width="14.875" customWidth="1" style="27" min="3840" max="3840"/>
+    <col width="23.875" customWidth="1" style="27" min="3841" max="3841"/>
+    <col width="13.25" customWidth="1" style="27" min="3842" max="3842"/>
+    <col width="9.125" customWidth="1" style="27" min="3843" max="4085"/>
+    <col width="7" customWidth="1" style="27" min="4086" max="4086"/>
+    <col width="14.75" customWidth="1" style="27" min="4087" max="4087"/>
+    <col width="13.375" customWidth="1" style="27" min="4088" max="4088"/>
+    <col width="9.875" customWidth="1" style="27" min="4089" max="4092"/>
+    <col width="10.75" customWidth="1" style="27" min="4093" max="4093"/>
+    <col width="9.875" customWidth="1" style="27" min="4094" max="4095"/>
+    <col width="14.875" customWidth="1" style="27" min="4096" max="4096"/>
+    <col width="23.875" customWidth="1" style="27" min="4097" max="4097"/>
+    <col width="13.25" customWidth="1" style="27" min="4098" max="4098"/>
+    <col width="9.125" customWidth="1" style="27" min="4099" max="4341"/>
+    <col width="7" customWidth="1" style="27" min="4342" max="4342"/>
+    <col width="14.75" customWidth="1" style="27" min="4343" max="4343"/>
+    <col width="13.375" customWidth="1" style="27" min="4344" max="4344"/>
+    <col width="9.875" customWidth="1" style="27" min="4345" max="4348"/>
+    <col width="10.75" customWidth="1" style="27" min="4349" max="4349"/>
+    <col width="9.875" customWidth="1" style="27" min="4350" max="4351"/>
+    <col width="14.875" customWidth="1" style="27" min="4352" max="4352"/>
+    <col width="23.875" customWidth="1" style="27" min="4353" max="4353"/>
+    <col width="13.25" customWidth="1" style="27" min="4354" max="4354"/>
+    <col width="9.125" customWidth="1" style="27" min="4355" max="4597"/>
+    <col width="7" customWidth="1" style="27" min="4598" max="4598"/>
+    <col width="14.75" customWidth="1" style="27" min="4599" max="4599"/>
+    <col width="13.375" customWidth="1" style="27" min="4600" max="4600"/>
+    <col width="9.875" customWidth="1" style="27" min="4601" max="4604"/>
+    <col width="10.75" customWidth="1" style="27" min="4605" max="4605"/>
+    <col width="9.875" customWidth="1" style="27" min="4606" max="4607"/>
+    <col width="14.875" customWidth="1" style="27" min="4608" max="4608"/>
+    <col width="23.875" customWidth="1" style="27" min="4609" max="4609"/>
+    <col width="13.25" customWidth="1" style="27" min="4610" max="4610"/>
+    <col width="9.125" customWidth="1" style="27" min="4611" max="4853"/>
+    <col width="7" customWidth="1" style="27" min="4854" max="4854"/>
+    <col width="14.75" customWidth="1" style="27" min="4855" max="4855"/>
+    <col width="13.375" customWidth="1" style="27" min="4856" max="4856"/>
+    <col width="9.875" customWidth="1" style="27" min="4857" max="4860"/>
+    <col width="10.75" customWidth="1" style="27" min="4861" max="4861"/>
+    <col width="9.875" customWidth="1" style="27" min="4862" max="4863"/>
+    <col width="14.875" customWidth="1" style="27" min="4864" max="4864"/>
+    <col width="23.875" customWidth="1" style="27" min="4865" max="4865"/>
+    <col width="13.25" customWidth="1" style="27" min="4866" max="4866"/>
+    <col width="9.125" customWidth="1" style="27" min="4867" max="5109"/>
+    <col width="7" customWidth="1" style="27" min="5110" max="5110"/>
+    <col width="14.75" customWidth="1" style="27" min="5111" max="5111"/>
+    <col width="13.375" customWidth="1" style="27" min="5112" max="5112"/>
+    <col width="9.875" customWidth="1" style="27" min="5113" max="5116"/>
+    <col width="10.75" customWidth="1" style="27" min="5117" max="5117"/>
+    <col width="9.875" customWidth="1" style="27" min="5118" max="5119"/>
+    <col width="14.875" customWidth="1" style="27" min="5120" max="5120"/>
+    <col width="23.875" customWidth="1" style="27" min="5121" max="5121"/>
+    <col width="13.25" customWidth="1" style="27" min="5122" max="5122"/>
+    <col width="9.125" customWidth="1" style="27" min="5123" max="5365"/>
+    <col width="7" customWidth="1" style="27" min="5366" max="5366"/>
+    <col width="14.75" customWidth="1" style="27" min="5367" max="5367"/>
+    <col width="13.375" customWidth="1" style="27" min="5368" max="5368"/>
+    <col width="9.875" customWidth="1" style="27" min="5369" max="5372"/>
+    <col width="10.75" customWidth="1" style="27" min="5373" max="5373"/>
+    <col width="9.875" customWidth="1" style="27" min="5374" max="5375"/>
+    <col width="14.875" customWidth="1" style="27" min="5376" max="5376"/>
+    <col width="23.875" customWidth="1" style="27" min="5377" max="5377"/>
+    <col width="13.25" customWidth="1" style="27" min="5378" max="5378"/>
+    <col width="9.125" customWidth="1" style="27" min="5379" max="5621"/>
+    <col width="7" customWidth="1" style="27" min="5622" max="5622"/>
+    <col width="14.75" customWidth="1" style="27" min="5623" max="5623"/>
+    <col width="13.375" customWidth="1" style="27" min="5624" max="5624"/>
+    <col width="9.875" customWidth="1" style="27" min="5625" max="5628"/>
+    <col width="10.75" customWidth="1" style="27" min="5629" max="5629"/>
+    <col width="9.875" customWidth="1" style="27" min="5630" max="5631"/>
+    <col width="14.875" customWidth="1" style="27" min="5632" max="5632"/>
+    <col width="23.875" customWidth="1" style="27" min="5633" max="5633"/>
+    <col width="13.25" customWidth="1" style="27" min="5634" max="5634"/>
+    <col width="9.125" customWidth="1" style="27" min="5635" max="5877"/>
+    <col width="7" customWidth="1" style="27" min="5878" max="5878"/>
+    <col width="14.75" customWidth="1" style="27" min="5879" max="5879"/>
+    <col width="13.375" customWidth="1" style="27" min="5880" max="5880"/>
+    <col width="9.875" customWidth="1" style="27" min="5881" max="5884"/>
+    <col width="10.75" customWidth="1" style="27" min="5885" max="5885"/>
+    <col width="9.875" customWidth="1" style="27" min="5886" max="5887"/>
+    <col width="14.875" customWidth="1" style="27" min="5888" max="5888"/>
+    <col width="23.875" customWidth="1" style="27" min="5889" max="5889"/>
+    <col width="13.25" customWidth="1" style="27" min="5890" max="5890"/>
+    <col width="9.125" customWidth="1" style="27" min="5891" max="6133"/>
+    <col width="7" customWidth="1" style="27" min="6134" max="6134"/>
+    <col width="14.75" customWidth="1" style="27" min="6135" max="6135"/>
+    <col width="13.375" customWidth="1" style="27" min="6136" max="6136"/>
+    <col width="9.875" customWidth="1" style="27" min="6137" max="6140"/>
+    <col width="10.75" customWidth="1" style="27" min="6141" max="6141"/>
+    <col width="9.875" customWidth="1" style="27" min="6142" max="6143"/>
+    <col width="14.875" customWidth="1" style="27" min="6144" max="6144"/>
+    <col width="23.875" customWidth="1" style="27" min="6145" max="6145"/>
+    <col width="13.25" customWidth="1" style="27" min="6146" max="6146"/>
+    <col width="9.125" customWidth="1" style="27" min="6147" max="6389"/>
+    <col width="7" customWidth="1" style="27" min="6390" max="6390"/>
+    <col width="14.75" customWidth="1" style="27" min="6391" max="6391"/>
+    <col width="13.375" customWidth="1" style="27" min="6392" max="6392"/>
+    <col width="9.875" customWidth="1" style="27" min="6393" max="6396"/>
+    <col width="10.75" customWidth="1" style="27" min="6397" max="6397"/>
+    <col width="9.875" customWidth="1" style="27" min="6398" max="6399"/>
+    <col width="14.875" customWidth="1" style="27" min="6400" max="6400"/>
+    <col width="23.875" customWidth="1" style="27" min="6401" max="6401"/>
+    <col width="13.25" customWidth="1" style="27" min="6402" max="6402"/>
+    <col width="9.125" customWidth="1" style="27" min="6403" max="6645"/>
+    <col width="7" customWidth="1" style="27" min="6646" max="6646"/>
+    <col width="14.75" customWidth="1" style="27" min="6647" max="6647"/>
+    <col width="13.375" customWidth="1" style="27" min="6648" max="6648"/>
+    <col width="9.875" customWidth="1" style="27" min="6649" max="6652"/>
+    <col width="10.75" customWidth="1" style="27" min="6653" max="6653"/>
+    <col width="9.875" customWidth="1" style="27" min="6654" max="6655"/>
+    <col width="14.875" customWidth="1" style="27" min="6656" max="6656"/>
+    <col width="23.875" customWidth="1" style="27" min="6657" max="6657"/>
+    <col width="13.25" customWidth="1" style="27" min="6658" max="6658"/>
+    <col width="9.125" customWidth="1" style="27" min="6659" max="6901"/>
+    <col width="7" customWidth="1" style="27" min="6902" max="6902"/>
+    <col width="14.75" customWidth="1" style="27" min="6903" max="6903"/>
+    <col width="13.375" customWidth="1" style="27" min="6904" max="6904"/>
+    <col width="9.875" customWidth="1" style="27" min="6905" max="6908"/>
+    <col width="10.75" customWidth="1" style="27" min="6909" max="6909"/>
+    <col width="9.875" customWidth="1" style="27" min="6910" max="6911"/>
+    <col width="14.875" customWidth="1" style="27" min="6912" max="6912"/>
+    <col width="23.875" customWidth="1" style="27" min="6913" max="6913"/>
+    <col width="13.25" customWidth="1" style="27" min="6914" max="6914"/>
+    <col width="9.125" customWidth="1" style="27" min="6915" max="7157"/>
+    <col width="7" customWidth="1" style="27" min="7158" max="7158"/>
+    <col width="14.75" customWidth="1" style="27" min="7159" max="7159"/>
+    <col width="13.375" customWidth="1" style="27" min="7160" max="7160"/>
+    <col width="9.875" customWidth="1" style="27" min="7161" max="7164"/>
+    <col width="10.75" customWidth="1" style="27" min="7165" max="7165"/>
+    <col width="9.875" customWidth="1" style="27" min="7166" max="7167"/>
+    <col width="14.875" customWidth="1" style="27" min="7168" max="7168"/>
+    <col width="23.875" customWidth="1" style="27" min="7169" max="7169"/>
+    <col width="13.25" customWidth="1" style="27" min="7170" max="7170"/>
+    <col width="9.125" customWidth="1" style="27" min="7171" max="7413"/>
+    <col width="7" customWidth="1" style="27" min="7414" max="7414"/>
+    <col width="14.75" customWidth="1" style="27" min="7415" max="7415"/>
+    <col width="13.375" customWidth="1" style="27" min="7416" max="7416"/>
+    <col width="9.875" customWidth="1" style="27" min="7417" max="7420"/>
+    <col width="10.75" customWidth="1" style="27" min="7421" max="7421"/>
+    <col width="9.875" customWidth="1" style="27" min="7422" max="7423"/>
+    <col width="14.875" customWidth="1" style="27" min="7424" max="7424"/>
+    <col width="23.875" customWidth="1" style="27" min="7425" max="7425"/>
+    <col width="13.25" customWidth="1" style="27" min="7426" max="7426"/>
+    <col width="9.125" customWidth="1" style="27" min="7427" max="7669"/>
+    <col width="7" customWidth="1" style="27" min="7670" max="7670"/>
+    <col width="14.75" customWidth="1" style="27" min="7671" max="7671"/>
+    <col width="13.375" customWidth="1" style="27" min="7672" max="7672"/>
+    <col width="9.875" customWidth="1" style="27" min="7673" max="7676"/>
+    <col width="10.75" customWidth="1" style="27" min="7677" max="7677"/>
+    <col width="9.875" customWidth="1" style="27" min="7678" max="7679"/>
+    <col width="14.875" customWidth="1" style="27" min="7680" max="7680"/>
+    <col width="23.875" customWidth="1" style="27" min="7681" max="7681"/>
+    <col width="13.25" customWidth="1" style="27" min="7682" max="7682"/>
+    <col width="9.125" customWidth="1" style="27" min="7683" max="7925"/>
+    <col width="7" customWidth="1" style="27" min="7926" max="7926"/>
+    <col width="14.75" customWidth="1" style="27" min="7927" max="7927"/>
+    <col width="13.375" customWidth="1" style="27" min="7928" max="7928"/>
+    <col width="9.875" customWidth="1" style="27" min="7929" max="7932"/>
+    <col width="10.75" customWidth="1" style="27" min="7933" max="7933"/>
+    <col width="9.875" customWidth="1" style="27" min="7934" max="7935"/>
+    <col width="14.875" customWidth="1" style="27" min="7936" max="7936"/>
+    <col width="23.875" customWidth="1" style="27" min="7937" max="7937"/>
+    <col width="13.25" customWidth="1" style="27" min="7938" max="7938"/>
+    <col width="9.125" customWidth="1" style="27" min="7939" max="8181"/>
+    <col width="7" customWidth="1" style="27" min="8182" max="8182"/>
+    <col width="14.75" customWidth="1" style="27" min="8183" max="8183"/>
+    <col width="13.375" customWidth="1" style="27" min="8184" max="8184"/>
+    <col width="9.875" customWidth="1" style="27" min="8185" max="8188"/>
+    <col width="10.75" customWidth="1" style="27" min="8189" max="8189"/>
+    <col width="9.875" customWidth="1" style="27" min="8190" max="8191"/>
+    <col width="14.875" customWidth="1" style="27" min="8192" max="8192"/>
+    <col width="23.875" customWidth="1" style="27" min="8193" max="8193"/>
+    <col width="13.25" customWidth="1" style="27" min="8194" max="8194"/>
+    <col width="9.125" customWidth="1" style="27" min="8195" max="8437"/>
+    <col width="7" customWidth="1" style="27" min="8438" max="8438"/>
+    <col width="14.75" customWidth="1" style="27" min="8439" max="8439"/>
+    <col width="13.375" customWidth="1" style="27" min="8440" max="8440"/>
+    <col width="9.875" customWidth="1" style="27" min="8441" max="8444"/>
+    <col width="10.75" customWidth="1" style="27" min="8445" max="8445"/>
+    <col width="9.875" customWidth="1" style="27" min="8446" max="8447"/>
+    <col width="14.875" customWidth="1" style="27" min="8448" max="8448"/>
+    <col width="23.875" customWidth="1" style="27" min="8449" max="8449"/>
+    <col width="13.25" customWidth="1" style="27" min="8450" max="8450"/>
+    <col width="9.125" customWidth="1" style="27" min="8451" max="8693"/>
+    <col width="7" customWidth="1" style="27" min="8694" max="8694"/>
+    <col width="14.75" customWidth="1" style="27" min="8695" max="8695"/>
+    <col width="13.375" customWidth="1" style="27" min="8696" max="8696"/>
+    <col width="9.875" customWidth="1" style="27" min="8697" max="8700"/>
+    <col width="10.75" customWidth="1" style="27" min="8701" max="8701"/>
+    <col width="9.875" customWidth="1" style="27" min="8702" max="8703"/>
+    <col width="14.875" customWidth="1" style="27" min="8704" max="8704"/>
+    <col width="23.875" customWidth="1" style="27" min="8705" max="8705"/>
+    <col width="13.25" customWidth="1" style="27" min="8706" max="8706"/>
+    <col width="9.125" customWidth="1" style="27" min="8707" max="8949"/>
+    <col width="7" customWidth="1" style="27" min="8950" max="8950"/>
+    <col width="14.75" customWidth="1" style="27" min="8951" max="8951"/>
+    <col width="13.375" customWidth="1" style="27" min="8952" max="8952"/>
+    <col width="9.875" customWidth="1" style="27" min="8953" max="8956"/>
+    <col width="10.75" customWidth="1" style="27" min="8957" max="8957"/>
+    <col width="9.875" customWidth="1" style="27" min="8958" max="8959"/>
+    <col width="14.875" customWidth="1" style="27" min="8960" max="8960"/>
+    <col width="23.875" customWidth="1" style="27" min="8961" max="8961"/>
+    <col width="13.25" customWidth="1" style="27" min="8962" max="8962"/>
+    <col width="9.125" customWidth="1" style="27" min="8963" max="9205"/>
+    <col width="7" customWidth="1" style="27" min="9206" max="9206"/>
+    <col width="14.75" customWidth="1" style="27" min="9207" max="9207"/>
+    <col width="13.375" customWidth="1" style="27" min="9208" max="9208"/>
+    <col width="9.875" customWidth="1" style="27" min="9209" max="9212"/>
+    <col width="10.75" customWidth="1" style="27" min="9213" max="9213"/>
+    <col width="9.875" customWidth="1" style="27" min="9214" max="9215"/>
+    <col width="14.875" customWidth="1" style="27" min="9216" max="9216"/>
+    <col width="23.875" customWidth="1" style="27" min="9217" max="9217"/>
+    <col width="13.25" customWidth="1" style="27" min="9218" max="9218"/>
+    <col width="9.125" customWidth="1" style="27" min="9219" max="9461"/>
+    <col width="7" customWidth="1" style="27" min="9462" max="9462"/>
+    <col width="14.75" customWidth="1" style="27" min="9463" max="9463"/>
+    <col width="13.375" customWidth="1" style="27" min="9464" max="9464"/>
+    <col width="9.875" customWidth="1" style="27" min="9465" max="9468"/>
+    <col width="10.75" customWidth="1" style="27" min="9469" max="9469"/>
+    <col width="9.875" customWidth="1" style="27" min="9470" max="9471"/>
+    <col width="14.875" customWidth="1" style="27" min="9472" max="9472"/>
+    <col width="23.875" customWidth="1" style="27" min="9473" max="9473"/>
+    <col width="13.25" customWidth="1" style="27" min="9474" max="9474"/>
+    <col width="9.125" customWidth="1" style="27" min="9475" max="9717"/>
+    <col width="7" customWidth="1" style="27" min="9718" max="9718"/>
+    <col width="14.75" customWidth="1" style="27" min="9719" max="9719"/>
+    <col width="13.375" customWidth="1" style="27" min="9720" max="9720"/>
+    <col width="9.875" customWidth="1" style="27" min="9721" max="9724"/>
+    <col width="10.75" customWidth="1" style="27" min="9725" max="9725"/>
+    <col width="9.875" customWidth="1" style="27" min="9726" max="9727"/>
+    <col width="14.875" customWidth="1" style="27" min="9728" max="9728"/>
+    <col width="23.875" customWidth="1" style="27" min="9729" max="9729"/>
+    <col width="13.25" customWidth="1" style="27" min="9730" max="9730"/>
+    <col width="9.125" customWidth="1" style="27" min="9731" max="9973"/>
+    <col width="7" customWidth="1" style="27" min="9974" max="9974"/>
+    <col width="14.75" customWidth="1" style="27" min="9975" max="9975"/>
+    <col width="13.375" customWidth="1" style="27" min="9976" max="9976"/>
+    <col width="9.875" customWidth="1" style="27" min="9977" max="9980"/>
+    <col width="10.75" customWidth="1" style="27" min="9981" max="9981"/>
+    <col width="9.875" customWidth="1" style="27" min="9982" max="9983"/>
+    <col width="14.875" customWidth="1" style="27" min="9984" max="9984"/>
+    <col width="23.875" customWidth="1" style="27" min="9985" max="9985"/>
+    <col width="13.25" customWidth="1" style="27" min="9986" max="9986"/>
+    <col width="9.125" customWidth="1" style="27" min="9987" max="10229"/>
+    <col width="7" customWidth="1" style="27" min="10230" max="10230"/>
+    <col width="14.75" customWidth="1" style="27" min="10231" max="10231"/>
+    <col width="13.375" customWidth="1" style="27" min="10232" max="10232"/>
+    <col width="9.875" customWidth="1" style="27" min="10233" max="10236"/>
+    <col width="10.75" customWidth="1" style="27" min="10237" max="10237"/>
+    <col width="9.875" customWidth="1" style="27" min="10238" max="10239"/>
+    <col width="14.875" customWidth="1" style="27" min="10240" max="10240"/>
+    <col width="23.875" customWidth="1" style="27" min="10241" max="10241"/>
+    <col width="13.25" customWidth="1" style="27" min="10242" max="10242"/>
+    <col width="9.125" customWidth="1" style="27" min="10243" max="10485"/>
+    <col width="7" customWidth="1" style="27" min="10486" max="10486"/>
+    <col width="14.75" customWidth="1" style="27" min="10487" max="10487"/>
+    <col width="13.375" customWidth="1" style="27" min="10488" max="10488"/>
+    <col width="9.875" customWidth="1" style="27" min="10489" max="10492"/>
+    <col width="10.75" customWidth="1" style="27" min="10493" max="10493"/>
+    <col width="9.875" customWidth="1" style="27" min="10494" max="10495"/>
+    <col width="14.875" customWidth="1" style="27" min="10496" max="10496"/>
+    <col width="23.875" customWidth="1" style="27" min="10497" max="10497"/>
+    <col width="13.25" customWidth="1" style="27" min="10498" max="10498"/>
+    <col width="9.125" customWidth="1" style="27" min="10499" max="10741"/>
+    <col width="7" customWidth="1" style="27" min="10742" max="10742"/>
+    <col width="14.75" customWidth="1" style="27" min="10743" max="10743"/>
+    <col width="13.375" customWidth="1" style="27" min="10744" max="10744"/>
+    <col width="9.875" customWidth="1" style="27" min="10745" max="10748"/>
+    <col width="10.75" customWidth="1" style="27" min="10749" max="10749"/>
+    <col width="9.875" customWidth="1" style="27" min="10750" max="10751"/>
+    <col width="14.875" customWidth="1" style="27" min="10752" max="10752"/>
+    <col width="23.875" customWidth="1" style="27" min="10753" max="10753"/>
+    <col width="13.25" customWidth="1" style="27" min="10754" max="10754"/>
+    <col width="9.125" customWidth="1" style="27" min="10755" max="10997"/>
+    <col width="7" customWidth="1" style="27" min="10998" max="10998"/>
+    <col width="14.75" customWidth="1" style="27" min="10999" max="10999"/>
+    <col width="13.375" customWidth="1" style="27" min="11000" max="11000"/>
+    <col width="9.875" customWidth="1" style="27" min="11001" max="11004"/>
+    <col width="10.75" customWidth="1" style="27" min="11005" max="11005"/>
+    <col width="9.875" customWidth="1" style="27" min="11006" max="11007"/>
+    <col width="14.875" customWidth="1" style="27" min="11008" max="11008"/>
+    <col width="23.875" customWidth="1" style="27" min="11009" max="11009"/>
+    <col width="13.25" customWidth="1" style="27" min="11010" max="11010"/>
+    <col width="9.125" customWidth="1" style="27" min="11011" max="11253"/>
+    <col width="7" customWidth="1" style="27" min="11254" max="11254"/>
+    <col width="14.75" customWidth="1" style="27" min="11255" max="11255"/>
+    <col width="13.375" customWidth="1" style="27" min="11256" max="11256"/>
+    <col width="9.875" customWidth="1" style="27" min="11257" max="11260"/>
+    <col width="10.75" customWidth="1" style="27" min="11261" max="11261"/>
+    <col width="9.875" customWidth="1" style="27" min="11262" max="11263"/>
+    <col width="14.875" customWidth="1" style="27" min="11264" max="11264"/>
+    <col width="23.875" customWidth="1" style="27" min="11265" max="11265"/>
+    <col width="13.25" customWidth="1" style="27" min="11266" max="11266"/>
+    <col width="9.125" customWidth="1" style="27" min="11267" max="11509"/>
+    <col width="7" customWidth="1" style="27" min="11510" max="11510"/>
+    <col width="14.75" customWidth="1" style="27" min="11511" max="11511"/>
+    <col width="13.375" customWidth="1" style="27" min="11512" max="11512"/>
+    <col width="9.875" customWidth="1" style="27" min="11513" max="11516"/>
+    <col width="10.75" customWidth="1" style="27" min="11517" max="11517"/>
+    <col width="9.875" customWidth="1" style="27" min="11518" max="11519"/>
+    <col width="14.875" customWidth="1" style="27" min="11520" max="11520"/>
+    <col width="23.875" customWidth="1" style="27" min="11521" max="11521"/>
+    <col width="13.25" customWidth="1" style="27" min="11522" max="11522"/>
+    <col width="9.125" customWidth="1" style="27" min="11523" max="11765"/>
+    <col width="7" customWidth="1" style="27" min="11766" max="11766"/>
+    <col width="14.75" customWidth="1" style="27" min="11767" max="11767"/>
+    <col width="13.375" customWidth="1" style="27" min="11768" max="11768"/>
+    <col width="9.875" customWidth="1" style="27" min="11769" max="11772"/>
+    <col width="10.75" customWidth="1" style="27" min="11773" max="11773"/>
+    <col width="9.875" customWidth="1" style="27" min="11774" max="11775"/>
+    <col width="14.875" customWidth="1" style="27" min="11776" max="11776"/>
+    <col width="23.875" customWidth="1" style="27" min="11777" max="11777"/>
+    <col width="13.25" customWidth="1" style="27" min="11778" max="11778"/>
+    <col width="9.125" customWidth="1" style="27" min="11779" max="12021"/>
+    <col width="7" customWidth="1" style="27" min="12022" max="12022"/>
+    <col width="14.75" customWidth="1" style="27" min="12023" max="12023"/>
+    <col width="13.375" customWidth="1" style="27" min="12024" max="12024"/>
+    <col width="9.875" customWidth="1" style="27" min="12025" max="12028"/>
+    <col width="10.75" customWidth="1" style="27" min="12029" max="12029"/>
+    <col width="9.875" customWidth="1" style="27" min="12030" max="12031"/>
+    <col width="14.875" customWidth="1" style="27" min="12032" max="12032"/>
+    <col width="23.875" customWidth="1" style="27" min="12033" max="12033"/>
+    <col width="13.25" customWidth="1" style="27" min="12034" max="12034"/>
+    <col width="9.125" customWidth="1" style="27" min="12035" max="12277"/>
+    <col width="7" customWidth="1" style="27" min="12278" max="12278"/>
+    <col width="14.75" customWidth="1" style="27" min="12279" max="12279"/>
+    <col width="13.375" customWidth="1" style="27" min="12280" max="12280"/>
+    <col width="9.875" customWidth="1" style="27" min="12281" max="12284"/>
+    <col width="10.75" customWidth="1" style="27" min="12285" max="12285"/>
+    <col width="9.875" customWidth="1" style="27" min="12286" max="12287"/>
+    <col width="14.875" customWidth="1" style="27" min="12288" max="12288"/>
+    <col width="23.875" customWidth="1" style="27" min="12289" max="12289"/>
+    <col width="13.25" customWidth="1" style="27" min="12290" max="12290"/>
+    <col width="9.125" customWidth="1" style="27" min="12291" max="12533"/>
+    <col width="7" customWidth="1" style="27" min="12534" max="12534"/>
+    <col width="14.75" customWidth="1" style="27" min="12535" max="12535"/>
+    <col width="13.375" customWidth="1" style="27" min="12536" max="12536"/>
+    <col width="9.875" customWidth="1" style="27" min="12537" max="12540"/>
+    <col width="10.75" customWidth="1" style="27" min="12541" max="12541"/>
+    <col width="9.875" customWidth="1" style="27" min="12542" max="12543"/>
+    <col width="14.875" customWidth="1" style="27" min="12544" max="12544"/>
+    <col width="23.875" customWidth="1" style="27" min="12545" max="12545"/>
+    <col width="13.25" customWidth="1" style="27" min="12546" max="12546"/>
+    <col width="9.125" customWidth="1" style="27" min="12547" max="12789"/>
+    <col width="7" customWidth="1" style="27" min="12790" max="12790"/>
+    <col width="14.75" customWidth="1" style="27" min="12791" max="12791"/>
+    <col width="13.375" customWidth="1" style="27" min="12792" max="12792"/>
+    <col width="9.875" customWidth="1" style="27" min="12793" max="12796"/>
+    <col width="10.75" customWidth="1" style="27" min="12797" max="12797"/>
+    <col width="9.875" customWidth="1" style="27" min="12798" max="12799"/>
+    <col width="14.875" customWidth="1" style="27" min="12800" max="12800"/>
+    <col width="23.875" customWidth="1" style="27" min="12801" max="12801"/>
+    <col width="13.25" customWidth="1" style="27" min="12802" max="12802"/>
+    <col width="9.125" customWidth="1" style="27" min="12803" max="13045"/>
+    <col width="7" customWidth="1" style="27" min="13046" max="13046"/>
+    <col width="14.75" customWidth="1" style="27" min="13047" max="13047"/>
+    <col width="13.375" customWidth="1" style="27" min="13048" max="13048"/>
+    <col width="9.875" customWidth="1" style="27" min="13049" max="13052"/>
+    <col width="10.75" customWidth="1" style="27" min="13053" max="13053"/>
+    <col width="9.875" customWidth="1" style="27" min="13054" max="13055"/>
+    <col width="14.875" customWidth="1" style="27" min="13056" max="13056"/>
+    <col width="23.875" customWidth="1" style="27" min="13057" max="13057"/>
+    <col width="13.25" customWidth="1" style="27" min="13058" max="13058"/>
+    <col width="9.125" customWidth="1" style="27" min="13059" max="13301"/>
+    <col width="7" customWidth="1" style="27" min="13302" max="13302"/>
+    <col width="14.75" customWidth="1" style="27" min="13303" max="13303"/>
+    <col width="13.375" customWidth="1" style="27" min="13304" max="13304"/>
+    <col width="9.875" customWidth="1" style="27" min="13305" max="13308"/>
+    <col width="10.75" customWidth="1" style="27" min="13309" max="13309"/>
+    <col width="9.875" customWidth="1" style="27" min="13310" max="13311"/>
+    <col width="14.875" customWidth="1" style="27" min="13312" max="13312"/>
+    <col width="23.875" customWidth="1" style="27" min="13313" max="13313"/>
+    <col width="13.25" customWidth="1" style="27" min="13314" max="13314"/>
+    <col width="9.125" customWidth="1" style="27" min="13315" max="13557"/>
+    <col width="7" customWidth="1" style="27" min="13558" max="13558"/>
+    <col width="14.75" customWidth="1" style="27" min="13559" max="13559"/>
+    <col width="13.375" customWidth="1" style="27" min="13560" max="13560"/>
+    <col width="9.875" customWidth="1" style="27" min="13561" max="13564"/>
+    <col width="10.75" customWidth="1" style="27" min="13565" max="13565"/>
+    <col width="9.875" customWidth="1" style="27" min="13566" max="13567"/>
+    <col width="14.875" customWidth="1" style="27" min="13568" max="13568"/>
+    <col width="23.875" customWidth="1" style="27" min="13569" max="13569"/>
+    <col width="13.25" customWidth="1" style="27" min="13570" max="13570"/>
+    <col width="9.125" customWidth="1" style="27" min="13571" max="13813"/>
+    <col width="7" customWidth="1" style="27" min="13814" max="13814"/>
+    <col width="14.75" customWidth="1" style="27" min="13815" max="13815"/>
+    <col width="13.375" customWidth="1" style="27" min="13816" max="13816"/>
+    <col width="9.875" customWidth="1" style="27" min="13817" max="13820"/>
+    <col width="10.75" customWidth="1" style="27" min="13821" max="13821"/>
+    <col width="9.875" customWidth="1" style="27" min="13822" max="13823"/>
+    <col width="14.875" customWidth="1" style="27" min="13824" max="13824"/>
+    <col width="23.875" customWidth="1" style="27" min="13825" max="13825"/>
+    <col width="13.25" customWidth="1" style="27" min="13826" max="13826"/>
+    <col width="9.125" customWidth="1" style="27" min="13827" max="14069"/>
+    <col width="7" customWidth="1" style="27" min="14070" max="14070"/>
+    <col width="14.75" customWidth="1" style="27" min="14071" max="14071"/>
+    <col width="13.375" customWidth="1" style="27" min="14072" max="14072"/>
+    <col width="9.875" customWidth="1" style="27" min="14073" max="14076"/>
+    <col width="10.75" customWidth="1" style="27" min="14077" max="14077"/>
+    <col width="9.875" customWidth="1" style="27" min="14078" max="14079"/>
+    <col width="14.875" customWidth="1" style="27" min="14080" max="14080"/>
+    <col width="23.875" customWidth="1" style="27" min="14081" max="14081"/>
+    <col width="13.25" customWidth="1" style="27" min="14082" max="14082"/>
+    <col width="9.125" customWidth="1" style="27" min="14083" max="14325"/>
+    <col width="7" customWidth="1" style="27" min="14326" max="14326"/>
+    <col width="14.75" customWidth="1" style="27" min="14327" max="14327"/>
+    <col width="13.375" customWidth="1" style="27" min="14328" max="14328"/>
+    <col width="9.875" customWidth="1" style="27" min="14329" max="14332"/>
+    <col width="10.75" customWidth="1" style="27" min="14333" max="14333"/>
+    <col width="9.875" customWidth="1" style="27" min="14334" max="14335"/>
+    <col width="14.875" customWidth="1" style="27" min="14336" max="14336"/>
+    <col width="23.875" customWidth="1" style="27" min="14337" max="14337"/>
+    <col width="13.25" customWidth="1" style="27" min="14338" max="14338"/>
+    <col width="9.125" customWidth="1" style="27" min="14339" max="14581"/>
+    <col width="7" customWidth="1" style="27" min="14582" max="14582"/>
+    <col width="14.75" customWidth="1" style="27" min="14583" max="14583"/>
+    <col width="13.375" customWidth="1" style="27" min="14584" max="14584"/>
+    <col width="9.875" customWidth="1" style="27" min="14585" max="14588"/>
+    <col width="10.75" customWidth="1" style="27" min="14589" max="14589"/>
+    <col width="9.875" customWidth="1" style="27" min="14590" max="14591"/>
+    <col width="14.875" customWidth="1" style="27" min="14592" max="14592"/>
+    <col width="23.875" customWidth="1" style="27" min="14593" max="14593"/>
+    <col width="13.25" customWidth="1" style="27" min="14594" max="14594"/>
+    <col width="9.125" customWidth="1" style="27" min="14595" max="14837"/>
+    <col width="7" customWidth="1" style="27" min="14838" max="14838"/>
+    <col width="14.75" customWidth="1" style="27" min="14839" max="14839"/>
+    <col width="13.375" customWidth="1" style="27" min="14840" max="14840"/>
+    <col width="9.875" customWidth="1" style="27" min="14841" max="14844"/>
+    <col width="10.75" customWidth="1" style="27" min="14845" max="14845"/>
+    <col width="9.875" customWidth="1" style="27" min="14846" max="14847"/>
+    <col width="14.875" customWidth="1" style="27" min="14848" max="14848"/>
+    <col width="23.875" customWidth="1" style="27" min="14849" max="14849"/>
+    <col width="13.25" customWidth="1" style="27" min="14850" max="14850"/>
+    <col width="9.125" customWidth="1" style="27" min="14851" max="15093"/>
+    <col width="7" customWidth="1" style="27" min="15094" max="15094"/>
+    <col width="14.75" customWidth="1" style="27" min="15095" max="15095"/>
+    <col width="13.375" customWidth="1" style="27" min="15096" max="15096"/>
+    <col width="9.875" customWidth="1" style="27" min="15097" max="15100"/>
+    <col width="10.75" customWidth="1" style="27" min="15101" max="15101"/>
+    <col width="9.875" customWidth="1" style="27" min="15102" max="15103"/>
+    <col width="14.875" customWidth="1" style="27" min="15104" max="15104"/>
+    <col width="23.875" customWidth="1" style="27" min="15105" max="15105"/>
+    <col width="13.25" customWidth="1" style="27" min="15106" max="15106"/>
+    <col width="9.125" customWidth="1" style="27" min="15107" max="15349"/>
+    <col width="7" customWidth="1" style="27" min="15350" max="15350"/>
+    <col width="14.75" customWidth="1" style="27" min="15351" max="15351"/>
+    <col width="13.375" customWidth="1" style="27" min="15352" max="15352"/>
+    <col width="9.875" customWidth="1" style="27" min="15353" max="15356"/>
+    <col width="10.75" customWidth="1" style="27" min="15357" max="15357"/>
+    <col width="9.875" customWidth="1" style="27" min="15358" max="15359"/>
+    <col width="14.875" customWidth="1" style="27" min="15360" max="15360"/>
+    <col width="23.875" customWidth="1" style="27" min="15361" max="15361"/>
+    <col width="13.25" customWidth="1" style="27" min="15362" max="15362"/>
+    <col width="9.125" customWidth="1" style="27" min="15363" max="15605"/>
+    <col width="7" customWidth="1" style="27" min="15606" max="15606"/>
+    <col width="14.75" customWidth="1" style="27" min="15607" max="15607"/>
+    <col width="13.375" customWidth="1" style="27" min="15608" max="15608"/>
+    <col width="9.875" customWidth="1" style="27" min="15609" max="15612"/>
+    <col width="10.75" customWidth="1" style="27" min="15613" max="15613"/>
+    <col width="9.875" customWidth="1" style="27" min="15614" max="15615"/>
+    <col width="14.875" customWidth="1" style="27" min="15616" max="15616"/>
+    <col width="23.875" customWidth="1" style="27" min="15617" max="15617"/>
+    <col width="13.25" customWidth="1" style="27" min="15618" max="15618"/>
+    <col width="9.125" customWidth="1" style="27" min="15619" max="15861"/>
+    <col width="7" customWidth="1" style="27" min="15862" max="15862"/>
+    <col width="14.75" customWidth="1" style="27" min="15863" max="15863"/>
+    <col width="13.375" customWidth="1" style="27" min="15864" max="15864"/>
+    <col width="9.875" customWidth="1" style="27" min="15865" max="15868"/>
+    <col width="10.75" customWidth="1" style="27" min="15869" max="15869"/>
+    <col width="9.875" customWidth="1" style="27" min="15870" max="15871"/>
+    <col width="14.875" customWidth="1" style="27" min="15872" max="15872"/>
+    <col width="23.875" customWidth="1" style="27" min="15873" max="15873"/>
+    <col width="13.25" customWidth="1" style="27" min="15874" max="15874"/>
+    <col width="9.125" customWidth="1" style="27" min="15875" max="16117"/>
+    <col width="7" customWidth="1" style="27" min="16118" max="16118"/>
+    <col width="14.75" customWidth="1" style="27" min="16119" max="16119"/>
+    <col width="13.375" customWidth="1" style="27" min="16120" max="16120"/>
+    <col width="9.875" customWidth="1" style="27" min="16121" max="16124"/>
+    <col width="10.75" customWidth="1" style="27" min="16125" max="16125"/>
+    <col width="9.875" customWidth="1" style="27" min="16126" max="16127"/>
+    <col width="14.875" customWidth="1" style="27" min="16128" max="16128"/>
+    <col width="23.875" customWidth="1" style="27" min="16129" max="16129"/>
+    <col width="13.25" customWidth="1" style="27" min="16130" max="16130"/>
+    <col width="9.125" customWidth="1" style="27" min="16131" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>ใบตรวจสอบเครื่อง CNC</t>
+        </is>
+      </c>
+      <c r="AA1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="AA2" s="43" t="inlineStr">
+        <is>
+          <t>Machine No. : 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="41">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="16" t="n"/>
+      <c r="W3" s="16" t="n"/>
+      <c r="X3" s="16" t="n"/>
+      <c r="Y3" s="16" t="n"/>
+      <c r="Z3" s="16" t="n"/>
+      <c r="AA3" s="16" t="n"/>
+      <c r="AB3" s="16" t="n"/>
+      <c r="AC3" s="16" t="n"/>
+      <c r="AD3" s="16" t="n"/>
+      <c r="AE3" s="16" t="n"/>
+      <c r="AF3" s="16" t="n"/>
+      <c r="AG3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="18" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>การตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ประจำเดือน  ………………………………..</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+      <c r="K4" s="36" t="n"/>
+      <c r="L4" s="36" t="n"/>
+      <c r="M4" s="36" t="n"/>
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="36" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="36" t="n"/>
+      <c r="S4" s="36" t="n"/>
+      <c r="T4" s="36" t="n"/>
+      <c r="U4" s="36" t="n"/>
+      <c r="V4" s="36" t="n"/>
+      <c r="W4" s="36" t="n"/>
+      <c r="X4" s="36" t="n"/>
+      <c r="Y4" s="36" t="n"/>
+      <c r="Z4" s="36" t="n"/>
+      <c r="AA4" s="36" t="n"/>
+      <c r="AB4" s="36" t="n"/>
+      <c r="AC4" s="36" t="n"/>
+      <c r="AD4" s="36" t="n"/>
+      <c r="AE4" s="36" t="n"/>
+      <c r="AF4" s="36" t="n"/>
+      <c r="AG4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Worm up เครื่องจักร 15 นาที ทุกครั้งที่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="22" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="22" t="n"/>
+      <c r="AA6" s="23" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="22" t="n"/>
+      <c r="AD6" s="22" t="n"/>
+      <c r="AE6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>เช็คระดับนำมันที่ Pump Hydraulic ทุกวัน เติมเมื่อพร่อง</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="23" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>ทำความสะอาด Air filter Mesh ทุกวัน</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="22" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="23" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจเช็คแรงดัน Air Control Unit ปกติเฉลี่ยที่ 0.5 Mpa</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+      <c r="U9" s="22" t="n"/>
+      <c r="V9" s="22" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="22" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="22" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="22" t="n"/>
+      <c r="AC9" s="22" t="n"/>
+      <c r="AD9" s="22" t="n"/>
+      <c r="AE9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>เช็คน้ำมันชุด Gear ของ ATC ทุกวัน(เปลี่ยนถ่ายทุกปี)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="23" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>อัดจารบี Ballscrew และ Linear Guideทุก 1ครั้งต่อเดือน</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="23" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบการเคลื่อนที่ของแกนทุกแกน (X,Y,Z)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="23" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสภาพของน้ำ Coolant ถ่ายรูปค่าที่วัดได้ส่งเข้าระบบ</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="22" t="n"/>
+      <c r="U13" s="22" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Coolant pump</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Unclamp และการเปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="22" t="n"/>
+      <c r="U15" s="22" t="n"/>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="22" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Spindle</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="22" t="n"/>
+      <c r="U16" s="22" t="n"/>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="22" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="22" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+      <c r="AE16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Arm เปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="n"/>
+      <c r="U17" s="22" t="n"/>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="22" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบระดับของน้ำ Coolant เติมเมื่ออยู่ระดับที่ต่ำ</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="22" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ความสะอาดทั่วไปของเครื่องจักรโดยรวม</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="23" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบความพร้อมสภาพโดยรวม(ฟังด้วยหู ดูด้วยตา)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="23" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสายไฮโดรลิกส์ และสายลม</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="22" t="n"/>
+      <c r="AA21" s="23" t="n"/>
+      <c r="AB21" s="22" t="n"/>
+      <c r="AC21" s="22" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n"/>
+      <c r="R22" s="28" t="n"/>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="33" t="n"/>
+      <c r="Y22" s="33" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="33" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="28" t="n"/>
+      <c r="AE22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AF22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AG22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="29" t="n"/>
+      <c r="N23" s="29" t="n"/>
+      <c r="O23" s="29" t="n"/>
+      <c r="P23" s="29" t="n"/>
+      <c r="Q23" s="29" t="n"/>
+      <c r="R23" s="29" t="n"/>
+      <c r="S23" s="29" t="n"/>
+      <c r="T23" s="29" t="n"/>
+      <c r="U23" s="29" t="n"/>
+      <c r="V23" s="29" t="n"/>
+      <c r="W23" s="29" t="n"/>
+      <c r="X23" s="29" t="n"/>
+      <c r="Y23" s="29" t="n"/>
+      <c r="Z23" s="29" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="29" t="n"/>
+      <c r="AC23" s="29" t="n"/>
+      <c r="AD23" s="29" t="n"/>
+      <c r="AE23" s="29" t="n"/>
+      <c r="AF23" s="29" t="n"/>
+      <c r="AG23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
+      <c r="M24" s="30" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="30" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="30" t="n"/>
+      <c r="U24" s="30" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="30" t="n"/>
+      <c r="X24" s="44" t="n"/>
+      <c r="Y24" s="44" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="44" t="n"/>
+      <c r="AB24" s="30" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="30" t="n"/>
+      <c r="AF24" s="30" t="n"/>
+      <c r="AG24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="29" t="n"/>
+      <c r="N25" s="29" t="n"/>
+      <c r="O25" s="29" t="n"/>
+      <c r="P25" s="29" t="n"/>
+      <c r="Q25" s="29" t="n"/>
+      <c r="R25" s="29" t="n"/>
+      <c r="S25" s="29" t="n"/>
+      <c r="T25" s="29" t="n"/>
+      <c r="U25" s="29" t="n"/>
+      <c r="V25" s="29" t="n"/>
+      <c r="W25" s="29" t="n"/>
+      <c r="X25" s="29" t="n"/>
+      <c r="Y25" s="29" t="n"/>
+      <c r="Z25" s="29" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="29" t="n"/>
+      <c r="AC25" s="29" t="n"/>
+      <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
+      <c r="AG25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>บันทึกเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="Y27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="173.25" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="AA29" s="19" t="n"/>
+      <c r="AB29" s="31" t="n"/>
+      <c r="AC29" s="32" t="n"/>
+      <c r="AD29" s="32" t="n"/>
+      <c r="AE29" s="32" t="n"/>
+      <c r="AF29" s="32" t="n"/>
+      <c r="AG29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="29.25" customHeight="1">
+      <c r="AB30" s="26" t="inlineStr">
+        <is>
+          <t>ผู้จัดการแผนกซ่อมบำรุง</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1">
+      <c r="D31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="C32" s="18" t="n"/>
+      <c r="AG32" s="20" t="inlineStr">
+        <is>
+          <t>FM-MN-07 Rev.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="71">
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="77" blackAndWhite="1" horizontalDpi="4294967293" verticalDpi="4294967293"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -581,4 +581,2338 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>33618</colOff>
+      <row>0</row>
+      <rowOff>11206</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>672353</colOff>
+      <row>2</row>
+      <rowOff>19163</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Picture 11" descr="LOGO PES.png"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="33618" y="11206"/>
+          <a:ext cx="963706" cy="657898"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>1</col>
+      <colOff>2206621</colOff>
+      <row>21</row>
+      <rowOff>42333</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>4413250</colOff>
+      <row>25</row>
+      <rowOff>31749</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill rotWithShape="1">
+        <a:blip r:embed="rId2"/>
+        <a:srcRect r="8552"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="2571746" y="4836583"/>
+          <a:ext cx="2206629" cy="1132416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+  <a:themeElements>
+    <a:clrScheme name="Office 2007 - 2010">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office 2007 - 2010">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office 2007 - 2010">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <cols>
+    <col width="4.875" customWidth="1" style="27" min="1" max="1"/>
+    <col width="58.5" customWidth="1" style="27" min="2" max="2"/>
+    <col width="3.375" customWidth="1" style="27" min="3" max="33"/>
+    <col width="9.125" customWidth="1" style="27" min="34" max="245"/>
+    <col width="7" customWidth="1" style="27" min="246" max="246"/>
+    <col width="14.75" customWidth="1" style="27" min="247" max="247"/>
+    <col width="13.375" customWidth="1" style="27" min="248" max="248"/>
+    <col width="9.875" customWidth="1" style="27" min="249" max="252"/>
+    <col width="10.75" customWidth="1" style="27" min="253" max="253"/>
+    <col width="9.875" customWidth="1" style="27" min="254" max="255"/>
+    <col width="14.875" customWidth="1" style="27" min="256" max="256"/>
+    <col width="23.875" customWidth="1" style="27" min="257" max="257"/>
+    <col width="13.25" customWidth="1" style="27" min="258" max="258"/>
+    <col width="9.125" customWidth="1" style="27" min="259" max="501"/>
+    <col width="7" customWidth="1" style="27" min="502" max="502"/>
+    <col width="14.75" customWidth="1" style="27" min="503" max="503"/>
+    <col width="13.375" customWidth="1" style="27" min="504" max="504"/>
+    <col width="9.875" customWidth="1" style="27" min="505" max="508"/>
+    <col width="10.75" customWidth="1" style="27" min="509" max="509"/>
+    <col width="9.875" customWidth="1" style="27" min="510" max="511"/>
+    <col width="14.875" customWidth="1" style="27" min="512" max="512"/>
+    <col width="23.875" customWidth="1" style="27" min="513" max="513"/>
+    <col width="13.25" customWidth="1" style="27" min="514" max="514"/>
+    <col width="9.125" customWidth="1" style="27" min="515" max="757"/>
+    <col width="7" customWidth="1" style="27" min="758" max="758"/>
+    <col width="14.75" customWidth="1" style="27" min="759" max="759"/>
+    <col width="13.375" customWidth="1" style="27" min="760" max="760"/>
+    <col width="9.875" customWidth="1" style="27" min="761" max="764"/>
+    <col width="10.75" customWidth="1" style="27" min="765" max="765"/>
+    <col width="9.875" customWidth="1" style="27" min="766" max="767"/>
+    <col width="14.875" customWidth="1" style="27" min="768" max="768"/>
+    <col width="23.875" customWidth="1" style="27" min="769" max="769"/>
+    <col width="13.25" customWidth="1" style="27" min="770" max="770"/>
+    <col width="9.125" customWidth="1" style="27" min="771" max="1013"/>
+    <col width="7" customWidth="1" style="27" min="1014" max="1014"/>
+    <col width="14.75" customWidth="1" style="27" min="1015" max="1015"/>
+    <col width="13.375" customWidth="1" style="27" min="1016" max="1016"/>
+    <col width="9.875" customWidth="1" style="27" min="1017" max="1020"/>
+    <col width="10.75" customWidth="1" style="27" min="1021" max="1021"/>
+    <col width="9.875" customWidth="1" style="27" min="1022" max="1023"/>
+    <col width="14.875" customWidth="1" style="27" min="1024" max="1024"/>
+    <col width="23.875" customWidth="1" style="27" min="1025" max="1025"/>
+    <col width="13.25" customWidth="1" style="27" min="1026" max="1026"/>
+    <col width="9.125" customWidth="1" style="27" min="1027" max="1269"/>
+    <col width="7" customWidth="1" style="27" min="1270" max="1270"/>
+    <col width="14.75" customWidth="1" style="27" min="1271" max="1271"/>
+    <col width="13.375" customWidth="1" style="27" min="1272" max="1272"/>
+    <col width="9.875" customWidth="1" style="27" min="1273" max="1276"/>
+    <col width="10.75" customWidth="1" style="27" min="1277" max="1277"/>
+    <col width="9.875" customWidth="1" style="27" min="1278" max="1279"/>
+    <col width="14.875" customWidth="1" style="27" min="1280" max="1280"/>
+    <col width="23.875" customWidth="1" style="27" min="1281" max="1281"/>
+    <col width="13.25" customWidth="1" style="27" min="1282" max="1282"/>
+    <col width="9.125" customWidth="1" style="27" min="1283" max="1525"/>
+    <col width="7" customWidth="1" style="27" min="1526" max="1526"/>
+    <col width="14.75" customWidth="1" style="27" min="1527" max="1527"/>
+    <col width="13.375" customWidth="1" style="27" min="1528" max="1528"/>
+    <col width="9.875" customWidth="1" style="27" min="1529" max="1532"/>
+    <col width="10.75" customWidth="1" style="27" min="1533" max="1533"/>
+    <col width="9.875" customWidth="1" style="27" min="1534" max="1535"/>
+    <col width="14.875" customWidth="1" style="27" min="1536" max="1536"/>
+    <col width="23.875" customWidth="1" style="27" min="1537" max="1537"/>
+    <col width="13.25" customWidth="1" style="27" min="1538" max="1538"/>
+    <col width="9.125" customWidth="1" style="27" min="1539" max="1781"/>
+    <col width="7" customWidth="1" style="27" min="1782" max="1782"/>
+    <col width="14.75" customWidth="1" style="27" min="1783" max="1783"/>
+    <col width="13.375" customWidth="1" style="27" min="1784" max="1784"/>
+    <col width="9.875" customWidth="1" style="27" min="1785" max="1788"/>
+    <col width="10.75" customWidth="1" style="27" min="1789" max="1789"/>
+    <col width="9.875" customWidth="1" style="27" min="1790" max="1791"/>
+    <col width="14.875" customWidth="1" style="27" min="1792" max="1792"/>
+    <col width="23.875" customWidth="1" style="27" min="1793" max="1793"/>
+    <col width="13.25" customWidth="1" style="27" min="1794" max="1794"/>
+    <col width="9.125" customWidth="1" style="27" min="1795" max="2037"/>
+    <col width="7" customWidth="1" style="27" min="2038" max="2038"/>
+    <col width="14.75" customWidth="1" style="27" min="2039" max="2039"/>
+    <col width="13.375" customWidth="1" style="27" min="2040" max="2040"/>
+    <col width="9.875" customWidth="1" style="27" min="2041" max="2044"/>
+    <col width="10.75" customWidth="1" style="27" min="2045" max="2045"/>
+    <col width="9.875" customWidth="1" style="27" min="2046" max="2047"/>
+    <col width="14.875" customWidth="1" style="27" min="2048" max="2048"/>
+    <col width="23.875" customWidth="1" style="27" min="2049" max="2049"/>
+    <col width="13.25" customWidth="1" style="27" min="2050" max="2050"/>
+    <col width="9.125" customWidth="1" style="27" min="2051" max="2293"/>
+    <col width="7" customWidth="1" style="27" min="2294" max="2294"/>
+    <col width="14.75" customWidth="1" style="27" min="2295" max="2295"/>
+    <col width="13.375" customWidth="1" style="27" min="2296" max="2296"/>
+    <col width="9.875" customWidth="1" style="27" min="2297" max="2300"/>
+    <col width="10.75" customWidth="1" style="27" min="2301" max="2301"/>
+    <col width="9.875" customWidth="1" style="27" min="2302" max="2303"/>
+    <col width="14.875" customWidth="1" style="27" min="2304" max="2304"/>
+    <col width="23.875" customWidth="1" style="27" min="2305" max="2305"/>
+    <col width="13.25" customWidth="1" style="27" min="2306" max="2306"/>
+    <col width="9.125" customWidth="1" style="27" min="2307" max="2549"/>
+    <col width="7" customWidth="1" style="27" min="2550" max="2550"/>
+    <col width="14.75" customWidth="1" style="27" min="2551" max="2551"/>
+    <col width="13.375" customWidth="1" style="27" min="2552" max="2552"/>
+    <col width="9.875" customWidth="1" style="27" min="2553" max="2556"/>
+    <col width="10.75" customWidth="1" style="27" min="2557" max="2557"/>
+    <col width="9.875" customWidth="1" style="27" min="2558" max="2559"/>
+    <col width="14.875" customWidth="1" style="27" min="2560" max="2560"/>
+    <col width="23.875" customWidth="1" style="27" min="2561" max="2561"/>
+    <col width="13.25" customWidth="1" style="27" min="2562" max="2562"/>
+    <col width="9.125" customWidth="1" style="27" min="2563" max="2805"/>
+    <col width="7" customWidth="1" style="27" min="2806" max="2806"/>
+    <col width="14.75" customWidth="1" style="27" min="2807" max="2807"/>
+    <col width="13.375" customWidth="1" style="27" min="2808" max="2808"/>
+    <col width="9.875" customWidth="1" style="27" min="2809" max="2812"/>
+    <col width="10.75" customWidth="1" style="27" min="2813" max="2813"/>
+    <col width="9.875" customWidth="1" style="27" min="2814" max="2815"/>
+    <col width="14.875" customWidth="1" style="27" min="2816" max="2816"/>
+    <col width="23.875" customWidth="1" style="27" min="2817" max="2817"/>
+    <col width="13.25" customWidth="1" style="27" min="2818" max="2818"/>
+    <col width="9.125" customWidth="1" style="27" min="2819" max="3061"/>
+    <col width="7" customWidth="1" style="27" min="3062" max="3062"/>
+    <col width="14.75" customWidth="1" style="27" min="3063" max="3063"/>
+    <col width="13.375" customWidth="1" style="27" min="3064" max="3064"/>
+    <col width="9.875" customWidth="1" style="27" min="3065" max="3068"/>
+    <col width="10.75" customWidth="1" style="27" min="3069" max="3069"/>
+    <col width="9.875" customWidth="1" style="27" min="3070" max="3071"/>
+    <col width="14.875" customWidth="1" style="27" min="3072" max="3072"/>
+    <col width="23.875" customWidth="1" style="27" min="3073" max="3073"/>
+    <col width="13.25" customWidth="1" style="27" min="3074" max="3074"/>
+    <col width="9.125" customWidth="1" style="27" min="3075" max="3317"/>
+    <col width="7" customWidth="1" style="27" min="3318" max="3318"/>
+    <col width="14.75" customWidth="1" style="27" min="3319" max="3319"/>
+    <col width="13.375" customWidth="1" style="27" min="3320" max="3320"/>
+    <col width="9.875" customWidth="1" style="27" min="3321" max="3324"/>
+    <col width="10.75" customWidth="1" style="27" min="3325" max="3325"/>
+    <col width="9.875" customWidth="1" style="27" min="3326" max="3327"/>
+    <col width="14.875" customWidth="1" style="27" min="3328" max="3328"/>
+    <col width="23.875" customWidth="1" style="27" min="3329" max="3329"/>
+    <col width="13.25" customWidth="1" style="27" min="3330" max="3330"/>
+    <col width="9.125" customWidth="1" style="27" min="3331" max="3573"/>
+    <col width="7" customWidth="1" style="27" min="3574" max="3574"/>
+    <col width="14.75" customWidth="1" style="27" min="3575" max="3575"/>
+    <col width="13.375" customWidth="1" style="27" min="3576" max="3576"/>
+    <col width="9.875" customWidth="1" style="27" min="3577" max="3580"/>
+    <col width="10.75" customWidth="1" style="27" min="3581" max="3581"/>
+    <col width="9.875" customWidth="1" style="27" min="3582" max="3583"/>
+    <col width="14.875" customWidth="1" style="27" min="3584" max="3584"/>
+    <col width="23.875" customWidth="1" style="27" min="3585" max="3585"/>
+    <col width="13.25" customWidth="1" style="27" min="3586" max="3586"/>
+    <col width="9.125" customWidth="1" style="27" min="3587" max="3829"/>
+    <col width="7" customWidth="1" style="27" min="3830" max="3830"/>
+    <col width="14.75" customWidth="1" style="27" min="3831" max="3831"/>
+    <col width="13.375" customWidth="1" style="27" min="3832" max="3832"/>
+    <col width="9.875" customWidth="1" style="27" min="3833" max="3836"/>
+    <col width="10.75" customWidth="1" style="27" min="3837" max="3837"/>
+    <col width="9.875" customWidth="1" style="27" min="3838" max="3839"/>
+    <col width="14.875" customWidth="1" style="27" min="3840" max="3840"/>
+    <col width="23.875" customWidth="1" style="27" min="3841" max="3841"/>
+    <col width="13.25" customWidth="1" style="27" min="3842" max="3842"/>
+    <col width="9.125" customWidth="1" style="27" min="3843" max="4085"/>
+    <col width="7" customWidth="1" style="27" min="4086" max="4086"/>
+    <col width="14.75" customWidth="1" style="27" min="4087" max="4087"/>
+    <col width="13.375" customWidth="1" style="27" min="4088" max="4088"/>
+    <col width="9.875" customWidth="1" style="27" min="4089" max="4092"/>
+    <col width="10.75" customWidth="1" style="27" min="4093" max="4093"/>
+    <col width="9.875" customWidth="1" style="27" min="4094" max="4095"/>
+    <col width="14.875" customWidth="1" style="27" min="4096" max="4096"/>
+    <col width="23.875" customWidth="1" style="27" min="4097" max="4097"/>
+    <col width="13.25" customWidth="1" style="27" min="4098" max="4098"/>
+    <col width="9.125" customWidth="1" style="27" min="4099" max="4341"/>
+    <col width="7" customWidth="1" style="27" min="4342" max="4342"/>
+    <col width="14.75" customWidth="1" style="27" min="4343" max="4343"/>
+    <col width="13.375" customWidth="1" style="27" min="4344" max="4344"/>
+    <col width="9.875" customWidth="1" style="27" min="4345" max="4348"/>
+    <col width="10.75" customWidth="1" style="27" min="4349" max="4349"/>
+    <col width="9.875" customWidth="1" style="27" min="4350" max="4351"/>
+    <col width="14.875" customWidth="1" style="27" min="4352" max="4352"/>
+    <col width="23.875" customWidth="1" style="27" min="4353" max="4353"/>
+    <col width="13.25" customWidth="1" style="27" min="4354" max="4354"/>
+    <col width="9.125" customWidth="1" style="27" min="4355" max="4597"/>
+    <col width="7" customWidth="1" style="27" min="4598" max="4598"/>
+    <col width="14.75" customWidth="1" style="27" min="4599" max="4599"/>
+    <col width="13.375" customWidth="1" style="27" min="4600" max="4600"/>
+    <col width="9.875" customWidth="1" style="27" min="4601" max="4604"/>
+    <col width="10.75" customWidth="1" style="27" min="4605" max="4605"/>
+    <col width="9.875" customWidth="1" style="27" min="4606" max="4607"/>
+    <col width="14.875" customWidth="1" style="27" min="4608" max="4608"/>
+    <col width="23.875" customWidth="1" style="27" min="4609" max="4609"/>
+    <col width="13.25" customWidth="1" style="27" min="4610" max="4610"/>
+    <col width="9.125" customWidth="1" style="27" min="4611" max="4853"/>
+    <col width="7" customWidth="1" style="27" min="4854" max="4854"/>
+    <col width="14.75" customWidth="1" style="27" min="4855" max="4855"/>
+    <col width="13.375" customWidth="1" style="27" min="4856" max="4856"/>
+    <col width="9.875" customWidth="1" style="27" min="4857" max="4860"/>
+    <col width="10.75" customWidth="1" style="27" min="4861" max="4861"/>
+    <col width="9.875" customWidth="1" style="27" min="4862" max="4863"/>
+    <col width="14.875" customWidth="1" style="27" min="4864" max="4864"/>
+    <col width="23.875" customWidth="1" style="27" min="4865" max="4865"/>
+    <col width="13.25" customWidth="1" style="27" min="4866" max="4866"/>
+    <col width="9.125" customWidth="1" style="27" min="4867" max="5109"/>
+    <col width="7" customWidth="1" style="27" min="5110" max="5110"/>
+    <col width="14.75" customWidth="1" style="27" min="5111" max="5111"/>
+    <col width="13.375" customWidth="1" style="27" min="5112" max="5112"/>
+    <col width="9.875" customWidth="1" style="27" min="5113" max="5116"/>
+    <col width="10.75" customWidth="1" style="27" min="5117" max="5117"/>
+    <col width="9.875" customWidth="1" style="27" min="5118" max="5119"/>
+    <col width="14.875" customWidth="1" style="27" min="5120" max="5120"/>
+    <col width="23.875" customWidth="1" style="27" min="5121" max="5121"/>
+    <col width="13.25" customWidth="1" style="27" min="5122" max="5122"/>
+    <col width="9.125" customWidth="1" style="27" min="5123" max="5365"/>
+    <col width="7" customWidth="1" style="27" min="5366" max="5366"/>
+    <col width="14.75" customWidth="1" style="27" min="5367" max="5367"/>
+    <col width="13.375" customWidth="1" style="27" min="5368" max="5368"/>
+    <col width="9.875" customWidth="1" style="27" min="5369" max="5372"/>
+    <col width="10.75" customWidth="1" style="27" min="5373" max="5373"/>
+    <col width="9.875" customWidth="1" style="27" min="5374" max="5375"/>
+    <col width="14.875" customWidth="1" style="27" min="5376" max="5376"/>
+    <col width="23.875" customWidth="1" style="27" min="5377" max="5377"/>
+    <col width="13.25" customWidth="1" style="27" min="5378" max="5378"/>
+    <col width="9.125" customWidth="1" style="27" min="5379" max="5621"/>
+    <col width="7" customWidth="1" style="27" min="5622" max="5622"/>
+    <col width="14.75" customWidth="1" style="27" min="5623" max="5623"/>
+    <col width="13.375" customWidth="1" style="27" min="5624" max="5624"/>
+    <col width="9.875" customWidth="1" style="27" min="5625" max="5628"/>
+    <col width="10.75" customWidth="1" style="27" min="5629" max="5629"/>
+    <col width="9.875" customWidth="1" style="27" min="5630" max="5631"/>
+    <col width="14.875" customWidth="1" style="27" min="5632" max="5632"/>
+    <col width="23.875" customWidth="1" style="27" min="5633" max="5633"/>
+    <col width="13.25" customWidth="1" style="27" min="5634" max="5634"/>
+    <col width="9.125" customWidth="1" style="27" min="5635" max="5877"/>
+    <col width="7" customWidth="1" style="27" min="5878" max="5878"/>
+    <col width="14.75" customWidth="1" style="27" min="5879" max="5879"/>
+    <col width="13.375" customWidth="1" style="27" min="5880" max="5880"/>
+    <col width="9.875" customWidth="1" style="27" min="5881" max="5884"/>
+    <col width="10.75" customWidth="1" style="27" min="5885" max="5885"/>
+    <col width="9.875" customWidth="1" style="27" min="5886" max="5887"/>
+    <col width="14.875" customWidth="1" style="27" min="5888" max="5888"/>
+    <col width="23.875" customWidth="1" style="27" min="5889" max="5889"/>
+    <col width="13.25" customWidth="1" style="27" min="5890" max="5890"/>
+    <col width="9.125" customWidth="1" style="27" min="5891" max="6133"/>
+    <col width="7" customWidth="1" style="27" min="6134" max="6134"/>
+    <col width="14.75" customWidth="1" style="27" min="6135" max="6135"/>
+    <col width="13.375" customWidth="1" style="27" min="6136" max="6136"/>
+    <col width="9.875" customWidth="1" style="27" min="6137" max="6140"/>
+    <col width="10.75" customWidth="1" style="27" min="6141" max="6141"/>
+    <col width="9.875" customWidth="1" style="27" min="6142" max="6143"/>
+    <col width="14.875" customWidth="1" style="27" min="6144" max="6144"/>
+    <col width="23.875" customWidth="1" style="27" min="6145" max="6145"/>
+    <col width="13.25" customWidth="1" style="27" min="6146" max="6146"/>
+    <col width="9.125" customWidth="1" style="27" min="6147" max="6389"/>
+    <col width="7" customWidth="1" style="27" min="6390" max="6390"/>
+    <col width="14.75" customWidth="1" style="27" min="6391" max="6391"/>
+    <col width="13.375" customWidth="1" style="27" min="6392" max="6392"/>
+    <col width="9.875" customWidth="1" style="27" min="6393" max="6396"/>
+    <col width="10.75" customWidth="1" style="27" min="6397" max="6397"/>
+    <col width="9.875" customWidth="1" style="27" min="6398" max="6399"/>
+    <col width="14.875" customWidth="1" style="27" min="6400" max="6400"/>
+    <col width="23.875" customWidth="1" style="27" min="6401" max="6401"/>
+    <col width="13.25" customWidth="1" style="27" min="6402" max="6402"/>
+    <col width="9.125" customWidth="1" style="27" min="6403" max="6645"/>
+    <col width="7" customWidth="1" style="27" min="6646" max="6646"/>
+    <col width="14.75" customWidth="1" style="27" min="6647" max="6647"/>
+    <col width="13.375" customWidth="1" style="27" min="6648" max="6648"/>
+    <col width="9.875" customWidth="1" style="27" min="6649" max="6652"/>
+    <col width="10.75" customWidth="1" style="27" min="6653" max="6653"/>
+    <col width="9.875" customWidth="1" style="27" min="6654" max="6655"/>
+    <col width="14.875" customWidth="1" style="27" min="6656" max="6656"/>
+    <col width="23.875" customWidth="1" style="27" min="6657" max="6657"/>
+    <col width="13.25" customWidth="1" style="27" min="6658" max="6658"/>
+    <col width="9.125" customWidth="1" style="27" min="6659" max="6901"/>
+    <col width="7" customWidth="1" style="27" min="6902" max="6902"/>
+    <col width="14.75" customWidth="1" style="27" min="6903" max="6903"/>
+    <col width="13.375" customWidth="1" style="27" min="6904" max="6904"/>
+    <col width="9.875" customWidth="1" style="27" min="6905" max="6908"/>
+    <col width="10.75" customWidth="1" style="27" min="6909" max="6909"/>
+    <col width="9.875" customWidth="1" style="27" min="6910" max="6911"/>
+    <col width="14.875" customWidth="1" style="27" min="6912" max="6912"/>
+    <col width="23.875" customWidth="1" style="27" min="6913" max="6913"/>
+    <col width="13.25" customWidth="1" style="27" min="6914" max="6914"/>
+    <col width="9.125" customWidth="1" style="27" min="6915" max="7157"/>
+    <col width="7" customWidth="1" style="27" min="7158" max="7158"/>
+    <col width="14.75" customWidth="1" style="27" min="7159" max="7159"/>
+    <col width="13.375" customWidth="1" style="27" min="7160" max="7160"/>
+    <col width="9.875" customWidth="1" style="27" min="7161" max="7164"/>
+    <col width="10.75" customWidth="1" style="27" min="7165" max="7165"/>
+    <col width="9.875" customWidth="1" style="27" min="7166" max="7167"/>
+    <col width="14.875" customWidth="1" style="27" min="7168" max="7168"/>
+    <col width="23.875" customWidth="1" style="27" min="7169" max="7169"/>
+    <col width="13.25" customWidth="1" style="27" min="7170" max="7170"/>
+    <col width="9.125" customWidth="1" style="27" min="7171" max="7413"/>
+    <col width="7" customWidth="1" style="27" min="7414" max="7414"/>
+    <col width="14.75" customWidth="1" style="27" min="7415" max="7415"/>
+    <col width="13.375" customWidth="1" style="27" min="7416" max="7416"/>
+    <col width="9.875" customWidth="1" style="27" min="7417" max="7420"/>
+    <col width="10.75" customWidth="1" style="27" min="7421" max="7421"/>
+    <col width="9.875" customWidth="1" style="27" min="7422" max="7423"/>
+    <col width="14.875" customWidth="1" style="27" min="7424" max="7424"/>
+    <col width="23.875" customWidth="1" style="27" min="7425" max="7425"/>
+    <col width="13.25" customWidth="1" style="27" min="7426" max="7426"/>
+    <col width="9.125" customWidth="1" style="27" min="7427" max="7669"/>
+    <col width="7" customWidth="1" style="27" min="7670" max="7670"/>
+    <col width="14.75" customWidth="1" style="27" min="7671" max="7671"/>
+    <col width="13.375" customWidth="1" style="27" min="7672" max="7672"/>
+    <col width="9.875" customWidth="1" style="27" min="7673" max="7676"/>
+    <col width="10.75" customWidth="1" style="27" min="7677" max="7677"/>
+    <col width="9.875" customWidth="1" style="27" min="7678" max="7679"/>
+    <col width="14.875" customWidth="1" style="27" min="7680" max="7680"/>
+    <col width="23.875" customWidth="1" style="27" min="7681" max="7681"/>
+    <col width="13.25" customWidth="1" style="27" min="7682" max="7682"/>
+    <col width="9.125" customWidth="1" style="27" min="7683" max="7925"/>
+    <col width="7" customWidth="1" style="27" min="7926" max="7926"/>
+    <col width="14.75" customWidth="1" style="27" min="7927" max="7927"/>
+    <col width="13.375" customWidth="1" style="27" min="7928" max="7928"/>
+    <col width="9.875" customWidth="1" style="27" min="7929" max="7932"/>
+    <col width="10.75" customWidth="1" style="27" min="7933" max="7933"/>
+    <col width="9.875" customWidth="1" style="27" min="7934" max="7935"/>
+    <col width="14.875" customWidth="1" style="27" min="7936" max="7936"/>
+    <col width="23.875" customWidth="1" style="27" min="7937" max="7937"/>
+    <col width="13.25" customWidth="1" style="27" min="7938" max="7938"/>
+    <col width="9.125" customWidth="1" style="27" min="7939" max="8181"/>
+    <col width="7" customWidth="1" style="27" min="8182" max="8182"/>
+    <col width="14.75" customWidth="1" style="27" min="8183" max="8183"/>
+    <col width="13.375" customWidth="1" style="27" min="8184" max="8184"/>
+    <col width="9.875" customWidth="1" style="27" min="8185" max="8188"/>
+    <col width="10.75" customWidth="1" style="27" min="8189" max="8189"/>
+    <col width="9.875" customWidth="1" style="27" min="8190" max="8191"/>
+    <col width="14.875" customWidth="1" style="27" min="8192" max="8192"/>
+    <col width="23.875" customWidth="1" style="27" min="8193" max="8193"/>
+    <col width="13.25" customWidth="1" style="27" min="8194" max="8194"/>
+    <col width="9.125" customWidth="1" style="27" min="8195" max="8437"/>
+    <col width="7" customWidth="1" style="27" min="8438" max="8438"/>
+    <col width="14.75" customWidth="1" style="27" min="8439" max="8439"/>
+    <col width="13.375" customWidth="1" style="27" min="8440" max="8440"/>
+    <col width="9.875" customWidth="1" style="27" min="8441" max="8444"/>
+    <col width="10.75" customWidth="1" style="27" min="8445" max="8445"/>
+    <col width="9.875" customWidth="1" style="27" min="8446" max="8447"/>
+    <col width="14.875" customWidth="1" style="27" min="8448" max="8448"/>
+    <col width="23.875" customWidth="1" style="27" min="8449" max="8449"/>
+    <col width="13.25" customWidth="1" style="27" min="8450" max="8450"/>
+    <col width="9.125" customWidth="1" style="27" min="8451" max="8693"/>
+    <col width="7" customWidth="1" style="27" min="8694" max="8694"/>
+    <col width="14.75" customWidth="1" style="27" min="8695" max="8695"/>
+    <col width="13.375" customWidth="1" style="27" min="8696" max="8696"/>
+    <col width="9.875" customWidth="1" style="27" min="8697" max="8700"/>
+    <col width="10.75" customWidth="1" style="27" min="8701" max="8701"/>
+    <col width="9.875" customWidth="1" style="27" min="8702" max="8703"/>
+    <col width="14.875" customWidth="1" style="27" min="8704" max="8704"/>
+    <col width="23.875" customWidth="1" style="27" min="8705" max="8705"/>
+    <col width="13.25" customWidth="1" style="27" min="8706" max="8706"/>
+    <col width="9.125" customWidth="1" style="27" min="8707" max="8949"/>
+    <col width="7" customWidth="1" style="27" min="8950" max="8950"/>
+    <col width="14.75" customWidth="1" style="27" min="8951" max="8951"/>
+    <col width="13.375" customWidth="1" style="27" min="8952" max="8952"/>
+    <col width="9.875" customWidth="1" style="27" min="8953" max="8956"/>
+    <col width="10.75" customWidth="1" style="27" min="8957" max="8957"/>
+    <col width="9.875" customWidth="1" style="27" min="8958" max="8959"/>
+    <col width="14.875" customWidth="1" style="27" min="8960" max="8960"/>
+    <col width="23.875" customWidth="1" style="27" min="8961" max="8961"/>
+    <col width="13.25" customWidth="1" style="27" min="8962" max="8962"/>
+    <col width="9.125" customWidth="1" style="27" min="8963" max="9205"/>
+    <col width="7" customWidth="1" style="27" min="9206" max="9206"/>
+    <col width="14.75" customWidth="1" style="27" min="9207" max="9207"/>
+    <col width="13.375" customWidth="1" style="27" min="9208" max="9208"/>
+    <col width="9.875" customWidth="1" style="27" min="9209" max="9212"/>
+    <col width="10.75" customWidth="1" style="27" min="9213" max="9213"/>
+    <col width="9.875" customWidth="1" style="27" min="9214" max="9215"/>
+    <col width="14.875" customWidth="1" style="27" min="9216" max="9216"/>
+    <col width="23.875" customWidth="1" style="27" min="9217" max="9217"/>
+    <col width="13.25" customWidth="1" style="27" min="9218" max="9218"/>
+    <col width="9.125" customWidth="1" style="27" min="9219" max="9461"/>
+    <col width="7" customWidth="1" style="27" min="9462" max="9462"/>
+    <col width="14.75" customWidth="1" style="27" min="9463" max="9463"/>
+    <col width="13.375" customWidth="1" style="27" min="9464" max="9464"/>
+    <col width="9.875" customWidth="1" style="27" min="9465" max="9468"/>
+    <col width="10.75" customWidth="1" style="27" min="9469" max="9469"/>
+    <col width="9.875" customWidth="1" style="27" min="9470" max="9471"/>
+    <col width="14.875" customWidth="1" style="27" min="9472" max="9472"/>
+    <col width="23.875" customWidth="1" style="27" min="9473" max="9473"/>
+    <col width="13.25" customWidth="1" style="27" min="9474" max="9474"/>
+    <col width="9.125" customWidth="1" style="27" min="9475" max="9717"/>
+    <col width="7" customWidth="1" style="27" min="9718" max="9718"/>
+    <col width="14.75" customWidth="1" style="27" min="9719" max="9719"/>
+    <col width="13.375" customWidth="1" style="27" min="9720" max="9720"/>
+    <col width="9.875" customWidth="1" style="27" min="9721" max="9724"/>
+    <col width="10.75" customWidth="1" style="27" min="9725" max="9725"/>
+    <col width="9.875" customWidth="1" style="27" min="9726" max="9727"/>
+    <col width="14.875" customWidth="1" style="27" min="9728" max="9728"/>
+    <col width="23.875" customWidth="1" style="27" min="9729" max="9729"/>
+    <col width="13.25" customWidth="1" style="27" min="9730" max="9730"/>
+    <col width="9.125" customWidth="1" style="27" min="9731" max="9973"/>
+    <col width="7" customWidth="1" style="27" min="9974" max="9974"/>
+    <col width="14.75" customWidth="1" style="27" min="9975" max="9975"/>
+    <col width="13.375" customWidth="1" style="27" min="9976" max="9976"/>
+    <col width="9.875" customWidth="1" style="27" min="9977" max="9980"/>
+    <col width="10.75" customWidth="1" style="27" min="9981" max="9981"/>
+    <col width="9.875" customWidth="1" style="27" min="9982" max="9983"/>
+    <col width="14.875" customWidth="1" style="27" min="9984" max="9984"/>
+    <col width="23.875" customWidth="1" style="27" min="9985" max="9985"/>
+    <col width="13.25" customWidth="1" style="27" min="9986" max="9986"/>
+    <col width="9.125" customWidth="1" style="27" min="9987" max="10229"/>
+    <col width="7" customWidth="1" style="27" min="10230" max="10230"/>
+    <col width="14.75" customWidth="1" style="27" min="10231" max="10231"/>
+    <col width="13.375" customWidth="1" style="27" min="10232" max="10232"/>
+    <col width="9.875" customWidth="1" style="27" min="10233" max="10236"/>
+    <col width="10.75" customWidth="1" style="27" min="10237" max="10237"/>
+    <col width="9.875" customWidth="1" style="27" min="10238" max="10239"/>
+    <col width="14.875" customWidth="1" style="27" min="10240" max="10240"/>
+    <col width="23.875" customWidth="1" style="27" min="10241" max="10241"/>
+    <col width="13.25" customWidth="1" style="27" min="10242" max="10242"/>
+    <col width="9.125" customWidth="1" style="27" min="10243" max="10485"/>
+    <col width="7" customWidth="1" style="27" min="10486" max="10486"/>
+    <col width="14.75" customWidth="1" style="27" min="10487" max="10487"/>
+    <col width="13.375" customWidth="1" style="27" min="10488" max="10488"/>
+    <col width="9.875" customWidth="1" style="27" min="10489" max="10492"/>
+    <col width="10.75" customWidth="1" style="27" min="10493" max="10493"/>
+    <col width="9.875" customWidth="1" style="27" min="10494" max="10495"/>
+    <col width="14.875" customWidth="1" style="27" min="10496" max="10496"/>
+    <col width="23.875" customWidth="1" style="27" min="10497" max="10497"/>
+    <col width="13.25" customWidth="1" style="27" min="10498" max="10498"/>
+    <col width="9.125" customWidth="1" style="27" min="10499" max="10741"/>
+    <col width="7" customWidth="1" style="27" min="10742" max="10742"/>
+    <col width="14.75" customWidth="1" style="27" min="10743" max="10743"/>
+    <col width="13.375" customWidth="1" style="27" min="10744" max="10744"/>
+    <col width="9.875" customWidth="1" style="27" min="10745" max="10748"/>
+    <col width="10.75" customWidth="1" style="27" min="10749" max="10749"/>
+    <col width="9.875" customWidth="1" style="27" min="10750" max="10751"/>
+    <col width="14.875" customWidth="1" style="27" min="10752" max="10752"/>
+    <col width="23.875" customWidth="1" style="27" min="10753" max="10753"/>
+    <col width="13.25" customWidth="1" style="27" min="10754" max="10754"/>
+    <col width="9.125" customWidth="1" style="27" min="10755" max="10997"/>
+    <col width="7" customWidth="1" style="27" min="10998" max="10998"/>
+    <col width="14.75" customWidth="1" style="27" min="10999" max="10999"/>
+    <col width="13.375" customWidth="1" style="27" min="11000" max="11000"/>
+    <col width="9.875" customWidth="1" style="27" min="11001" max="11004"/>
+    <col width="10.75" customWidth="1" style="27" min="11005" max="11005"/>
+    <col width="9.875" customWidth="1" style="27" min="11006" max="11007"/>
+    <col width="14.875" customWidth="1" style="27" min="11008" max="11008"/>
+    <col width="23.875" customWidth="1" style="27" min="11009" max="11009"/>
+    <col width="13.25" customWidth="1" style="27" min="11010" max="11010"/>
+    <col width="9.125" customWidth="1" style="27" min="11011" max="11253"/>
+    <col width="7" customWidth="1" style="27" min="11254" max="11254"/>
+    <col width="14.75" customWidth="1" style="27" min="11255" max="11255"/>
+    <col width="13.375" customWidth="1" style="27" min="11256" max="11256"/>
+    <col width="9.875" customWidth="1" style="27" min="11257" max="11260"/>
+    <col width="10.75" customWidth="1" style="27" min="11261" max="11261"/>
+    <col width="9.875" customWidth="1" style="27" min="11262" max="11263"/>
+    <col width="14.875" customWidth="1" style="27" min="11264" max="11264"/>
+    <col width="23.875" customWidth="1" style="27" min="11265" max="11265"/>
+    <col width="13.25" customWidth="1" style="27" min="11266" max="11266"/>
+    <col width="9.125" customWidth="1" style="27" min="11267" max="11509"/>
+    <col width="7" customWidth="1" style="27" min="11510" max="11510"/>
+    <col width="14.75" customWidth="1" style="27" min="11511" max="11511"/>
+    <col width="13.375" customWidth="1" style="27" min="11512" max="11512"/>
+    <col width="9.875" customWidth="1" style="27" min="11513" max="11516"/>
+    <col width="10.75" customWidth="1" style="27" min="11517" max="11517"/>
+    <col width="9.875" customWidth="1" style="27" min="11518" max="11519"/>
+    <col width="14.875" customWidth="1" style="27" min="11520" max="11520"/>
+    <col width="23.875" customWidth="1" style="27" min="11521" max="11521"/>
+    <col width="13.25" customWidth="1" style="27" min="11522" max="11522"/>
+    <col width="9.125" customWidth="1" style="27" min="11523" max="11765"/>
+    <col width="7" customWidth="1" style="27" min="11766" max="11766"/>
+    <col width="14.75" customWidth="1" style="27" min="11767" max="11767"/>
+    <col width="13.375" customWidth="1" style="27" min="11768" max="11768"/>
+    <col width="9.875" customWidth="1" style="27" min="11769" max="11772"/>
+    <col width="10.75" customWidth="1" style="27" min="11773" max="11773"/>
+    <col width="9.875" customWidth="1" style="27" min="11774" max="11775"/>
+    <col width="14.875" customWidth="1" style="27" min="11776" max="11776"/>
+    <col width="23.875" customWidth="1" style="27" min="11777" max="11777"/>
+    <col width="13.25" customWidth="1" style="27" min="11778" max="11778"/>
+    <col width="9.125" customWidth="1" style="27" min="11779" max="12021"/>
+    <col width="7" customWidth="1" style="27" min="12022" max="12022"/>
+    <col width="14.75" customWidth="1" style="27" min="12023" max="12023"/>
+    <col width="13.375" customWidth="1" style="27" min="12024" max="12024"/>
+    <col width="9.875" customWidth="1" style="27" min="12025" max="12028"/>
+    <col width="10.75" customWidth="1" style="27" min="12029" max="12029"/>
+    <col width="9.875" customWidth="1" style="27" min="12030" max="12031"/>
+    <col width="14.875" customWidth="1" style="27" min="12032" max="12032"/>
+    <col width="23.875" customWidth="1" style="27" min="12033" max="12033"/>
+    <col width="13.25" customWidth="1" style="27" min="12034" max="12034"/>
+    <col width="9.125" customWidth="1" style="27" min="12035" max="12277"/>
+    <col width="7" customWidth="1" style="27" min="12278" max="12278"/>
+    <col width="14.75" customWidth="1" style="27" min="12279" max="12279"/>
+    <col width="13.375" customWidth="1" style="27" min="12280" max="12280"/>
+    <col width="9.875" customWidth="1" style="27" min="12281" max="12284"/>
+    <col width="10.75" customWidth="1" style="27" min="12285" max="12285"/>
+    <col width="9.875" customWidth="1" style="27" min="12286" max="12287"/>
+    <col width="14.875" customWidth="1" style="27" min="12288" max="12288"/>
+    <col width="23.875" customWidth="1" style="27" min="12289" max="12289"/>
+    <col width="13.25" customWidth="1" style="27" min="12290" max="12290"/>
+    <col width="9.125" customWidth="1" style="27" min="12291" max="12533"/>
+    <col width="7" customWidth="1" style="27" min="12534" max="12534"/>
+    <col width="14.75" customWidth="1" style="27" min="12535" max="12535"/>
+    <col width="13.375" customWidth="1" style="27" min="12536" max="12536"/>
+    <col width="9.875" customWidth="1" style="27" min="12537" max="12540"/>
+    <col width="10.75" customWidth="1" style="27" min="12541" max="12541"/>
+    <col width="9.875" customWidth="1" style="27" min="12542" max="12543"/>
+    <col width="14.875" customWidth="1" style="27" min="12544" max="12544"/>
+    <col width="23.875" customWidth="1" style="27" min="12545" max="12545"/>
+    <col width="13.25" customWidth="1" style="27" min="12546" max="12546"/>
+    <col width="9.125" customWidth="1" style="27" min="12547" max="12789"/>
+    <col width="7" customWidth="1" style="27" min="12790" max="12790"/>
+    <col width="14.75" customWidth="1" style="27" min="12791" max="12791"/>
+    <col width="13.375" customWidth="1" style="27" min="12792" max="12792"/>
+    <col width="9.875" customWidth="1" style="27" min="12793" max="12796"/>
+    <col width="10.75" customWidth="1" style="27" min="12797" max="12797"/>
+    <col width="9.875" customWidth="1" style="27" min="12798" max="12799"/>
+    <col width="14.875" customWidth="1" style="27" min="12800" max="12800"/>
+    <col width="23.875" customWidth="1" style="27" min="12801" max="12801"/>
+    <col width="13.25" customWidth="1" style="27" min="12802" max="12802"/>
+    <col width="9.125" customWidth="1" style="27" min="12803" max="13045"/>
+    <col width="7" customWidth="1" style="27" min="13046" max="13046"/>
+    <col width="14.75" customWidth="1" style="27" min="13047" max="13047"/>
+    <col width="13.375" customWidth="1" style="27" min="13048" max="13048"/>
+    <col width="9.875" customWidth="1" style="27" min="13049" max="13052"/>
+    <col width="10.75" customWidth="1" style="27" min="13053" max="13053"/>
+    <col width="9.875" customWidth="1" style="27" min="13054" max="13055"/>
+    <col width="14.875" customWidth="1" style="27" min="13056" max="13056"/>
+    <col width="23.875" customWidth="1" style="27" min="13057" max="13057"/>
+    <col width="13.25" customWidth="1" style="27" min="13058" max="13058"/>
+    <col width="9.125" customWidth="1" style="27" min="13059" max="13301"/>
+    <col width="7" customWidth="1" style="27" min="13302" max="13302"/>
+    <col width="14.75" customWidth="1" style="27" min="13303" max="13303"/>
+    <col width="13.375" customWidth="1" style="27" min="13304" max="13304"/>
+    <col width="9.875" customWidth="1" style="27" min="13305" max="13308"/>
+    <col width="10.75" customWidth="1" style="27" min="13309" max="13309"/>
+    <col width="9.875" customWidth="1" style="27" min="13310" max="13311"/>
+    <col width="14.875" customWidth="1" style="27" min="13312" max="13312"/>
+    <col width="23.875" customWidth="1" style="27" min="13313" max="13313"/>
+    <col width="13.25" customWidth="1" style="27" min="13314" max="13314"/>
+    <col width="9.125" customWidth="1" style="27" min="13315" max="13557"/>
+    <col width="7" customWidth="1" style="27" min="13558" max="13558"/>
+    <col width="14.75" customWidth="1" style="27" min="13559" max="13559"/>
+    <col width="13.375" customWidth="1" style="27" min="13560" max="13560"/>
+    <col width="9.875" customWidth="1" style="27" min="13561" max="13564"/>
+    <col width="10.75" customWidth="1" style="27" min="13565" max="13565"/>
+    <col width="9.875" customWidth="1" style="27" min="13566" max="13567"/>
+    <col width="14.875" customWidth="1" style="27" min="13568" max="13568"/>
+    <col width="23.875" customWidth="1" style="27" min="13569" max="13569"/>
+    <col width="13.25" customWidth="1" style="27" min="13570" max="13570"/>
+    <col width="9.125" customWidth="1" style="27" min="13571" max="13813"/>
+    <col width="7" customWidth="1" style="27" min="13814" max="13814"/>
+    <col width="14.75" customWidth="1" style="27" min="13815" max="13815"/>
+    <col width="13.375" customWidth="1" style="27" min="13816" max="13816"/>
+    <col width="9.875" customWidth="1" style="27" min="13817" max="13820"/>
+    <col width="10.75" customWidth="1" style="27" min="13821" max="13821"/>
+    <col width="9.875" customWidth="1" style="27" min="13822" max="13823"/>
+    <col width="14.875" customWidth="1" style="27" min="13824" max="13824"/>
+    <col width="23.875" customWidth="1" style="27" min="13825" max="13825"/>
+    <col width="13.25" customWidth="1" style="27" min="13826" max="13826"/>
+    <col width="9.125" customWidth="1" style="27" min="13827" max="14069"/>
+    <col width="7" customWidth="1" style="27" min="14070" max="14070"/>
+    <col width="14.75" customWidth="1" style="27" min="14071" max="14071"/>
+    <col width="13.375" customWidth="1" style="27" min="14072" max="14072"/>
+    <col width="9.875" customWidth="1" style="27" min="14073" max="14076"/>
+    <col width="10.75" customWidth="1" style="27" min="14077" max="14077"/>
+    <col width="9.875" customWidth="1" style="27" min="14078" max="14079"/>
+    <col width="14.875" customWidth="1" style="27" min="14080" max="14080"/>
+    <col width="23.875" customWidth="1" style="27" min="14081" max="14081"/>
+    <col width="13.25" customWidth="1" style="27" min="14082" max="14082"/>
+    <col width="9.125" customWidth="1" style="27" min="14083" max="14325"/>
+    <col width="7" customWidth="1" style="27" min="14326" max="14326"/>
+    <col width="14.75" customWidth="1" style="27" min="14327" max="14327"/>
+    <col width="13.375" customWidth="1" style="27" min="14328" max="14328"/>
+    <col width="9.875" customWidth="1" style="27" min="14329" max="14332"/>
+    <col width="10.75" customWidth="1" style="27" min="14333" max="14333"/>
+    <col width="9.875" customWidth="1" style="27" min="14334" max="14335"/>
+    <col width="14.875" customWidth="1" style="27" min="14336" max="14336"/>
+    <col width="23.875" customWidth="1" style="27" min="14337" max="14337"/>
+    <col width="13.25" customWidth="1" style="27" min="14338" max="14338"/>
+    <col width="9.125" customWidth="1" style="27" min="14339" max="14581"/>
+    <col width="7" customWidth="1" style="27" min="14582" max="14582"/>
+    <col width="14.75" customWidth="1" style="27" min="14583" max="14583"/>
+    <col width="13.375" customWidth="1" style="27" min="14584" max="14584"/>
+    <col width="9.875" customWidth="1" style="27" min="14585" max="14588"/>
+    <col width="10.75" customWidth="1" style="27" min="14589" max="14589"/>
+    <col width="9.875" customWidth="1" style="27" min="14590" max="14591"/>
+    <col width="14.875" customWidth="1" style="27" min="14592" max="14592"/>
+    <col width="23.875" customWidth="1" style="27" min="14593" max="14593"/>
+    <col width="13.25" customWidth="1" style="27" min="14594" max="14594"/>
+    <col width="9.125" customWidth="1" style="27" min="14595" max="14837"/>
+    <col width="7" customWidth="1" style="27" min="14838" max="14838"/>
+    <col width="14.75" customWidth="1" style="27" min="14839" max="14839"/>
+    <col width="13.375" customWidth="1" style="27" min="14840" max="14840"/>
+    <col width="9.875" customWidth="1" style="27" min="14841" max="14844"/>
+    <col width="10.75" customWidth="1" style="27" min="14845" max="14845"/>
+    <col width="9.875" customWidth="1" style="27" min="14846" max="14847"/>
+    <col width="14.875" customWidth="1" style="27" min="14848" max="14848"/>
+    <col width="23.875" customWidth="1" style="27" min="14849" max="14849"/>
+    <col width="13.25" customWidth="1" style="27" min="14850" max="14850"/>
+    <col width="9.125" customWidth="1" style="27" min="14851" max="15093"/>
+    <col width="7" customWidth="1" style="27" min="15094" max="15094"/>
+    <col width="14.75" customWidth="1" style="27" min="15095" max="15095"/>
+    <col width="13.375" customWidth="1" style="27" min="15096" max="15096"/>
+    <col width="9.875" customWidth="1" style="27" min="15097" max="15100"/>
+    <col width="10.75" customWidth="1" style="27" min="15101" max="15101"/>
+    <col width="9.875" customWidth="1" style="27" min="15102" max="15103"/>
+    <col width="14.875" customWidth="1" style="27" min="15104" max="15104"/>
+    <col width="23.875" customWidth="1" style="27" min="15105" max="15105"/>
+    <col width="13.25" customWidth="1" style="27" min="15106" max="15106"/>
+    <col width="9.125" customWidth="1" style="27" min="15107" max="15349"/>
+    <col width="7" customWidth="1" style="27" min="15350" max="15350"/>
+    <col width="14.75" customWidth="1" style="27" min="15351" max="15351"/>
+    <col width="13.375" customWidth="1" style="27" min="15352" max="15352"/>
+    <col width="9.875" customWidth="1" style="27" min="15353" max="15356"/>
+    <col width="10.75" customWidth="1" style="27" min="15357" max="15357"/>
+    <col width="9.875" customWidth="1" style="27" min="15358" max="15359"/>
+    <col width="14.875" customWidth="1" style="27" min="15360" max="15360"/>
+    <col width="23.875" customWidth="1" style="27" min="15361" max="15361"/>
+    <col width="13.25" customWidth="1" style="27" min="15362" max="15362"/>
+    <col width="9.125" customWidth="1" style="27" min="15363" max="15605"/>
+    <col width="7" customWidth="1" style="27" min="15606" max="15606"/>
+    <col width="14.75" customWidth="1" style="27" min="15607" max="15607"/>
+    <col width="13.375" customWidth="1" style="27" min="15608" max="15608"/>
+    <col width="9.875" customWidth="1" style="27" min="15609" max="15612"/>
+    <col width="10.75" customWidth="1" style="27" min="15613" max="15613"/>
+    <col width="9.875" customWidth="1" style="27" min="15614" max="15615"/>
+    <col width="14.875" customWidth="1" style="27" min="15616" max="15616"/>
+    <col width="23.875" customWidth="1" style="27" min="15617" max="15617"/>
+    <col width="13.25" customWidth="1" style="27" min="15618" max="15618"/>
+    <col width="9.125" customWidth="1" style="27" min="15619" max="15861"/>
+    <col width="7" customWidth="1" style="27" min="15862" max="15862"/>
+    <col width="14.75" customWidth="1" style="27" min="15863" max="15863"/>
+    <col width="13.375" customWidth="1" style="27" min="15864" max="15864"/>
+    <col width="9.875" customWidth="1" style="27" min="15865" max="15868"/>
+    <col width="10.75" customWidth="1" style="27" min="15869" max="15869"/>
+    <col width="9.875" customWidth="1" style="27" min="15870" max="15871"/>
+    <col width="14.875" customWidth="1" style="27" min="15872" max="15872"/>
+    <col width="23.875" customWidth="1" style="27" min="15873" max="15873"/>
+    <col width="13.25" customWidth="1" style="27" min="15874" max="15874"/>
+    <col width="9.125" customWidth="1" style="27" min="15875" max="16117"/>
+    <col width="7" customWidth="1" style="27" min="16118" max="16118"/>
+    <col width="14.75" customWidth="1" style="27" min="16119" max="16119"/>
+    <col width="13.375" customWidth="1" style="27" min="16120" max="16120"/>
+    <col width="9.875" customWidth="1" style="27" min="16121" max="16124"/>
+    <col width="10.75" customWidth="1" style="27" min="16125" max="16125"/>
+    <col width="9.875" customWidth="1" style="27" min="16126" max="16127"/>
+    <col width="14.875" customWidth="1" style="27" min="16128" max="16128"/>
+    <col width="23.875" customWidth="1" style="27" min="16129" max="16129"/>
+    <col width="13.25" customWidth="1" style="27" min="16130" max="16130"/>
+    <col width="9.125" customWidth="1" style="27" min="16131" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>ใบตรวจสอบเครื่อง CNC</t>
+        </is>
+      </c>
+      <c r="AA1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="AA2" s="43" t="inlineStr">
+        <is>
+          <t>Machine No. : 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="41">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="16" t="n"/>
+      <c r="W3" s="16" t="n"/>
+      <c r="X3" s="16" t="n"/>
+      <c r="Y3" s="16" t="n"/>
+      <c r="Z3" s="16" t="n"/>
+      <c r="AA3" s="16" t="n"/>
+      <c r="AB3" s="16" t="n"/>
+      <c r="AC3" s="16" t="n"/>
+      <c r="AD3" s="16" t="n"/>
+      <c r="AE3" s="16" t="n"/>
+      <c r="AF3" s="16" t="n"/>
+      <c r="AG3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="18" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>การตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ประจำเดือน  ………………………………..</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+      <c r="K4" s="36" t="n"/>
+      <c r="L4" s="36" t="n"/>
+      <c r="M4" s="36" t="n"/>
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="36" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="36" t="n"/>
+      <c r="S4" s="36" t="n"/>
+      <c r="T4" s="36" t="n"/>
+      <c r="U4" s="36" t="n"/>
+      <c r="V4" s="36" t="n"/>
+      <c r="W4" s="36" t="n"/>
+      <c r="X4" s="36" t="n"/>
+      <c r="Y4" s="36" t="n"/>
+      <c r="Z4" s="36" t="n"/>
+      <c r="AA4" s="36" t="n"/>
+      <c r="AB4" s="36" t="n"/>
+      <c r="AC4" s="36" t="n"/>
+      <c r="AD4" s="36" t="n"/>
+      <c r="AE4" s="36" t="n"/>
+      <c r="AF4" s="36" t="n"/>
+      <c r="AG4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Worm up เครื่องจักร 15 นาที ทุกครั้งที่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="22" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="22" t="n"/>
+      <c r="AA6" s="23" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="22" t="n"/>
+      <c r="AD6" s="22" t="n"/>
+      <c r="AE6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>เช็คระดับนำมันที่ Pump Hydraulic ทุกวัน เติมเมื่อพร่อง</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="23" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>ทำความสะอาด Air filter Mesh ทุกวัน</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="22" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="23" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจเช็คแรงดัน Air Control Unit ปกติเฉลี่ยที่ 0.5 Mpa</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+      <c r="U9" s="22" t="n"/>
+      <c r="V9" s="22" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="22" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="22" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="22" t="n"/>
+      <c r="AC9" s="22" t="n"/>
+      <c r="AD9" s="22" t="n"/>
+      <c r="AE9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>เช็คน้ำมันชุด Gear ของ ATC ทุกวัน(เปลี่ยนถ่ายทุกปี)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="23" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>อัดจารบี Ballscrew และ Linear Guideทุก 1ครั้งต่อเดือน</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="23" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบการเคลื่อนที่ของแกนทุกแกน (X,Y,Z)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="23" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสภาพของน้ำ Coolant ถ่ายรูปค่าที่วัดได้ส่งเข้าระบบ</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="22" t="n"/>
+      <c r="U13" s="22" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Coolant pump</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Unclamp และการเปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="22" t="n"/>
+      <c r="U15" s="22" t="n"/>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="22" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Spindle</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="22" t="n"/>
+      <c r="U16" s="22" t="n"/>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="22" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="22" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+      <c r="AE16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Arm เปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="n"/>
+      <c r="U17" s="22" t="n"/>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="22" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบระดับของน้ำ Coolant เติมเมื่ออยู่ระดับที่ต่ำ</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="22" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ความสะอาดทั่วไปของเครื่องจักรโดยรวม</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="23" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบความพร้อมสภาพโดยรวม(ฟังด้วยหู ดูด้วยตา)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="23" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสายไฮโดรลิกส์ และสายลม</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="22" t="n"/>
+      <c r="AA21" s="23" t="n"/>
+      <c r="AB21" s="22" t="n"/>
+      <c r="AC21" s="22" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n"/>
+      <c r="R22" s="28" t="n"/>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="33" t="n"/>
+      <c r="Y22" s="33" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="33" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="28" t="n"/>
+      <c r="AE22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AF22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AG22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="29" t="n"/>
+      <c r="N23" s="29" t="n"/>
+      <c r="O23" s="29" t="n"/>
+      <c r="P23" s="29" t="n"/>
+      <c r="Q23" s="29" t="n"/>
+      <c r="R23" s="29" t="n"/>
+      <c r="S23" s="29" t="n"/>
+      <c r="T23" s="29" t="n"/>
+      <c r="U23" s="29" t="n"/>
+      <c r="V23" s="29" t="n"/>
+      <c r="W23" s="29" t="n"/>
+      <c r="X23" s="29" t="n"/>
+      <c r="Y23" s="29" t="n"/>
+      <c r="Z23" s="29" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="29" t="n"/>
+      <c r="AC23" s="29" t="n"/>
+      <c r="AD23" s="29" t="n"/>
+      <c r="AE23" s="29" t="n"/>
+      <c r="AF23" s="29" t="n"/>
+      <c r="AG23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
+      <c r="M24" s="30" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="30" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="30" t="n"/>
+      <c r="U24" s="30" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="30" t="n"/>
+      <c r="X24" s="44" t="n"/>
+      <c r="Y24" s="44" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="44" t="n"/>
+      <c r="AB24" s="30" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="30" t="n"/>
+      <c r="AF24" s="30" t="n"/>
+      <c r="AG24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="29" t="n"/>
+      <c r="N25" s="29" t="n"/>
+      <c r="O25" s="29" t="n"/>
+      <c r="P25" s="29" t="n"/>
+      <c r="Q25" s="29" t="n"/>
+      <c r="R25" s="29" t="n"/>
+      <c r="S25" s="29" t="n"/>
+      <c r="T25" s="29" t="n"/>
+      <c r="U25" s="29" t="n"/>
+      <c r="V25" s="29" t="n"/>
+      <c r="W25" s="29" t="n"/>
+      <c r="X25" s="29" t="n"/>
+      <c r="Y25" s="29" t="n"/>
+      <c r="Z25" s="29" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="29" t="n"/>
+      <c r="AC25" s="29" t="n"/>
+      <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
+      <c r="AG25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>บันทึกเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="Y27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="173.25" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="AA29" s="19" t="n"/>
+      <c r="AB29" s="31" t="n"/>
+      <c r="AC29" s="32" t="n"/>
+      <c r="AD29" s="32" t="n"/>
+      <c r="AE29" s="32" t="n"/>
+      <c r="AF29" s="32" t="n"/>
+      <c r="AG29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="29.25" customHeight="1">
+      <c r="AB30" s="26" t="inlineStr">
+        <is>
+          <t>ผู้จัดการแผนกซ่อมบำรุง</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1">
+      <c r="D31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="C32" s="18" t="n"/>
+      <c r="AG32" s="20" t="inlineStr">
+        <is>
+          <t>FM-MN-07 Rev.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="71">
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="77" blackAndWhite="1" horizontalDpi="4294967293" verticalDpi="4294967293"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -669,4 +669,2250 @@
     <clientData/>
   </twoCellAnchor>
 </wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+  <a:themeElements>
+    <a:clrScheme name="Office 2007 - 2010">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office 2007 - 2010">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office 2007 - 2010">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
+  <cols>
+    <col width="4.875" customWidth="1" style="27" min="1" max="1"/>
+    <col width="58.5" customWidth="1" style="27" min="2" max="2"/>
+    <col width="3.375" customWidth="1" style="27" min="3" max="33"/>
+    <col width="9.125" customWidth="1" style="27" min="34" max="245"/>
+    <col width="7" customWidth="1" style="27" min="246" max="246"/>
+    <col width="14.75" customWidth="1" style="27" min="247" max="247"/>
+    <col width="13.375" customWidth="1" style="27" min="248" max="248"/>
+    <col width="9.875" customWidth="1" style="27" min="249" max="252"/>
+    <col width="10.75" customWidth="1" style="27" min="253" max="253"/>
+    <col width="9.875" customWidth="1" style="27" min="254" max="255"/>
+    <col width="14.875" customWidth="1" style="27" min="256" max="256"/>
+    <col width="23.875" customWidth="1" style="27" min="257" max="257"/>
+    <col width="13.25" customWidth="1" style="27" min="258" max="258"/>
+    <col width="9.125" customWidth="1" style="27" min="259" max="501"/>
+    <col width="7" customWidth="1" style="27" min="502" max="502"/>
+    <col width="14.75" customWidth="1" style="27" min="503" max="503"/>
+    <col width="13.375" customWidth="1" style="27" min="504" max="504"/>
+    <col width="9.875" customWidth="1" style="27" min="505" max="508"/>
+    <col width="10.75" customWidth="1" style="27" min="509" max="509"/>
+    <col width="9.875" customWidth="1" style="27" min="510" max="511"/>
+    <col width="14.875" customWidth="1" style="27" min="512" max="512"/>
+    <col width="23.875" customWidth="1" style="27" min="513" max="513"/>
+    <col width="13.25" customWidth="1" style="27" min="514" max="514"/>
+    <col width="9.125" customWidth="1" style="27" min="515" max="757"/>
+    <col width="7" customWidth="1" style="27" min="758" max="758"/>
+    <col width="14.75" customWidth="1" style="27" min="759" max="759"/>
+    <col width="13.375" customWidth="1" style="27" min="760" max="760"/>
+    <col width="9.875" customWidth="1" style="27" min="761" max="764"/>
+    <col width="10.75" customWidth="1" style="27" min="765" max="765"/>
+    <col width="9.875" customWidth="1" style="27" min="766" max="767"/>
+    <col width="14.875" customWidth="1" style="27" min="768" max="768"/>
+    <col width="23.875" customWidth="1" style="27" min="769" max="769"/>
+    <col width="13.25" customWidth="1" style="27" min="770" max="770"/>
+    <col width="9.125" customWidth="1" style="27" min="771" max="1013"/>
+    <col width="7" customWidth="1" style="27" min="1014" max="1014"/>
+    <col width="14.75" customWidth="1" style="27" min="1015" max="1015"/>
+    <col width="13.375" customWidth="1" style="27" min="1016" max="1016"/>
+    <col width="9.875" customWidth="1" style="27" min="1017" max="1020"/>
+    <col width="10.75" customWidth="1" style="27" min="1021" max="1021"/>
+    <col width="9.875" customWidth="1" style="27" min="1022" max="1023"/>
+    <col width="14.875" customWidth="1" style="27" min="1024" max="1024"/>
+    <col width="23.875" customWidth="1" style="27" min="1025" max="1025"/>
+    <col width="13.25" customWidth="1" style="27" min="1026" max="1026"/>
+    <col width="9.125" customWidth="1" style="27" min="1027" max="1269"/>
+    <col width="7" customWidth="1" style="27" min="1270" max="1270"/>
+    <col width="14.75" customWidth="1" style="27" min="1271" max="1271"/>
+    <col width="13.375" customWidth="1" style="27" min="1272" max="1272"/>
+    <col width="9.875" customWidth="1" style="27" min="1273" max="1276"/>
+    <col width="10.75" customWidth="1" style="27" min="1277" max="1277"/>
+    <col width="9.875" customWidth="1" style="27" min="1278" max="1279"/>
+    <col width="14.875" customWidth="1" style="27" min="1280" max="1280"/>
+    <col width="23.875" customWidth="1" style="27" min="1281" max="1281"/>
+    <col width="13.25" customWidth="1" style="27" min="1282" max="1282"/>
+    <col width="9.125" customWidth="1" style="27" min="1283" max="1525"/>
+    <col width="7" customWidth="1" style="27" min="1526" max="1526"/>
+    <col width="14.75" customWidth="1" style="27" min="1527" max="1527"/>
+    <col width="13.375" customWidth="1" style="27" min="1528" max="1528"/>
+    <col width="9.875" customWidth="1" style="27" min="1529" max="1532"/>
+    <col width="10.75" customWidth="1" style="27" min="1533" max="1533"/>
+    <col width="9.875" customWidth="1" style="27" min="1534" max="1535"/>
+    <col width="14.875" customWidth="1" style="27" min="1536" max="1536"/>
+    <col width="23.875" customWidth="1" style="27" min="1537" max="1537"/>
+    <col width="13.25" customWidth="1" style="27" min="1538" max="1538"/>
+    <col width="9.125" customWidth="1" style="27" min="1539" max="1781"/>
+    <col width="7" customWidth="1" style="27" min="1782" max="1782"/>
+    <col width="14.75" customWidth="1" style="27" min="1783" max="1783"/>
+    <col width="13.375" customWidth="1" style="27" min="1784" max="1784"/>
+    <col width="9.875" customWidth="1" style="27" min="1785" max="1788"/>
+    <col width="10.75" customWidth="1" style="27" min="1789" max="1789"/>
+    <col width="9.875" customWidth="1" style="27" min="1790" max="1791"/>
+    <col width="14.875" customWidth="1" style="27" min="1792" max="1792"/>
+    <col width="23.875" customWidth="1" style="27" min="1793" max="1793"/>
+    <col width="13.25" customWidth="1" style="27" min="1794" max="1794"/>
+    <col width="9.125" customWidth="1" style="27" min="1795" max="2037"/>
+    <col width="7" customWidth="1" style="27" min="2038" max="2038"/>
+    <col width="14.75" customWidth="1" style="27" min="2039" max="2039"/>
+    <col width="13.375" customWidth="1" style="27" min="2040" max="2040"/>
+    <col width="9.875" customWidth="1" style="27" min="2041" max="2044"/>
+    <col width="10.75" customWidth="1" style="27" min="2045" max="2045"/>
+    <col width="9.875" customWidth="1" style="27" min="2046" max="2047"/>
+    <col width="14.875" customWidth="1" style="27" min="2048" max="2048"/>
+    <col width="23.875" customWidth="1" style="27" min="2049" max="2049"/>
+    <col width="13.25" customWidth="1" style="27" min="2050" max="2050"/>
+    <col width="9.125" customWidth="1" style="27" min="2051" max="2293"/>
+    <col width="7" customWidth="1" style="27" min="2294" max="2294"/>
+    <col width="14.75" customWidth="1" style="27" min="2295" max="2295"/>
+    <col width="13.375" customWidth="1" style="27" min="2296" max="2296"/>
+    <col width="9.875" customWidth="1" style="27" min="2297" max="2300"/>
+    <col width="10.75" customWidth="1" style="27" min="2301" max="2301"/>
+    <col width="9.875" customWidth="1" style="27" min="2302" max="2303"/>
+    <col width="14.875" customWidth="1" style="27" min="2304" max="2304"/>
+    <col width="23.875" customWidth="1" style="27" min="2305" max="2305"/>
+    <col width="13.25" customWidth="1" style="27" min="2306" max="2306"/>
+    <col width="9.125" customWidth="1" style="27" min="2307" max="2549"/>
+    <col width="7" customWidth="1" style="27" min="2550" max="2550"/>
+    <col width="14.75" customWidth="1" style="27" min="2551" max="2551"/>
+    <col width="13.375" customWidth="1" style="27" min="2552" max="2552"/>
+    <col width="9.875" customWidth="1" style="27" min="2553" max="2556"/>
+    <col width="10.75" customWidth="1" style="27" min="2557" max="2557"/>
+    <col width="9.875" customWidth="1" style="27" min="2558" max="2559"/>
+    <col width="14.875" customWidth="1" style="27" min="2560" max="2560"/>
+    <col width="23.875" customWidth="1" style="27" min="2561" max="2561"/>
+    <col width="13.25" customWidth="1" style="27" min="2562" max="2562"/>
+    <col width="9.125" customWidth="1" style="27" min="2563" max="2805"/>
+    <col width="7" customWidth="1" style="27" min="2806" max="2806"/>
+    <col width="14.75" customWidth="1" style="27" min="2807" max="2807"/>
+    <col width="13.375" customWidth="1" style="27" min="2808" max="2808"/>
+    <col width="9.875" customWidth="1" style="27" min="2809" max="2812"/>
+    <col width="10.75" customWidth="1" style="27" min="2813" max="2813"/>
+    <col width="9.875" customWidth="1" style="27" min="2814" max="2815"/>
+    <col width="14.875" customWidth="1" style="27" min="2816" max="2816"/>
+    <col width="23.875" customWidth="1" style="27" min="2817" max="2817"/>
+    <col width="13.25" customWidth="1" style="27" min="2818" max="2818"/>
+    <col width="9.125" customWidth="1" style="27" min="2819" max="3061"/>
+    <col width="7" customWidth="1" style="27" min="3062" max="3062"/>
+    <col width="14.75" customWidth="1" style="27" min="3063" max="3063"/>
+    <col width="13.375" customWidth="1" style="27" min="3064" max="3064"/>
+    <col width="9.875" customWidth="1" style="27" min="3065" max="3068"/>
+    <col width="10.75" customWidth="1" style="27" min="3069" max="3069"/>
+    <col width="9.875" customWidth="1" style="27" min="3070" max="3071"/>
+    <col width="14.875" customWidth="1" style="27" min="3072" max="3072"/>
+    <col width="23.875" customWidth="1" style="27" min="3073" max="3073"/>
+    <col width="13.25" customWidth="1" style="27" min="3074" max="3074"/>
+    <col width="9.125" customWidth="1" style="27" min="3075" max="3317"/>
+    <col width="7" customWidth="1" style="27" min="3318" max="3318"/>
+    <col width="14.75" customWidth="1" style="27" min="3319" max="3319"/>
+    <col width="13.375" customWidth="1" style="27" min="3320" max="3320"/>
+    <col width="9.875" customWidth="1" style="27" min="3321" max="3324"/>
+    <col width="10.75" customWidth="1" style="27" min="3325" max="3325"/>
+    <col width="9.875" customWidth="1" style="27" min="3326" max="3327"/>
+    <col width="14.875" customWidth="1" style="27" min="3328" max="3328"/>
+    <col width="23.875" customWidth="1" style="27" min="3329" max="3329"/>
+    <col width="13.25" customWidth="1" style="27" min="3330" max="3330"/>
+    <col width="9.125" customWidth="1" style="27" min="3331" max="3573"/>
+    <col width="7" customWidth="1" style="27" min="3574" max="3574"/>
+    <col width="14.75" customWidth="1" style="27" min="3575" max="3575"/>
+    <col width="13.375" customWidth="1" style="27" min="3576" max="3576"/>
+    <col width="9.875" customWidth="1" style="27" min="3577" max="3580"/>
+    <col width="10.75" customWidth="1" style="27" min="3581" max="3581"/>
+    <col width="9.875" customWidth="1" style="27" min="3582" max="3583"/>
+    <col width="14.875" customWidth="1" style="27" min="3584" max="3584"/>
+    <col width="23.875" customWidth="1" style="27" min="3585" max="3585"/>
+    <col width="13.25" customWidth="1" style="27" min="3586" max="3586"/>
+    <col width="9.125" customWidth="1" style="27" min="3587" max="3829"/>
+    <col width="7" customWidth="1" style="27" min="3830" max="3830"/>
+    <col width="14.75" customWidth="1" style="27" min="3831" max="3831"/>
+    <col width="13.375" customWidth="1" style="27" min="3832" max="3832"/>
+    <col width="9.875" customWidth="1" style="27" min="3833" max="3836"/>
+    <col width="10.75" customWidth="1" style="27" min="3837" max="3837"/>
+    <col width="9.875" customWidth="1" style="27" min="3838" max="3839"/>
+    <col width="14.875" customWidth="1" style="27" min="3840" max="3840"/>
+    <col width="23.875" customWidth="1" style="27" min="3841" max="3841"/>
+    <col width="13.25" customWidth="1" style="27" min="3842" max="3842"/>
+    <col width="9.125" customWidth="1" style="27" min="3843" max="4085"/>
+    <col width="7" customWidth="1" style="27" min="4086" max="4086"/>
+    <col width="14.75" customWidth="1" style="27" min="4087" max="4087"/>
+    <col width="13.375" customWidth="1" style="27" min="4088" max="4088"/>
+    <col width="9.875" customWidth="1" style="27" min="4089" max="4092"/>
+    <col width="10.75" customWidth="1" style="27" min="4093" max="4093"/>
+    <col width="9.875" customWidth="1" style="27" min="4094" max="4095"/>
+    <col width="14.875" customWidth="1" style="27" min="4096" max="4096"/>
+    <col width="23.875" customWidth="1" style="27" min="4097" max="4097"/>
+    <col width="13.25" customWidth="1" style="27" min="4098" max="4098"/>
+    <col width="9.125" customWidth="1" style="27" min="4099" max="4341"/>
+    <col width="7" customWidth="1" style="27" min="4342" max="4342"/>
+    <col width="14.75" customWidth="1" style="27" min="4343" max="4343"/>
+    <col width="13.375" customWidth="1" style="27" min="4344" max="4344"/>
+    <col width="9.875" customWidth="1" style="27" min="4345" max="4348"/>
+    <col width="10.75" customWidth="1" style="27" min="4349" max="4349"/>
+    <col width="9.875" customWidth="1" style="27" min="4350" max="4351"/>
+    <col width="14.875" customWidth="1" style="27" min="4352" max="4352"/>
+    <col width="23.875" customWidth="1" style="27" min="4353" max="4353"/>
+    <col width="13.25" customWidth="1" style="27" min="4354" max="4354"/>
+    <col width="9.125" customWidth="1" style="27" min="4355" max="4597"/>
+    <col width="7" customWidth="1" style="27" min="4598" max="4598"/>
+    <col width="14.75" customWidth="1" style="27" min="4599" max="4599"/>
+    <col width="13.375" customWidth="1" style="27" min="4600" max="4600"/>
+    <col width="9.875" customWidth="1" style="27" min="4601" max="4604"/>
+    <col width="10.75" customWidth="1" style="27" min="4605" max="4605"/>
+    <col width="9.875" customWidth="1" style="27" min="4606" max="4607"/>
+    <col width="14.875" customWidth="1" style="27" min="4608" max="4608"/>
+    <col width="23.875" customWidth="1" style="27" min="4609" max="4609"/>
+    <col width="13.25" customWidth="1" style="27" min="4610" max="4610"/>
+    <col width="9.125" customWidth="1" style="27" min="4611" max="4853"/>
+    <col width="7" customWidth="1" style="27" min="4854" max="4854"/>
+    <col width="14.75" customWidth="1" style="27" min="4855" max="4855"/>
+    <col width="13.375" customWidth="1" style="27" min="4856" max="4856"/>
+    <col width="9.875" customWidth="1" style="27" min="4857" max="4860"/>
+    <col width="10.75" customWidth="1" style="27" min="4861" max="4861"/>
+    <col width="9.875" customWidth="1" style="27" min="4862" max="4863"/>
+    <col width="14.875" customWidth="1" style="27" min="4864" max="4864"/>
+    <col width="23.875" customWidth="1" style="27" min="4865" max="4865"/>
+    <col width="13.25" customWidth="1" style="27" min="4866" max="4866"/>
+    <col width="9.125" customWidth="1" style="27" min="4867" max="5109"/>
+    <col width="7" customWidth="1" style="27" min="5110" max="5110"/>
+    <col width="14.75" customWidth="1" style="27" min="5111" max="5111"/>
+    <col width="13.375" customWidth="1" style="27" min="5112" max="5112"/>
+    <col width="9.875" customWidth="1" style="27" min="5113" max="5116"/>
+    <col width="10.75" customWidth="1" style="27" min="5117" max="5117"/>
+    <col width="9.875" customWidth="1" style="27" min="5118" max="5119"/>
+    <col width="14.875" customWidth="1" style="27" min="5120" max="5120"/>
+    <col width="23.875" customWidth="1" style="27" min="5121" max="5121"/>
+    <col width="13.25" customWidth="1" style="27" min="5122" max="5122"/>
+    <col width="9.125" customWidth="1" style="27" min="5123" max="5365"/>
+    <col width="7" customWidth="1" style="27" min="5366" max="5366"/>
+    <col width="14.75" customWidth="1" style="27" min="5367" max="5367"/>
+    <col width="13.375" customWidth="1" style="27" min="5368" max="5368"/>
+    <col width="9.875" customWidth="1" style="27" min="5369" max="5372"/>
+    <col width="10.75" customWidth="1" style="27" min="5373" max="5373"/>
+    <col width="9.875" customWidth="1" style="27" min="5374" max="5375"/>
+    <col width="14.875" customWidth="1" style="27" min="5376" max="5376"/>
+    <col width="23.875" customWidth="1" style="27" min="5377" max="5377"/>
+    <col width="13.25" customWidth="1" style="27" min="5378" max="5378"/>
+    <col width="9.125" customWidth="1" style="27" min="5379" max="5621"/>
+    <col width="7" customWidth="1" style="27" min="5622" max="5622"/>
+    <col width="14.75" customWidth="1" style="27" min="5623" max="5623"/>
+    <col width="13.375" customWidth="1" style="27" min="5624" max="5624"/>
+    <col width="9.875" customWidth="1" style="27" min="5625" max="5628"/>
+    <col width="10.75" customWidth="1" style="27" min="5629" max="5629"/>
+    <col width="9.875" customWidth="1" style="27" min="5630" max="5631"/>
+    <col width="14.875" customWidth="1" style="27" min="5632" max="5632"/>
+    <col width="23.875" customWidth="1" style="27" min="5633" max="5633"/>
+    <col width="13.25" customWidth="1" style="27" min="5634" max="5634"/>
+    <col width="9.125" customWidth="1" style="27" min="5635" max="5877"/>
+    <col width="7" customWidth="1" style="27" min="5878" max="5878"/>
+    <col width="14.75" customWidth="1" style="27" min="5879" max="5879"/>
+    <col width="13.375" customWidth="1" style="27" min="5880" max="5880"/>
+    <col width="9.875" customWidth="1" style="27" min="5881" max="5884"/>
+    <col width="10.75" customWidth="1" style="27" min="5885" max="5885"/>
+    <col width="9.875" customWidth="1" style="27" min="5886" max="5887"/>
+    <col width="14.875" customWidth="1" style="27" min="5888" max="5888"/>
+    <col width="23.875" customWidth="1" style="27" min="5889" max="5889"/>
+    <col width="13.25" customWidth="1" style="27" min="5890" max="5890"/>
+    <col width="9.125" customWidth="1" style="27" min="5891" max="6133"/>
+    <col width="7" customWidth="1" style="27" min="6134" max="6134"/>
+    <col width="14.75" customWidth="1" style="27" min="6135" max="6135"/>
+    <col width="13.375" customWidth="1" style="27" min="6136" max="6136"/>
+    <col width="9.875" customWidth="1" style="27" min="6137" max="6140"/>
+    <col width="10.75" customWidth="1" style="27" min="6141" max="6141"/>
+    <col width="9.875" customWidth="1" style="27" min="6142" max="6143"/>
+    <col width="14.875" customWidth="1" style="27" min="6144" max="6144"/>
+    <col width="23.875" customWidth="1" style="27" min="6145" max="6145"/>
+    <col width="13.25" customWidth="1" style="27" min="6146" max="6146"/>
+    <col width="9.125" customWidth="1" style="27" min="6147" max="6389"/>
+    <col width="7" customWidth="1" style="27" min="6390" max="6390"/>
+    <col width="14.75" customWidth="1" style="27" min="6391" max="6391"/>
+    <col width="13.375" customWidth="1" style="27" min="6392" max="6392"/>
+    <col width="9.875" customWidth="1" style="27" min="6393" max="6396"/>
+    <col width="10.75" customWidth="1" style="27" min="6397" max="6397"/>
+    <col width="9.875" customWidth="1" style="27" min="6398" max="6399"/>
+    <col width="14.875" customWidth="1" style="27" min="6400" max="6400"/>
+    <col width="23.875" customWidth="1" style="27" min="6401" max="6401"/>
+    <col width="13.25" customWidth="1" style="27" min="6402" max="6402"/>
+    <col width="9.125" customWidth="1" style="27" min="6403" max="6645"/>
+    <col width="7" customWidth="1" style="27" min="6646" max="6646"/>
+    <col width="14.75" customWidth="1" style="27" min="6647" max="6647"/>
+    <col width="13.375" customWidth="1" style="27" min="6648" max="6648"/>
+    <col width="9.875" customWidth="1" style="27" min="6649" max="6652"/>
+    <col width="10.75" customWidth="1" style="27" min="6653" max="6653"/>
+    <col width="9.875" customWidth="1" style="27" min="6654" max="6655"/>
+    <col width="14.875" customWidth="1" style="27" min="6656" max="6656"/>
+    <col width="23.875" customWidth="1" style="27" min="6657" max="6657"/>
+    <col width="13.25" customWidth="1" style="27" min="6658" max="6658"/>
+    <col width="9.125" customWidth="1" style="27" min="6659" max="6901"/>
+    <col width="7" customWidth="1" style="27" min="6902" max="6902"/>
+    <col width="14.75" customWidth="1" style="27" min="6903" max="6903"/>
+    <col width="13.375" customWidth="1" style="27" min="6904" max="6904"/>
+    <col width="9.875" customWidth="1" style="27" min="6905" max="6908"/>
+    <col width="10.75" customWidth="1" style="27" min="6909" max="6909"/>
+    <col width="9.875" customWidth="1" style="27" min="6910" max="6911"/>
+    <col width="14.875" customWidth="1" style="27" min="6912" max="6912"/>
+    <col width="23.875" customWidth="1" style="27" min="6913" max="6913"/>
+    <col width="13.25" customWidth="1" style="27" min="6914" max="6914"/>
+    <col width="9.125" customWidth="1" style="27" min="6915" max="7157"/>
+    <col width="7" customWidth="1" style="27" min="7158" max="7158"/>
+    <col width="14.75" customWidth="1" style="27" min="7159" max="7159"/>
+    <col width="13.375" customWidth="1" style="27" min="7160" max="7160"/>
+    <col width="9.875" customWidth="1" style="27" min="7161" max="7164"/>
+    <col width="10.75" customWidth="1" style="27" min="7165" max="7165"/>
+    <col width="9.875" customWidth="1" style="27" min="7166" max="7167"/>
+    <col width="14.875" customWidth="1" style="27" min="7168" max="7168"/>
+    <col width="23.875" customWidth="1" style="27" min="7169" max="7169"/>
+    <col width="13.25" customWidth="1" style="27" min="7170" max="7170"/>
+    <col width="9.125" customWidth="1" style="27" min="7171" max="7413"/>
+    <col width="7" customWidth="1" style="27" min="7414" max="7414"/>
+    <col width="14.75" customWidth="1" style="27" min="7415" max="7415"/>
+    <col width="13.375" customWidth="1" style="27" min="7416" max="7416"/>
+    <col width="9.875" customWidth="1" style="27" min="7417" max="7420"/>
+    <col width="10.75" customWidth="1" style="27" min="7421" max="7421"/>
+    <col width="9.875" customWidth="1" style="27" min="7422" max="7423"/>
+    <col width="14.875" customWidth="1" style="27" min="7424" max="7424"/>
+    <col width="23.875" customWidth="1" style="27" min="7425" max="7425"/>
+    <col width="13.25" customWidth="1" style="27" min="7426" max="7426"/>
+    <col width="9.125" customWidth="1" style="27" min="7427" max="7669"/>
+    <col width="7" customWidth="1" style="27" min="7670" max="7670"/>
+    <col width="14.75" customWidth="1" style="27" min="7671" max="7671"/>
+    <col width="13.375" customWidth="1" style="27" min="7672" max="7672"/>
+    <col width="9.875" customWidth="1" style="27" min="7673" max="7676"/>
+    <col width="10.75" customWidth="1" style="27" min="7677" max="7677"/>
+    <col width="9.875" customWidth="1" style="27" min="7678" max="7679"/>
+    <col width="14.875" customWidth="1" style="27" min="7680" max="7680"/>
+    <col width="23.875" customWidth="1" style="27" min="7681" max="7681"/>
+    <col width="13.25" customWidth="1" style="27" min="7682" max="7682"/>
+    <col width="9.125" customWidth="1" style="27" min="7683" max="7925"/>
+    <col width="7" customWidth="1" style="27" min="7926" max="7926"/>
+    <col width="14.75" customWidth="1" style="27" min="7927" max="7927"/>
+    <col width="13.375" customWidth="1" style="27" min="7928" max="7928"/>
+    <col width="9.875" customWidth="1" style="27" min="7929" max="7932"/>
+    <col width="10.75" customWidth="1" style="27" min="7933" max="7933"/>
+    <col width="9.875" customWidth="1" style="27" min="7934" max="7935"/>
+    <col width="14.875" customWidth="1" style="27" min="7936" max="7936"/>
+    <col width="23.875" customWidth="1" style="27" min="7937" max="7937"/>
+    <col width="13.25" customWidth="1" style="27" min="7938" max="7938"/>
+    <col width="9.125" customWidth="1" style="27" min="7939" max="8181"/>
+    <col width="7" customWidth="1" style="27" min="8182" max="8182"/>
+    <col width="14.75" customWidth="1" style="27" min="8183" max="8183"/>
+    <col width="13.375" customWidth="1" style="27" min="8184" max="8184"/>
+    <col width="9.875" customWidth="1" style="27" min="8185" max="8188"/>
+    <col width="10.75" customWidth="1" style="27" min="8189" max="8189"/>
+    <col width="9.875" customWidth="1" style="27" min="8190" max="8191"/>
+    <col width="14.875" customWidth="1" style="27" min="8192" max="8192"/>
+    <col width="23.875" customWidth="1" style="27" min="8193" max="8193"/>
+    <col width="13.25" customWidth="1" style="27" min="8194" max="8194"/>
+    <col width="9.125" customWidth="1" style="27" min="8195" max="8437"/>
+    <col width="7" customWidth="1" style="27" min="8438" max="8438"/>
+    <col width="14.75" customWidth="1" style="27" min="8439" max="8439"/>
+    <col width="13.375" customWidth="1" style="27" min="8440" max="8440"/>
+    <col width="9.875" customWidth="1" style="27" min="8441" max="8444"/>
+    <col width="10.75" customWidth="1" style="27" min="8445" max="8445"/>
+    <col width="9.875" customWidth="1" style="27" min="8446" max="8447"/>
+    <col width="14.875" customWidth="1" style="27" min="8448" max="8448"/>
+    <col width="23.875" customWidth="1" style="27" min="8449" max="8449"/>
+    <col width="13.25" customWidth="1" style="27" min="8450" max="8450"/>
+    <col width="9.125" customWidth="1" style="27" min="8451" max="8693"/>
+    <col width="7" customWidth="1" style="27" min="8694" max="8694"/>
+    <col width="14.75" customWidth="1" style="27" min="8695" max="8695"/>
+    <col width="13.375" customWidth="1" style="27" min="8696" max="8696"/>
+    <col width="9.875" customWidth="1" style="27" min="8697" max="8700"/>
+    <col width="10.75" customWidth="1" style="27" min="8701" max="8701"/>
+    <col width="9.875" customWidth="1" style="27" min="8702" max="8703"/>
+    <col width="14.875" customWidth="1" style="27" min="8704" max="8704"/>
+    <col width="23.875" customWidth="1" style="27" min="8705" max="8705"/>
+    <col width="13.25" customWidth="1" style="27" min="8706" max="8706"/>
+    <col width="9.125" customWidth="1" style="27" min="8707" max="8949"/>
+    <col width="7" customWidth="1" style="27" min="8950" max="8950"/>
+    <col width="14.75" customWidth="1" style="27" min="8951" max="8951"/>
+    <col width="13.375" customWidth="1" style="27" min="8952" max="8952"/>
+    <col width="9.875" customWidth="1" style="27" min="8953" max="8956"/>
+    <col width="10.75" customWidth="1" style="27" min="8957" max="8957"/>
+    <col width="9.875" customWidth="1" style="27" min="8958" max="8959"/>
+    <col width="14.875" customWidth="1" style="27" min="8960" max="8960"/>
+    <col width="23.875" customWidth="1" style="27" min="8961" max="8961"/>
+    <col width="13.25" customWidth="1" style="27" min="8962" max="8962"/>
+    <col width="9.125" customWidth="1" style="27" min="8963" max="9205"/>
+    <col width="7" customWidth="1" style="27" min="9206" max="9206"/>
+    <col width="14.75" customWidth="1" style="27" min="9207" max="9207"/>
+    <col width="13.375" customWidth="1" style="27" min="9208" max="9208"/>
+    <col width="9.875" customWidth="1" style="27" min="9209" max="9212"/>
+    <col width="10.75" customWidth="1" style="27" min="9213" max="9213"/>
+    <col width="9.875" customWidth="1" style="27" min="9214" max="9215"/>
+    <col width="14.875" customWidth="1" style="27" min="9216" max="9216"/>
+    <col width="23.875" customWidth="1" style="27" min="9217" max="9217"/>
+    <col width="13.25" customWidth="1" style="27" min="9218" max="9218"/>
+    <col width="9.125" customWidth="1" style="27" min="9219" max="9461"/>
+    <col width="7" customWidth="1" style="27" min="9462" max="9462"/>
+    <col width="14.75" customWidth="1" style="27" min="9463" max="9463"/>
+    <col width="13.375" customWidth="1" style="27" min="9464" max="9464"/>
+    <col width="9.875" customWidth="1" style="27" min="9465" max="9468"/>
+    <col width="10.75" customWidth="1" style="27" min="9469" max="9469"/>
+    <col width="9.875" customWidth="1" style="27" min="9470" max="9471"/>
+    <col width="14.875" customWidth="1" style="27" min="9472" max="9472"/>
+    <col width="23.875" customWidth="1" style="27" min="9473" max="9473"/>
+    <col width="13.25" customWidth="1" style="27" min="9474" max="9474"/>
+    <col width="9.125" customWidth="1" style="27" min="9475" max="9717"/>
+    <col width="7" customWidth="1" style="27" min="9718" max="9718"/>
+    <col width="14.75" customWidth="1" style="27" min="9719" max="9719"/>
+    <col width="13.375" customWidth="1" style="27" min="9720" max="9720"/>
+    <col width="9.875" customWidth="1" style="27" min="9721" max="9724"/>
+    <col width="10.75" customWidth="1" style="27" min="9725" max="9725"/>
+    <col width="9.875" customWidth="1" style="27" min="9726" max="9727"/>
+    <col width="14.875" customWidth="1" style="27" min="9728" max="9728"/>
+    <col width="23.875" customWidth="1" style="27" min="9729" max="9729"/>
+    <col width="13.25" customWidth="1" style="27" min="9730" max="9730"/>
+    <col width="9.125" customWidth="1" style="27" min="9731" max="9973"/>
+    <col width="7" customWidth="1" style="27" min="9974" max="9974"/>
+    <col width="14.75" customWidth="1" style="27" min="9975" max="9975"/>
+    <col width="13.375" customWidth="1" style="27" min="9976" max="9976"/>
+    <col width="9.875" customWidth="1" style="27" min="9977" max="9980"/>
+    <col width="10.75" customWidth="1" style="27" min="9981" max="9981"/>
+    <col width="9.875" customWidth="1" style="27" min="9982" max="9983"/>
+    <col width="14.875" customWidth="1" style="27" min="9984" max="9984"/>
+    <col width="23.875" customWidth="1" style="27" min="9985" max="9985"/>
+    <col width="13.25" customWidth="1" style="27" min="9986" max="9986"/>
+    <col width="9.125" customWidth="1" style="27" min="9987" max="10229"/>
+    <col width="7" customWidth="1" style="27" min="10230" max="10230"/>
+    <col width="14.75" customWidth="1" style="27" min="10231" max="10231"/>
+    <col width="13.375" customWidth="1" style="27" min="10232" max="10232"/>
+    <col width="9.875" customWidth="1" style="27" min="10233" max="10236"/>
+    <col width="10.75" customWidth="1" style="27" min="10237" max="10237"/>
+    <col width="9.875" customWidth="1" style="27" min="10238" max="10239"/>
+    <col width="14.875" customWidth="1" style="27" min="10240" max="10240"/>
+    <col width="23.875" customWidth="1" style="27" min="10241" max="10241"/>
+    <col width="13.25" customWidth="1" style="27" min="10242" max="10242"/>
+    <col width="9.125" customWidth="1" style="27" min="10243" max="10485"/>
+    <col width="7" customWidth="1" style="27" min="10486" max="10486"/>
+    <col width="14.75" customWidth="1" style="27" min="10487" max="10487"/>
+    <col width="13.375" customWidth="1" style="27" min="10488" max="10488"/>
+    <col width="9.875" customWidth="1" style="27" min="10489" max="10492"/>
+    <col width="10.75" customWidth="1" style="27" min="10493" max="10493"/>
+    <col width="9.875" customWidth="1" style="27" min="10494" max="10495"/>
+    <col width="14.875" customWidth="1" style="27" min="10496" max="10496"/>
+    <col width="23.875" customWidth="1" style="27" min="10497" max="10497"/>
+    <col width="13.25" customWidth="1" style="27" min="10498" max="10498"/>
+    <col width="9.125" customWidth="1" style="27" min="10499" max="10741"/>
+    <col width="7" customWidth="1" style="27" min="10742" max="10742"/>
+    <col width="14.75" customWidth="1" style="27" min="10743" max="10743"/>
+    <col width="13.375" customWidth="1" style="27" min="10744" max="10744"/>
+    <col width="9.875" customWidth="1" style="27" min="10745" max="10748"/>
+    <col width="10.75" customWidth="1" style="27" min="10749" max="10749"/>
+    <col width="9.875" customWidth="1" style="27" min="10750" max="10751"/>
+    <col width="14.875" customWidth="1" style="27" min="10752" max="10752"/>
+    <col width="23.875" customWidth="1" style="27" min="10753" max="10753"/>
+    <col width="13.25" customWidth="1" style="27" min="10754" max="10754"/>
+    <col width="9.125" customWidth="1" style="27" min="10755" max="10997"/>
+    <col width="7" customWidth="1" style="27" min="10998" max="10998"/>
+    <col width="14.75" customWidth="1" style="27" min="10999" max="10999"/>
+    <col width="13.375" customWidth="1" style="27" min="11000" max="11000"/>
+    <col width="9.875" customWidth="1" style="27" min="11001" max="11004"/>
+    <col width="10.75" customWidth="1" style="27" min="11005" max="11005"/>
+    <col width="9.875" customWidth="1" style="27" min="11006" max="11007"/>
+    <col width="14.875" customWidth="1" style="27" min="11008" max="11008"/>
+    <col width="23.875" customWidth="1" style="27" min="11009" max="11009"/>
+    <col width="13.25" customWidth="1" style="27" min="11010" max="11010"/>
+    <col width="9.125" customWidth="1" style="27" min="11011" max="11253"/>
+    <col width="7" customWidth="1" style="27" min="11254" max="11254"/>
+    <col width="14.75" customWidth="1" style="27" min="11255" max="11255"/>
+    <col width="13.375" customWidth="1" style="27" min="11256" max="11256"/>
+    <col width="9.875" customWidth="1" style="27" min="11257" max="11260"/>
+    <col width="10.75" customWidth="1" style="27" min="11261" max="11261"/>
+    <col width="9.875" customWidth="1" style="27" min="11262" max="11263"/>
+    <col width="14.875" customWidth="1" style="27" min="11264" max="11264"/>
+    <col width="23.875" customWidth="1" style="27" min="11265" max="11265"/>
+    <col width="13.25" customWidth="1" style="27" min="11266" max="11266"/>
+    <col width="9.125" customWidth="1" style="27" min="11267" max="11509"/>
+    <col width="7" customWidth="1" style="27" min="11510" max="11510"/>
+    <col width="14.75" customWidth="1" style="27" min="11511" max="11511"/>
+    <col width="13.375" customWidth="1" style="27" min="11512" max="11512"/>
+    <col width="9.875" customWidth="1" style="27" min="11513" max="11516"/>
+    <col width="10.75" customWidth="1" style="27" min="11517" max="11517"/>
+    <col width="9.875" customWidth="1" style="27" min="11518" max="11519"/>
+    <col width="14.875" customWidth="1" style="27" min="11520" max="11520"/>
+    <col width="23.875" customWidth="1" style="27" min="11521" max="11521"/>
+    <col width="13.25" customWidth="1" style="27" min="11522" max="11522"/>
+    <col width="9.125" customWidth="1" style="27" min="11523" max="11765"/>
+    <col width="7" customWidth="1" style="27" min="11766" max="11766"/>
+    <col width="14.75" customWidth="1" style="27" min="11767" max="11767"/>
+    <col width="13.375" customWidth="1" style="27" min="11768" max="11768"/>
+    <col width="9.875" customWidth="1" style="27" min="11769" max="11772"/>
+    <col width="10.75" customWidth="1" style="27" min="11773" max="11773"/>
+    <col width="9.875" customWidth="1" style="27" min="11774" max="11775"/>
+    <col width="14.875" customWidth="1" style="27" min="11776" max="11776"/>
+    <col width="23.875" customWidth="1" style="27" min="11777" max="11777"/>
+    <col width="13.25" customWidth="1" style="27" min="11778" max="11778"/>
+    <col width="9.125" customWidth="1" style="27" min="11779" max="12021"/>
+    <col width="7" customWidth="1" style="27" min="12022" max="12022"/>
+    <col width="14.75" customWidth="1" style="27" min="12023" max="12023"/>
+    <col width="13.375" customWidth="1" style="27" min="12024" max="12024"/>
+    <col width="9.875" customWidth="1" style="27" min="12025" max="12028"/>
+    <col width="10.75" customWidth="1" style="27" min="12029" max="12029"/>
+    <col width="9.875" customWidth="1" style="27" min="12030" max="12031"/>
+    <col width="14.875" customWidth="1" style="27" min="12032" max="12032"/>
+    <col width="23.875" customWidth="1" style="27" min="12033" max="12033"/>
+    <col width="13.25" customWidth="1" style="27" min="12034" max="12034"/>
+    <col width="9.125" customWidth="1" style="27" min="12035" max="12277"/>
+    <col width="7" customWidth="1" style="27" min="12278" max="12278"/>
+    <col width="14.75" customWidth="1" style="27" min="12279" max="12279"/>
+    <col width="13.375" customWidth="1" style="27" min="12280" max="12280"/>
+    <col width="9.875" customWidth="1" style="27" min="12281" max="12284"/>
+    <col width="10.75" customWidth="1" style="27" min="12285" max="12285"/>
+    <col width="9.875" customWidth="1" style="27" min="12286" max="12287"/>
+    <col width="14.875" customWidth="1" style="27" min="12288" max="12288"/>
+    <col width="23.875" customWidth="1" style="27" min="12289" max="12289"/>
+    <col width="13.25" customWidth="1" style="27" min="12290" max="12290"/>
+    <col width="9.125" customWidth="1" style="27" min="12291" max="12533"/>
+    <col width="7" customWidth="1" style="27" min="12534" max="12534"/>
+    <col width="14.75" customWidth="1" style="27" min="12535" max="12535"/>
+    <col width="13.375" customWidth="1" style="27" min="12536" max="12536"/>
+    <col width="9.875" customWidth="1" style="27" min="12537" max="12540"/>
+    <col width="10.75" customWidth="1" style="27" min="12541" max="12541"/>
+    <col width="9.875" customWidth="1" style="27" min="12542" max="12543"/>
+    <col width="14.875" customWidth="1" style="27" min="12544" max="12544"/>
+    <col width="23.875" customWidth="1" style="27" min="12545" max="12545"/>
+    <col width="13.25" customWidth="1" style="27" min="12546" max="12546"/>
+    <col width="9.125" customWidth="1" style="27" min="12547" max="12789"/>
+    <col width="7" customWidth="1" style="27" min="12790" max="12790"/>
+    <col width="14.75" customWidth="1" style="27" min="12791" max="12791"/>
+    <col width="13.375" customWidth="1" style="27" min="12792" max="12792"/>
+    <col width="9.875" customWidth="1" style="27" min="12793" max="12796"/>
+    <col width="10.75" customWidth="1" style="27" min="12797" max="12797"/>
+    <col width="9.875" customWidth="1" style="27" min="12798" max="12799"/>
+    <col width="14.875" customWidth="1" style="27" min="12800" max="12800"/>
+    <col width="23.875" customWidth="1" style="27" min="12801" max="12801"/>
+    <col width="13.25" customWidth="1" style="27" min="12802" max="12802"/>
+    <col width="9.125" customWidth="1" style="27" min="12803" max="13045"/>
+    <col width="7" customWidth="1" style="27" min="13046" max="13046"/>
+    <col width="14.75" customWidth="1" style="27" min="13047" max="13047"/>
+    <col width="13.375" customWidth="1" style="27" min="13048" max="13048"/>
+    <col width="9.875" customWidth="1" style="27" min="13049" max="13052"/>
+    <col width="10.75" customWidth="1" style="27" min="13053" max="13053"/>
+    <col width="9.875" customWidth="1" style="27" min="13054" max="13055"/>
+    <col width="14.875" customWidth="1" style="27" min="13056" max="13056"/>
+    <col width="23.875" customWidth="1" style="27" min="13057" max="13057"/>
+    <col width="13.25" customWidth="1" style="27" min="13058" max="13058"/>
+    <col width="9.125" customWidth="1" style="27" min="13059" max="13301"/>
+    <col width="7" customWidth="1" style="27" min="13302" max="13302"/>
+    <col width="14.75" customWidth="1" style="27" min="13303" max="13303"/>
+    <col width="13.375" customWidth="1" style="27" min="13304" max="13304"/>
+    <col width="9.875" customWidth="1" style="27" min="13305" max="13308"/>
+    <col width="10.75" customWidth="1" style="27" min="13309" max="13309"/>
+    <col width="9.875" customWidth="1" style="27" min="13310" max="13311"/>
+    <col width="14.875" customWidth="1" style="27" min="13312" max="13312"/>
+    <col width="23.875" customWidth="1" style="27" min="13313" max="13313"/>
+    <col width="13.25" customWidth="1" style="27" min="13314" max="13314"/>
+    <col width="9.125" customWidth="1" style="27" min="13315" max="13557"/>
+    <col width="7" customWidth="1" style="27" min="13558" max="13558"/>
+    <col width="14.75" customWidth="1" style="27" min="13559" max="13559"/>
+    <col width="13.375" customWidth="1" style="27" min="13560" max="13560"/>
+    <col width="9.875" customWidth="1" style="27" min="13561" max="13564"/>
+    <col width="10.75" customWidth="1" style="27" min="13565" max="13565"/>
+    <col width="9.875" customWidth="1" style="27" min="13566" max="13567"/>
+    <col width="14.875" customWidth="1" style="27" min="13568" max="13568"/>
+    <col width="23.875" customWidth="1" style="27" min="13569" max="13569"/>
+    <col width="13.25" customWidth="1" style="27" min="13570" max="13570"/>
+    <col width="9.125" customWidth="1" style="27" min="13571" max="13813"/>
+    <col width="7" customWidth="1" style="27" min="13814" max="13814"/>
+    <col width="14.75" customWidth="1" style="27" min="13815" max="13815"/>
+    <col width="13.375" customWidth="1" style="27" min="13816" max="13816"/>
+    <col width="9.875" customWidth="1" style="27" min="13817" max="13820"/>
+    <col width="10.75" customWidth="1" style="27" min="13821" max="13821"/>
+    <col width="9.875" customWidth="1" style="27" min="13822" max="13823"/>
+    <col width="14.875" customWidth="1" style="27" min="13824" max="13824"/>
+    <col width="23.875" customWidth="1" style="27" min="13825" max="13825"/>
+    <col width="13.25" customWidth="1" style="27" min="13826" max="13826"/>
+    <col width="9.125" customWidth="1" style="27" min="13827" max="14069"/>
+    <col width="7" customWidth="1" style="27" min="14070" max="14070"/>
+    <col width="14.75" customWidth="1" style="27" min="14071" max="14071"/>
+    <col width="13.375" customWidth="1" style="27" min="14072" max="14072"/>
+    <col width="9.875" customWidth="1" style="27" min="14073" max="14076"/>
+    <col width="10.75" customWidth="1" style="27" min="14077" max="14077"/>
+    <col width="9.875" customWidth="1" style="27" min="14078" max="14079"/>
+    <col width="14.875" customWidth="1" style="27" min="14080" max="14080"/>
+    <col width="23.875" customWidth="1" style="27" min="14081" max="14081"/>
+    <col width="13.25" customWidth="1" style="27" min="14082" max="14082"/>
+    <col width="9.125" customWidth="1" style="27" min="14083" max="14325"/>
+    <col width="7" customWidth="1" style="27" min="14326" max="14326"/>
+    <col width="14.75" customWidth="1" style="27" min="14327" max="14327"/>
+    <col width="13.375" customWidth="1" style="27" min="14328" max="14328"/>
+    <col width="9.875" customWidth="1" style="27" min="14329" max="14332"/>
+    <col width="10.75" customWidth="1" style="27" min="14333" max="14333"/>
+    <col width="9.875" customWidth="1" style="27" min="14334" max="14335"/>
+    <col width="14.875" customWidth="1" style="27" min="14336" max="14336"/>
+    <col width="23.875" customWidth="1" style="27" min="14337" max="14337"/>
+    <col width="13.25" customWidth="1" style="27" min="14338" max="14338"/>
+    <col width="9.125" customWidth="1" style="27" min="14339" max="14581"/>
+    <col width="7" customWidth="1" style="27" min="14582" max="14582"/>
+    <col width="14.75" customWidth="1" style="27" min="14583" max="14583"/>
+    <col width="13.375" customWidth="1" style="27" min="14584" max="14584"/>
+    <col width="9.875" customWidth="1" style="27" min="14585" max="14588"/>
+    <col width="10.75" customWidth="1" style="27" min="14589" max="14589"/>
+    <col width="9.875" customWidth="1" style="27" min="14590" max="14591"/>
+    <col width="14.875" customWidth="1" style="27" min="14592" max="14592"/>
+    <col width="23.875" customWidth="1" style="27" min="14593" max="14593"/>
+    <col width="13.25" customWidth="1" style="27" min="14594" max="14594"/>
+    <col width="9.125" customWidth="1" style="27" min="14595" max="14837"/>
+    <col width="7" customWidth="1" style="27" min="14838" max="14838"/>
+    <col width="14.75" customWidth="1" style="27" min="14839" max="14839"/>
+    <col width="13.375" customWidth="1" style="27" min="14840" max="14840"/>
+    <col width="9.875" customWidth="1" style="27" min="14841" max="14844"/>
+    <col width="10.75" customWidth="1" style="27" min="14845" max="14845"/>
+    <col width="9.875" customWidth="1" style="27" min="14846" max="14847"/>
+    <col width="14.875" customWidth="1" style="27" min="14848" max="14848"/>
+    <col width="23.875" customWidth="1" style="27" min="14849" max="14849"/>
+    <col width="13.25" customWidth="1" style="27" min="14850" max="14850"/>
+    <col width="9.125" customWidth="1" style="27" min="14851" max="15093"/>
+    <col width="7" customWidth="1" style="27" min="15094" max="15094"/>
+    <col width="14.75" customWidth="1" style="27" min="15095" max="15095"/>
+    <col width="13.375" customWidth="1" style="27" min="15096" max="15096"/>
+    <col width="9.875" customWidth="1" style="27" min="15097" max="15100"/>
+    <col width="10.75" customWidth="1" style="27" min="15101" max="15101"/>
+    <col width="9.875" customWidth="1" style="27" min="15102" max="15103"/>
+    <col width="14.875" customWidth="1" style="27" min="15104" max="15104"/>
+    <col width="23.875" customWidth="1" style="27" min="15105" max="15105"/>
+    <col width="13.25" customWidth="1" style="27" min="15106" max="15106"/>
+    <col width="9.125" customWidth="1" style="27" min="15107" max="15349"/>
+    <col width="7" customWidth="1" style="27" min="15350" max="15350"/>
+    <col width="14.75" customWidth="1" style="27" min="15351" max="15351"/>
+    <col width="13.375" customWidth="1" style="27" min="15352" max="15352"/>
+    <col width="9.875" customWidth="1" style="27" min="15353" max="15356"/>
+    <col width="10.75" customWidth="1" style="27" min="15357" max="15357"/>
+    <col width="9.875" customWidth="1" style="27" min="15358" max="15359"/>
+    <col width="14.875" customWidth="1" style="27" min="15360" max="15360"/>
+    <col width="23.875" customWidth="1" style="27" min="15361" max="15361"/>
+    <col width="13.25" customWidth="1" style="27" min="15362" max="15362"/>
+    <col width="9.125" customWidth="1" style="27" min="15363" max="15605"/>
+    <col width="7" customWidth="1" style="27" min="15606" max="15606"/>
+    <col width="14.75" customWidth="1" style="27" min="15607" max="15607"/>
+    <col width="13.375" customWidth="1" style="27" min="15608" max="15608"/>
+    <col width="9.875" customWidth="1" style="27" min="15609" max="15612"/>
+    <col width="10.75" customWidth="1" style="27" min="15613" max="15613"/>
+    <col width="9.875" customWidth="1" style="27" min="15614" max="15615"/>
+    <col width="14.875" customWidth="1" style="27" min="15616" max="15616"/>
+    <col width="23.875" customWidth="1" style="27" min="15617" max="15617"/>
+    <col width="13.25" customWidth="1" style="27" min="15618" max="15618"/>
+    <col width="9.125" customWidth="1" style="27" min="15619" max="15861"/>
+    <col width="7" customWidth="1" style="27" min="15862" max="15862"/>
+    <col width="14.75" customWidth="1" style="27" min="15863" max="15863"/>
+    <col width="13.375" customWidth="1" style="27" min="15864" max="15864"/>
+    <col width="9.875" customWidth="1" style="27" min="15865" max="15868"/>
+    <col width="10.75" customWidth="1" style="27" min="15869" max="15869"/>
+    <col width="9.875" customWidth="1" style="27" min="15870" max="15871"/>
+    <col width="14.875" customWidth="1" style="27" min="15872" max="15872"/>
+    <col width="23.875" customWidth="1" style="27" min="15873" max="15873"/>
+    <col width="13.25" customWidth="1" style="27" min="15874" max="15874"/>
+    <col width="9.125" customWidth="1" style="27" min="15875" max="16117"/>
+    <col width="7" customWidth="1" style="27" min="16118" max="16118"/>
+    <col width="14.75" customWidth="1" style="27" min="16119" max="16119"/>
+    <col width="13.375" customWidth="1" style="27" min="16120" max="16120"/>
+    <col width="9.875" customWidth="1" style="27" min="16121" max="16124"/>
+    <col width="10.75" customWidth="1" style="27" min="16125" max="16125"/>
+    <col width="9.875" customWidth="1" style="27" min="16126" max="16127"/>
+    <col width="14.875" customWidth="1" style="27" min="16128" max="16128"/>
+    <col width="23.875" customWidth="1" style="27" min="16129" max="16129"/>
+    <col width="13.25" customWidth="1" style="27" min="16130" max="16130"/>
+    <col width="9.125" customWidth="1" style="27" min="16131" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>ใบตรวจสอบเครื่อง CNC</t>
+        </is>
+      </c>
+      <c r="AA1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="25.5" customFormat="1" customHeight="1" s="41">
+      <c r="AA2" s="43" t="inlineStr">
+        <is>
+          <t>Machine No. : 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="41">
+      <c r="A3" s="7" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
+      <c r="M3" s="16" t="n"/>
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="16" t="n"/>
+      <c r="W3" s="16" t="n"/>
+      <c r="X3" s="16" t="n"/>
+      <c r="Y3" s="16" t="n"/>
+      <c r="Z3" s="16" t="n"/>
+      <c r="AA3" s="16" t="n"/>
+      <c r="AB3" s="16" t="n"/>
+      <c r="AC3" s="16" t="n"/>
+      <c r="AD3" s="16" t="n"/>
+      <c r="AE3" s="16" t="n"/>
+      <c r="AF3" s="16" t="n"/>
+      <c r="AG3" s="16" t="n"/>
+    </row>
+    <row r="4" ht="18" customFormat="1" customHeight="1" s="1">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>การตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="C4" s="35" t="inlineStr">
+        <is>
+          <t>ประจำเดือน  ………………………………..</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="36" t="n"/>
+      <c r="J4" s="36" t="n"/>
+      <c r="K4" s="36" t="n"/>
+      <c r="L4" s="36" t="n"/>
+      <c r="M4" s="36" t="n"/>
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="36" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="36" t="n"/>
+      <c r="S4" s="36" t="n"/>
+      <c r="T4" s="36" t="n"/>
+      <c r="U4" s="36" t="n"/>
+      <c r="V4" s="36" t="n"/>
+      <c r="W4" s="36" t="n"/>
+      <c r="X4" s="36" t="n"/>
+      <c r="Y4" s="36" t="n"/>
+      <c r="Z4" s="36" t="n"/>
+      <c r="AA4" s="36" t="n"/>
+      <c r="AB4" s="36" t="n"/>
+      <c r="AC4" s="36" t="n"/>
+      <c r="AD4" s="36" t="n"/>
+      <c r="AE4" s="36" t="n"/>
+      <c r="AF4" s="36" t="n"/>
+      <c r="AG4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="39" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="4" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Worm up เครื่องจักร 15 นาที ทุกครั้งที่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+      <c r="K6" s="22" t="n"/>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="22" t="n"/>
+      <c r="N6" s="22" t="n"/>
+      <c r="O6" s="22" t="n"/>
+      <c r="P6" s="22" t="n"/>
+      <c r="Q6" s="22" t="n"/>
+      <c r="R6" s="22" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="22" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="23" t="n"/>
+      <c r="Z6" s="22" t="n"/>
+      <c r="AA6" s="23" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="22" t="n"/>
+      <c r="AD6" s="22" t="n"/>
+      <c r="AE6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>เช็คระดับนำมันที่ Pump Hydraulic ทุกวัน เติมเมื่อพร่อง</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="22" t="n"/>
+      <c r="P7" s="22" t="n"/>
+      <c r="Q7" s="22" t="n"/>
+      <c r="R7" s="22" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="22" t="n"/>
+      <c r="W7" s="22" t="n"/>
+      <c r="X7" s="22" t="n"/>
+      <c r="Y7" s="23" t="n"/>
+      <c r="Z7" s="22" t="n"/>
+      <c r="AA7" s="23" t="n"/>
+      <c r="AB7" s="22" t="n"/>
+      <c r="AC7" s="22" t="n"/>
+      <c r="AD7" s="22" t="n"/>
+      <c r="AE7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>ทำความสะอาด Air filter Mesh ทุกวัน</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="22" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="N8" s="22" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="22" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="R8" s="22" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="22" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="22" t="n"/>
+      <c r="Y8" s="23" t="n"/>
+      <c r="Z8" s="22" t="n"/>
+      <c r="AA8" s="23" t="n"/>
+      <c r="AB8" s="22" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AD8" s="22" t="n"/>
+      <c r="AE8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจเช็คแรงดัน Air Control Unit ปกติเฉลี่ยที่ 0.5 Mpa</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="n"/>
+      <c r="P9" s="22" t="n"/>
+      <c r="Q9" s="22" t="n"/>
+      <c r="R9" s="22" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+      <c r="U9" s="22" t="n"/>
+      <c r="V9" s="22" t="n"/>
+      <c r="W9" s="22" t="n"/>
+      <c r="X9" s="22" t="n"/>
+      <c r="Y9" s="23" t="n"/>
+      <c r="Z9" s="22" t="n"/>
+      <c r="AA9" s="23" t="n"/>
+      <c r="AB9" s="22" t="n"/>
+      <c r="AC9" s="22" t="n"/>
+      <c r="AD9" s="22" t="n"/>
+      <c r="AE9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>เช็คน้ำมันชุด Gear ของ ATC ทุกวัน(เปลี่ยนถ่ายทุกปี)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="22" t="n"/>
+      <c r="O10" s="22" t="n"/>
+      <c r="P10" s="22" t="n"/>
+      <c r="Q10" s="22" t="n"/>
+      <c r="R10" s="22" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+      <c r="U10" s="22" t="n"/>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="22" t="n"/>
+      <c r="Y10" s="23" t="n"/>
+      <c r="Z10" s="22" t="n"/>
+      <c r="AA10" s="23" t="n"/>
+      <c r="AB10" s="22" t="n"/>
+      <c r="AC10" s="22" t="n"/>
+      <c r="AD10" s="22" t="n"/>
+      <c r="AE10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>อัดจารบี Ballscrew และ Linear Guideทุก 1ครั้งต่อเดือน</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="R11" s="22" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="22" t="n"/>
+      <c r="Y11" s="23" t="n"/>
+      <c r="Z11" s="22" t="n"/>
+      <c r="AA11" s="23" t="n"/>
+      <c r="AB11" s="22" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AD11" s="22" t="n"/>
+      <c r="AE11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG11" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบการเคลื่อนที่ของแกนทุกแกน (X,Y,Z)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="22" t="n"/>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="22" t="n"/>
+      <c r="Y12" s="23" t="n"/>
+      <c r="Z12" s="22" t="n"/>
+      <c r="AA12" s="23" t="n"/>
+      <c r="AB12" s="22" t="n"/>
+      <c r="AC12" s="22" t="n"/>
+      <c r="AD12" s="22" t="n"/>
+      <c r="AE12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสภาพของน้ำ Coolant ถ่ายรูปค่าที่วัดได้ส่งเข้าระบบ</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="22" t="n"/>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="22" t="n"/>
+      <c r="N13" s="22" t="n"/>
+      <c r="O13" s="22" t="n"/>
+      <c r="P13" s="22" t="n"/>
+      <c r="Q13" s="22" t="n"/>
+      <c r="R13" s="22" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="22" t="n"/>
+      <c r="U13" s="22" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
+      <c r="Y13" s="23" t="n"/>
+      <c r="Z13" s="22" t="n"/>
+      <c r="AA13" s="23" t="n"/>
+      <c r="AB13" s="22" t="n"/>
+      <c r="AC13" s="22" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Coolant pump</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="R14" s="22" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="22" t="n"/>
+      <c r="Y14" s="23" t="n"/>
+      <c r="Z14" s="22" t="n"/>
+      <c r="AA14" s="23" t="n"/>
+      <c r="AB14" s="22" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Unclamp และการเปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="22" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="22" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="22" t="n"/>
+      <c r="U15" s="22" t="n"/>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="22" t="n"/>
+      <c r="X15" s="22" t="n"/>
+      <c r="Y15" s="23" t="n"/>
+      <c r="Z15" s="22" t="n"/>
+      <c r="AA15" s="23" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Spindle</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n"/>
+      <c r="M16" s="22" t="n"/>
+      <c r="N16" s="22" t="n"/>
+      <c r="O16" s="22" t="n"/>
+      <c r="P16" s="22" t="n"/>
+      <c r="Q16" s="22" t="n"/>
+      <c r="R16" s="22" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="22" t="n"/>
+      <c r="U16" s="22" t="n"/>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="22" t="n"/>
+      <c r="X16" s="22" t="n"/>
+      <c r="Y16" s="23" t="n"/>
+      <c r="Z16" s="22" t="n"/>
+      <c r="AA16" s="23" t="n"/>
+      <c r="AB16" s="22" t="n"/>
+      <c r="AC16" s="22" t="n"/>
+      <c r="AD16" s="22" t="n"/>
+      <c r="AE16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>การทำงานของ Arm เปลี่ยน Tool</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="22" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="R17" s="22" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="n"/>
+      <c r="U17" s="22" t="n"/>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="22" t="n"/>
+      <c r="Y17" s="23" t="n"/>
+      <c r="Z17" s="22" t="n"/>
+      <c r="AA17" s="23" t="n"/>
+      <c r="AB17" s="22" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบระดับของน้ำ Coolant เติมเมื่ออยู่ระดับที่ต่ำ</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="22" t="n"/>
+      <c r="P18" s="22" t="n"/>
+      <c r="Q18" s="22" t="n"/>
+      <c r="R18" s="22" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+      <c r="U18" s="22" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="22" t="n"/>
+      <c r="X18" s="22" t="n"/>
+      <c r="Y18" s="23" t="n"/>
+      <c r="Z18" s="22" t="n"/>
+      <c r="AA18" s="23" t="n"/>
+      <c r="AB18" s="22" t="n"/>
+      <c r="AC18" s="22" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ความสะอาดทั่วไปของเครื่องจักรโดยรวม</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
+      <c r="L19" s="22" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
+      <c r="Q19" s="22" t="n"/>
+      <c r="R19" s="22" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+      <c r="U19" s="22" t="n"/>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="22" t="n"/>
+      <c r="X19" s="22" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="22" t="n"/>
+      <c r="AA19" s="23" t="n"/>
+      <c r="AB19" s="22" t="n"/>
+      <c r="AC19" s="22" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบความพร้อมสภาพโดยรวม(ฟังด้วยหู ดูด้วยตา)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="22" t="n"/>
+      <c r="M20" s="22" t="n"/>
+      <c r="N20" s="22" t="n"/>
+      <c r="O20" s="22" t="n"/>
+      <c r="P20" s="22" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="22" t="n"/>
+      <c r="X20" s="22" t="n"/>
+      <c r="Y20" s="23" t="n"/>
+      <c r="Z20" s="22" t="n"/>
+      <c r="AA20" s="23" t="n"/>
+      <c r="AB20" s="22" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AD20" s="22" t="n"/>
+      <c r="AE20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสายไฮโดรลิกส์ และสายลม</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="22" t="n"/>
+      <c r="L21" s="22" t="n"/>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="22" t="n"/>
+      <c r="O21" s="22" t="n"/>
+      <c r="P21" s="22" t="n"/>
+      <c r="Q21" s="22" t="n"/>
+      <c r="R21" s="22" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
+      <c r="Y21" s="23" t="n"/>
+      <c r="Z21" s="22" t="n"/>
+      <c r="AA21" s="23" t="n"/>
+      <c r="AB21" s="22" t="n"/>
+      <c r="AC21" s="22" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AG21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n"/>
+      <c r="R22" s="28" t="n"/>
+      <c r="S22" s="28" t="n"/>
+      <c r="T22" s="28" t="n"/>
+      <c r="U22" s="28" t="n"/>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28" t="n"/>
+      <c r="X22" s="33" t="n"/>
+      <c r="Y22" s="33" t="n"/>
+      <c r="Z22" s="28" t="n"/>
+      <c r="AA22" s="33" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="28" t="n"/>
+      <c r="AD22" s="28" t="n"/>
+      <c r="AE22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AF22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+      <c r="AG22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="29" t="n"/>
+      <c r="N23" s="29" t="n"/>
+      <c r="O23" s="29" t="n"/>
+      <c r="P23" s="29" t="n"/>
+      <c r="Q23" s="29" t="n"/>
+      <c r="R23" s="29" t="n"/>
+      <c r="S23" s="29" t="n"/>
+      <c r="T23" s="29" t="n"/>
+      <c r="U23" s="29" t="n"/>
+      <c r="V23" s="29" t="n"/>
+      <c r="W23" s="29" t="n"/>
+      <c r="X23" s="29" t="n"/>
+      <c r="Y23" s="29" t="n"/>
+      <c r="Z23" s="29" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="29" t="n"/>
+      <c r="AC23" s="29" t="n"/>
+      <c r="AD23" s="29" t="n"/>
+      <c r="AE23" s="29" t="n"/>
+      <c r="AF23" s="29" t="n"/>
+      <c r="AG23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="30" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="30" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
+      <c r="M24" s="30" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="30" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="30" t="n"/>
+      <c r="U24" s="30" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="30" t="n"/>
+      <c r="X24" s="44" t="n"/>
+      <c r="Y24" s="44" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="44" t="n"/>
+      <c r="AB24" s="30" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="30" t="n"/>
+      <c r="AF24" s="30" t="n"/>
+      <c r="AG24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="29" t="n"/>
+      <c r="N25" s="29" t="n"/>
+      <c r="O25" s="29" t="n"/>
+      <c r="P25" s="29" t="n"/>
+      <c r="Q25" s="29" t="n"/>
+      <c r="R25" s="29" t="n"/>
+      <c r="S25" s="29" t="n"/>
+      <c r="T25" s="29" t="n"/>
+      <c r="U25" s="29" t="n"/>
+      <c r="V25" s="29" t="n"/>
+      <c r="W25" s="29" t="n"/>
+      <c r="X25" s="29" t="n"/>
+      <c r="Y25" s="29" t="n"/>
+      <c r="Z25" s="29" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="29" t="n"/>
+      <c r="AC25" s="29" t="n"/>
+      <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
+      <c r="AG25" s="29" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>บันทึกเพิ่มเติม</t>
+        </is>
+      </c>
+      <c r="Y27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="173.25" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="AA29" s="19" t="n"/>
+      <c r="AB29" s="31" t="n"/>
+      <c r="AC29" s="32" t="n"/>
+      <c r="AD29" s="32" t="n"/>
+      <c r="AE29" s="32" t="n"/>
+      <c r="AF29" s="32" t="n"/>
+      <c r="AG29" s="32" t="n"/>
+    </row>
+    <row r="30" ht="29.25" customHeight="1">
+      <c r="AB30" s="26" t="inlineStr">
+        <is>
+          <t>ผู้จัดการแผนกซ่อมบำรุง</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="7.5" customHeight="1">
+      <c r="D31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="C32" s="18" t="n"/>
+      <c r="AG32" s="20" t="inlineStr">
+        <is>
+          <t>FM-MN-07 Rev.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="71">
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="AG22:AG23"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="AF24:AF25"/>
+    <mergeCell ref="AE22:AE23"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="AC22:AC23"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="AF22:AF23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="AG24:AG25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AB30:AG30"/>
+    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AD22:AD23"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="AB29:AG29"/>
+    <mergeCell ref="A1:Z2"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.16" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="77" blackAndWhite="1" horizontalDpi="4294967293" verticalDpi="4294967293"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -1804,49 +1804,37 @@
           <t>Worm up เครื่องจักร 15 นาที ทุกครั้งที่ใช้งาน</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="22" t="n"/>
-      <c r="I6" s="22" t="n"/>
-      <c r="J6" s="22" t="n"/>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="22" t="n"/>
-      <c r="M6" s="22" t="n"/>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n"/>
-      <c r="P6" s="22" t="n"/>
-      <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="22" t="n"/>
-      <c r="T6" s="22" t="n"/>
-      <c r="U6" s="22" t="n"/>
-      <c r="V6" s="22" t="n"/>
-      <c r="W6" s="22" t="n"/>
-      <c r="X6" s="22" t="n"/>
-      <c r="Y6" s="23" t="n"/>
-      <c r="Z6" s="22" t="n"/>
-      <c r="AA6" s="23" t="n"/>
-      <c r="AB6" s="22" t="n"/>
-      <c r="AC6" s="22" t="n"/>
-      <c r="AD6" s="22" t="n"/>
-      <c r="AE6" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
+      <c r="J6" s="22" t="inlineStr"/>
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="22" t="inlineStr"/>
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="22" t="inlineStr"/>
+      <c r="P6" s="22" t="inlineStr"/>
+      <c r="Q6" s="22" t="inlineStr"/>
+      <c r="R6" s="22" t="inlineStr"/>
+      <c r="S6" s="22" t="inlineStr"/>
+      <c r="T6" s="22" t="inlineStr"/>
+      <c r="U6" s="22" t="inlineStr"/>
+      <c r="V6" s="22" t="inlineStr"/>
+      <c r="W6" s="22" t="inlineStr"/>
+      <c r="X6" s="22" t="inlineStr"/>
+      <c r="Y6" s="23" t="inlineStr"/>
+      <c r="Z6" s="22" t="inlineStr"/>
+      <c r="AA6" s="23" t="inlineStr"/>
+      <c r="AB6" s="22" t="inlineStr"/>
+      <c r="AC6" s="22" t="inlineStr"/>
+      <c r="AD6" s="22" t="inlineStr"/>
+      <c r="AE6" s="23" t="inlineStr"/>
+      <c r="AF6" s="23" t="inlineStr"/>
+      <c r="AG6" s="23" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="14" t="n">
@@ -1857,49 +1845,37 @@
           <t>เช็คระดับนำมันที่ Pump Hydraulic ทุกวัน เติมเมื่อพร่อง</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="23" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="23" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr"/>
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr"/>
+      <c r="K7" s="22" t="inlineStr"/>
+      <c r="L7" s="22" t="inlineStr"/>
+      <c r="M7" s="22" t="inlineStr"/>
+      <c r="N7" s="22" t="inlineStr"/>
+      <c r="O7" s="22" t="inlineStr"/>
+      <c r="P7" s="22" t="inlineStr"/>
+      <c r="Q7" s="22" t="inlineStr"/>
+      <c r="R7" s="22" t="inlineStr"/>
+      <c r="S7" s="22" t="inlineStr"/>
+      <c r="T7" s="22" t="inlineStr"/>
+      <c r="U7" s="22" t="inlineStr"/>
+      <c r="V7" s="22" t="inlineStr"/>
+      <c r="W7" s="22" t="inlineStr"/>
+      <c r="X7" s="22" t="inlineStr"/>
+      <c r="Y7" s="23" t="inlineStr"/>
+      <c r="Z7" s="22" t="inlineStr"/>
+      <c r="AA7" s="23" t="inlineStr"/>
+      <c r="AB7" s="22" t="inlineStr"/>
+      <c r="AC7" s="22" t="inlineStr"/>
+      <c r="AD7" s="22" t="inlineStr"/>
+      <c r="AE7" s="23" t="inlineStr"/>
+      <c r="AF7" s="23" t="inlineStr"/>
+      <c r="AG7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="14" t="n">
@@ -1910,49 +1886,37 @@
           <t>ทำความสะอาด Air filter Mesh ทุกวัน</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="V8" s="22" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="23" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="23" t="n"/>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C8" s="22" t="inlineStr"/>
+      <c r="D8" s="22" t="inlineStr"/>
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="22" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr"/>
+      <c r="J8" s="22" t="inlineStr"/>
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="22" t="inlineStr"/>
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="22" t="inlineStr"/>
+      <c r="P8" s="22" t="inlineStr"/>
+      <c r="Q8" s="22" t="inlineStr"/>
+      <c r="R8" s="22" t="inlineStr"/>
+      <c r="S8" s="22" t="inlineStr"/>
+      <c r="T8" s="22" t="inlineStr"/>
+      <c r="U8" s="22" t="inlineStr"/>
+      <c r="V8" s="22" t="inlineStr"/>
+      <c r="W8" s="22" t="inlineStr"/>
+      <c r="X8" s="22" t="inlineStr"/>
+      <c r="Y8" s="23" t="inlineStr"/>
+      <c r="Z8" s="22" t="inlineStr"/>
+      <c r="AA8" s="23" t="inlineStr"/>
+      <c r="AB8" s="22" t="inlineStr"/>
+      <c r="AC8" s="22" t="inlineStr"/>
+      <c r="AD8" s="22" t="inlineStr"/>
+      <c r="AE8" s="23" t="inlineStr"/>
+      <c r="AF8" s="23" t="inlineStr"/>
+      <c r="AG8" s="23" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="14" t="n">
@@ -1963,49 +1927,37 @@
           <t>ตรวจเช็คแรงดัน Air Control Unit ปกติเฉลี่ยที่ 0.5 Mpa</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-      <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="22" t="n"/>
-      <c r="S9" s="22" t="n"/>
-      <c r="T9" s="22" t="n"/>
-      <c r="U9" s="22" t="n"/>
-      <c r="V9" s="22" t="n"/>
-      <c r="W9" s="22" t="n"/>
-      <c r="X9" s="22" t="n"/>
-      <c r="Y9" s="23" t="n"/>
-      <c r="Z9" s="22" t="n"/>
-      <c r="AA9" s="23" t="n"/>
-      <c r="AB9" s="22" t="n"/>
-      <c r="AC9" s="22" t="n"/>
-      <c r="AD9" s="22" t="n"/>
-      <c r="AE9" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="22" t="inlineStr"/>
+      <c r="D9" s="22" t="inlineStr"/>
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr"/>
+      <c r="J9" s="22" t="inlineStr"/>
+      <c r="K9" s="22" t="inlineStr"/>
+      <c r="L9" s="22" t="inlineStr"/>
+      <c r="M9" s="22" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr"/>
+      <c r="O9" s="22" t="inlineStr"/>
+      <c r="P9" s="22" t="inlineStr"/>
+      <c r="Q9" s="22" t="inlineStr"/>
+      <c r="R9" s="22" t="inlineStr"/>
+      <c r="S9" s="22" t="inlineStr"/>
+      <c r="T9" s="22" t="inlineStr"/>
+      <c r="U9" s="22" t="inlineStr"/>
+      <c r="V9" s="22" t="inlineStr"/>
+      <c r="W9" s="22" t="inlineStr"/>
+      <c r="X9" s="22" t="inlineStr"/>
+      <c r="Y9" s="23" t="inlineStr"/>
+      <c r="Z9" s="22" t="inlineStr"/>
+      <c r="AA9" s="23" t="inlineStr"/>
+      <c r="AB9" s="22" t="inlineStr"/>
+      <c r="AC9" s="22" t="inlineStr"/>
+      <c r="AD9" s="22" t="inlineStr"/>
+      <c r="AE9" s="23" t="inlineStr"/>
+      <c r="AF9" s="23" t="inlineStr"/>
+      <c r="AG9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="n">
@@ -2016,49 +1968,37 @@
           <t>เช็คน้ำมันชุด Gear ของ ATC ทุกวัน(เปลี่ยนถ่ายทุกปี)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n"/>
-      <c r="T10" s="22" t="n"/>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="23" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="23" t="n"/>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="22" t="inlineStr"/>
+      <c r="D10" s="22" t="inlineStr"/>
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr"/>
+      <c r="J10" s="22" t="inlineStr"/>
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="22" t="inlineStr"/>
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="22" t="inlineStr"/>
+      <c r="P10" s="22" t="inlineStr"/>
+      <c r="Q10" s="22" t="inlineStr"/>
+      <c r="R10" s="22" t="inlineStr"/>
+      <c r="S10" s="22" t="inlineStr"/>
+      <c r="T10" s="22" t="inlineStr"/>
+      <c r="U10" s="22" t="inlineStr"/>
+      <c r="V10" s="22" t="inlineStr"/>
+      <c r="W10" s="22" t="inlineStr"/>
+      <c r="X10" s="22" t="inlineStr"/>
+      <c r="Y10" s="23" t="inlineStr"/>
+      <c r="Z10" s="22" t="inlineStr"/>
+      <c r="AA10" s="23" t="inlineStr"/>
+      <c r="AB10" s="22" t="inlineStr"/>
+      <c r="AC10" s="22" t="inlineStr"/>
+      <c r="AD10" s="22" t="inlineStr"/>
+      <c r="AE10" s="23" t="inlineStr"/>
+      <c r="AF10" s="23" t="inlineStr"/>
+      <c r="AG10" s="23" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="14" t="n">
@@ -2069,49 +2009,37 @@
           <t>อัดจารบี Ballscrew และ Linear Guideทุก 1ครั้งต่อเดือน</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="22" t="n"/>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="22" t="n"/>
-      <c r="M11" s="22" t="n"/>
-      <c r="N11" s="22" t="n"/>
-      <c r="O11" s="22" t="n"/>
-      <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="22" t="n"/>
-      <c r="R11" s="22" t="n"/>
-      <c r="S11" s="22" t="n"/>
-      <c r="T11" s="22" t="n"/>
-      <c r="U11" s="22" t="n"/>
-      <c r="V11" s="22" t="n"/>
-      <c r="W11" s="22" t="n"/>
-      <c r="X11" s="22" t="n"/>
-      <c r="Y11" s="23" t="n"/>
-      <c r="Z11" s="22" t="n"/>
-      <c r="AA11" s="23" t="n"/>
-      <c r="AB11" s="22" t="n"/>
-      <c r="AC11" s="22" t="n"/>
-      <c r="AD11" s="22" t="n"/>
-      <c r="AE11" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF11" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG11" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C11" s="22" t="inlineStr"/>
+      <c r="D11" s="22" t="inlineStr"/>
+      <c r="E11" s="22" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr"/>
+      <c r="H11" s="22" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr"/>
+      <c r="J11" s="22" t="inlineStr"/>
+      <c r="K11" s="22" t="inlineStr"/>
+      <c r="L11" s="22" t="inlineStr"/>
+      <c r="M11" s="22" t="inlineStr"/>
+      <c r="N11" s="22" t="inlineStr"/>
+      <c r="O11" s="22" t="inlineStr"/>
+      <c r="P11" s="22" t="inlineStr"/>
+      <c r="Q11" s="22" t="inlineStr"/>
+      <c r="R11" s="22" t="inlineStr"/>
+      <c r="S11" s="22" t="inlineStr"/>
+      <c r="T11" s="22" t="inlineStr"/>
+      <c r="U11" s="22" t="inlineStr"/>
+      <c r="V11" s="22" t="inlineStr"/>
+      <c r="W11" s="22" t="inlineStr"/>
+      <c r="X11" s="22" t="inlineStr"/>
+      <c r="Y11" s="23" t="inlineStr"/>
+      <c r="Z11" s="22" t="inlineStr"/>
+      <c r="AA11" s="23" t="inlineStr"/>
+      <c r="AB11" s="22" t="inlineStr"/>
+      <c r="AC11" s="22" t="inlineStr"/>
+      <c r="AD11" s="22" t="inlineStr"/>
+      <c r="AE11" s="23" t="inlineStr"/>
+      <c r="AF11" s="23" t="inlineStr"/>
+      <c r="AG11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="14" t="n">
@@ -2122,49 +2050,37 @@
           <t>ตรวจสอบการเคลื่อนที่ของแกนทุกแกน (X,Y,Z)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="22" t="n"/>
-      <c r="M12" s="22" t="n"/>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="22" t="n"/>
-      <c r="P12" s="22" t="n"/>
-      <c r="Q12" s="22" t="n"/>
-      <c r="R12" s="22" t="n"/>
-      <c r="S12" s="22" t="n"/>
-      <c r="T12" s="22" t="n"/>
-      <c r="U12" s="22" t="n"/>
-      <c r="V12" s="22" t="n"/>
-      <c r="W12" s="22" t="n"/>
-      <c r="X12" s="22" t="n"/>
-      <c r="Y12" s="23" t="n"/>
-      <c r="Z12" s="22" t="n"/>
-      <c r="AA12" s="23" t="n"/>
-      <c r="AB12" s="22" t="n"/>
-      <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="22" t="n"/>
-      <c r="AE12" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG12" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C12" s="22" t="inlineStr"/>
+      <c r="D12" s="22" t="inlineStr"/>
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr"/>
+      <c r="I12" s="22" t="inlineStr"/>
+      <c r="J12" s="22" t="inlineStr"/>
+      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="22" t="inlineStr"/>
+      <c r="M12" s="22" t="inlineStr"/>
+      <c r="N12" s="22" t="inlineStr"/>
+      <c r="O12" s="22" t="inlineStr"/>
+      <c r="P12" s="22" t="inlineStr"/>
+      <c r="Q12" s="22" t="inlineStr"/>
+      <c r="R12" s="22" t="inlineStr"/>
+      <c r="S12" s="22" t="inlineStr"/>
+      <c r="T12" s="22" t="inlineStr"/>
+      <c r="U12" s="22" t="inlineStr"/>
+      <c r="V12" s="22" t="inlineStr"/>
+      <c r="W12" s="22" t="inlineStr"/>
+      <c r="X12" s="22" t="inlineStr"/>
+      <c r="Y12" s="23" t="inlineStr"/>
+      <c r="Z12" s="22" t="inlineStr"/>
+      <c r="AA12" s="23" t="inlineStr"/>
+      <c r="AB12" s="22" t="inlineStr"/>
+      <c r="AC12" s="22" t="inlineStr"/>
+      <c r="AD12" s="22" t="inlineStr"/>
+      <c r="AE12" s="23" t="inlineStr"/>
+      <c r="AF12" s="23" t="inlineStr"/>
+      <c r="AG12" s="23" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="14" t="n">
@@ -2175,49 +2091,37 @@
           <t>ตรวจสอบสภาพของน้ำ Coolant ถ่ายรูปค่าที่วัดได้ส่งเข้าระบบ</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="22" t="n"/>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="22" t="n"/>
-      <c r="M13" s="22" t="n"/>
-      <c r="N13" s="22" t="n"/>
-      <c r="O13" s="22" t="n"/>
-      <c r="P13" s="22" t="n"/>
-      <c r="Q13" s="22" t="n"/>
-      <c r="R13" s="22" t="n"/>
-      <c r="S13" s="22" t="n"/>
-      <c r="T13" s="22" t="n"/>
-      <c r="U13" s="22" t="n"/>
-      <c r="V13" s="22" t="n"/>
-      <c r="W13" s="22" t="n"/>
-      <c r="X13" s="22" t="n"/>
-      <c r="Y13" s="23" t="n"/>
-      <c r="Z13" s="22" t="n"/>
-      <c r="AA13" s="23" t="n"/>
-      <c r="AB13" s="22" t="n"/>
-      <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="22" t="n"/>
-      <c r="AE13" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF13" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG13" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C13" s="22" t="inlineStr"/>
+      <c r="D13" s="22" t="inlineStr"/>
+      <c r="E13" s="22" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr"/>
+      <c r="J13" s="22" t="inlineStr"/>
+      <c r="K13" s="22" t="inlineStr"/>
+      <c r="L13" s="22" t="inlineStr"/>
+      <c r="M13" s="22" t="inlineStr"/>
+      <c r="N13" s="22" t="inlineStr"/>
+      <c r="O13" s="22" t="inlineStr"/>
+      <c r="P13" s="22" t="inlineStr"/>
+      <c r="Q13" s="22" t="inlineStr"/>
+      <c r="R13" s="22" t="inlineStr"/>
+      <c r="S13" s="22" t="inlineStr"/>
+      <c r="T13" s="22" t="inlineStr"/>
+      <c r="U13" s="22" t="inlineStr"/>
+      <c r="V13" s="22" t="inlineStr"/>
+      <c r="W13" s="22" t="inlineStr"/>
+      <c r="X13" s="22" t="inlineStr"/>
+      <c r="Y13" s="23" t="inlineStr"/>
+      <c r="Z13" s="22" t="inlineStr"/>
+      <c r="AA13" s="23" t="inlineStr"/>
+      <c r="AB13" s="22" t="inlineStr"/>
+      <c r="AC13" s="22" t="inlineStr"/>
+      <c r="AD13" s="22" t="inlineStr"/>
+      <c r="AE13" s="23" t="inlineStr"/>
+      <c r="AF13" s="23" t="inlineStr"/>
+      <c r="AG13" s="23" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="14" t="n">
@@ -2228,49 +2132,37 @@
           <t>การทำงานของ Coolant pump</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="22" t="n"/>
-      <c r="L14" s="22" t="n"/>
-      <c r="M14" s="22" t="n"/>
-      <c r="N14" s="22" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="22" t="n"/>
-      <c r="Q14" s="22" t="n"/>
-      <c r="R14" s="22" t="n"/>
-      <c r="S14" s="22" t="n"/>
-      <c r="T14" s="22" t="n"/>
-      <c r="U14" s="22" t="n"/>
-      <c r="V14" s="22" t="n"/>
-      <c r="W14" s="22" t="n"/>
-      <c r="X14" s="22" t="n"/>
-      <c r="Y14" s="23" t="n"/>
-      <c r="Z14" s="22" t="n"/>
-      <c r="AA14" s="23" t="n"/>
-      <c r="AB14" s="22" t="n"/>
-      <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="22" t="n"/>
-      <c r="AE14" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF14" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG14" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C14" s="22" t="inlineStr"/>
+      <c r="D14" s="22" t="inlineStr"/>
+      <c r="E14" s="22" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr"/>
+      <c r="I14" s="22" t="inlineStr"/>
+      <c r="J14" s="22" t="inlineStr"/>
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr"/>
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="22" t="inlineStr"/>
+      <c r="O14" s="22" t="inlineStr"/>
+      <c r="P14" s="22" t="inlineStr"/>
+      <c r="Q14" s="22" t="inlineStr"/>
+      <c r="R14" s="22" t="inlineStr"/>
+      <c r="S14" s="22" t="inlineStr"/>
+      <c r="T14" s="22" t="inlineStr"/>
+      <c r="U14" s="22" t="inlineStr"/>
+      <c r="V14" s="22" t="inlineStr"/>
+      <c r="W14" s="22" t="inlineStr"/>
+      <c r="X14" s="22" t="inlineStr"/>
+      <c r="Y14" s="23" t="inlineStr"/>
+      <c r="Z14" s="22" t="inlineStr"/>
+      <c r="AA14" s="23" t="inlineStr"/>
+      <c r="AB14" s="22" t="inlineStr"/>
+      <c r="AC14" s="22" t="inlineStr"/>
+      <c r="AD14" s="22" t="inlineStr"/>
+      <c r="AE14" s="23" t="inlineStr"/>
+      <c r="AF14" s="23" t="inlineStr"/>
+      <c r="AG14" s="23" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="14" t="n">
@@ -2281,49 +2173,37 @@
           <t>การทำงานของ Unclamp และการเปลี่ยน Tool</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="22" t="n"/>
-      <c r="O15" s="22" t="n"/>
-      <c r="P15" s="22" t="n"/>
-      <c r="Q15" s="22" t="n"/>
-      <c r="R15" s="22" t="n"/>
-      <c r="S15" s="22" t="n"/>
-      <c r="T15" s="22" t="n"/>
-      <c r="U15" s="22" t="n"/>
-      <c r="V15" s="22" t="n"/>
-      <c r="W15" s="22" t="n"/>
-      <c r="X15" s="22" t="n"/>
-      <c r="Y15" s="23" t="n"/>
-      <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="23" t="n"/>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="22" t="n"/>
-      <c r="AE15" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF15" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG15" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C15" s="22" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr"/>
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr"/>
+      <c r="J15" s="22" t="inlineStr"/>
+      <c r="K15" s="22" t="inlineStr"/>
+      <c r="L15" s="22" t="inlineStr"/>
+      <c r="M15" s="22" t="inlineStr"/>
+      <c r="N15" s="22" t="inlineStr"/>
+      <c r="O15" s="22" t="inlineStr"/>
+      <c r="P15" s="22" t="inlineStr"/>
+      <c r="Q15" s="22" t="inlineStr"/>
+      <c r="R15" s="22" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr"/>
+      <c r="T15" s="22" t="inlineStr"/>
+      <c r="U15" s="22" t="inlineStr"/>
+      <c r="V15" s="22" t="inlineStr"/>
+      <c r="W15" s="22" t="inlineStr"/>
+      <c r="X15" s="22" t="inlineStr"/>
+      <c r="Y15" s="23" t="inlineStr"/>
+      <c r="Z15" s="22" t="inlineStr"/>
+      <c r="AA15" s="23" t="inlineStr"/>
+      <c r="AB15" s="22" t="inlineStr"/>
+      <c r="AC15" s="22" t="inlineStr"/>
+      <c r="AD15" s="22" t="inlineStr"/>
+      <c r="AE15" s="23" t="inlineStr"/>
+      <c r="AF15" s="23" t="inlineStr"/>
+      <c r="AG15" s="23" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="14" t="n">
@@ -2334,49 +2214,37 @@
           <t>การทำงานของ Spindle</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="22" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="22" t="n"/>
-      <c r="J16" s="22" t="n"/>
-      <c r="K16" s="22" t="n"/>
-      <c r="L16" s="22" t="n"/>
-      <c r="M16" s="22" t="n"/>
-      <c r="N16" s="22" t="n"/>
-      <c r="O16" s="22" t="n"/>
-      <c r="P16" s="22" t="n"/>
-      <c r="Q16" s="22" t="n"/>
-      <c r="R16" s="22" t="n"/>
-      <c r="S16" s="22" t="n"/>
-      <c r="T16" s="22" t="n"/>
-      <c r="U16" s="22" t="n"/>
-      <c r="V16" s="22" t="n"/>
-      <c r="W16" s="22" t="n"/>
-      <c r="X16" s="22" t="n"/>
-      <c r="Y16" s="23" t="n"/>
-      <c r="Z16" s="22" t="n"/>
-      <c r="AA16" s="23" t="n"/>
-      <c r="AB16" s="22" t="n"/>
-      <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="22" t="n"/>
-      <c r="AE16" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF16" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG16" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C16" s="22" t="inlineStr"/>
+      <c r="D16" s="22" t="inlineStr"/>
+      <c r="E16" s="22" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr"/>
+      <c r="I16" s="22" t="inlineStr"/>
+      <c r="J16" s="22" t="inlineStr"/>
+      <c r="K16" s="22" t="inlineStr"/>
+      <c r="L16" s="22" t="inlineStr"/>
+      <c r="M16" s="22" t="inlineStr"/>
+      <c r="N16" s="22" t="inlineStr"/>
+      <c r="O16" s="22" t="inlineStr"/>
+      <c r="P16" s="22" t="inlineStr"/>
+      <c r="Q16" s="22" t="inlineStr"/>
+      <c r="R16" s="22" t="inlineStr"/>
+      <c r="S16" s="22" t="inlineStr"/>
+      <c r="T16" s="22" t="inlineStr"/>
+      <c r="U16" s="22" t="inlineStr"/>
+      <c r="V16" s="22" t="inlineStr"/>
+      <c r="W16" s="22" t="inlineStr"/>
+      <c r="X16" s="22" t="inlineStr"/>
+      <c r="Y16" s="23" t="inlineStr"/>
+      <c r="Z16" s="22" t="inlineStr"/>
+      <c r="AA16" s="23" t="inlineStr"/>
+      <c r="AB16" s="22" t="inlineStr"/>
+      <c r="AC16" s="22" t="inlineStr"/>
+      <c r="AD16" s="22" t="inlineStr"/>
+      <c r="AE16" s="23" t="inlineStr"/>
+      <c r="AF16" s="23" t="inlineStr"/>
+      <c r="AG16" s="23" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="14" t="n">
@@ -2387,49 +2255,37 @@
           <t>การทำงานของ Arm เปลี่ยน Tool</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="J17" s="22" t="n"/>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="22" t="n"/>
-      <c r="M17" s="22" t="n"/>
-      <c r="N17" s="22" t="n"/>
-      <c r="O17" s="22" t="n"/>
-      <c r="P17" s="22" t="n"/>
-      <c r="Q17" s="22" t="n"/>
-      <c r="R17" s="22" t="n"/>
-      <c r="S17" s="22" t="n"/>
-      <c r="T17" s="22" t="n"/>
-      <c r="U17" s="22" t="n"/>
-      <c r="V17" s="22" t="n"/>
-      <c r="W17" s="22" t="n"/>
-      <c r="X17" s="22" t="n"/>
-      <c r="Y17" s="23" t="n"/>
-      <c r="Z17" s="22" t="n"/>
-      <c r="AA17" s="23" t="n"/>
-      <c r="AB17" s="22" t="n"/>
-      <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="22" t="n"/>
-      <c r="AE17" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AF17" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AG17" s="23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="C17" s="22" t="inlineStr"/>
+      <c r="D17" s="22" t="inlineStr"/>
+      <c r="E17" s="22" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr"/>
+      <c r="H17" s="22" t="inlineStr"/>
+      <c r="I17" s="22" t="inlineStr"/>
+      <c r="J17" s="22" t="inlineStr"/>
+      <c r="K17" s="22" t="inlineStr"/>
+      <c r="L17" s="22" t="inlineStr"/>
+      <c r="M17" s="22" t="inlineStr"/>
+      <c r="N17" s="22" t="inlineStr"/>
+      <c r="O17" s="22" t="inlineStr"/>
+      <c r="P17" s="22" t="inlineStr"/>
+      <c r="Q17" s="22" t="inlineStr"/>
+      <c r="R17" s="22" t="inlineStr"/>
+      <c r="S17" s="22" t="inlineStr"/>
+      <c r="T17" s="22" t="inlineStr"/>
+      <c r="U17" s="22" t="inlineStr"/>
+      <c r="V17" s="22" t="inlineStr"/>
+      <c r="W17" s="22" t="inlineStr"/>
+      <c r="X17" s="22" t="inlineStr"/>
+      <c r="Y17" s="23" t="inlineStr"/>
+      <c r="Z17" s="22" t="inlineStr"/>
+      <c r="AA17" s="23" t="inlineStr"/>
+      <c r="AB17" s="22" t="inlineStr"/>
+      <c r="AC17" s="22" t="inlineStr"/>
+      <c r="AD17" s="22" t="inlineStr"/>
+      <c r="AE17" s="23" t="inlineStr"/>
+      <c r="AF17" s="23" t="inlineStr"/>
+      <c r="AG17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="14" t="n">
@@ -2440,49 +2296,37 @@
           <t>ตรวจสอบระดับของน้ำ Coolant เติมเมื่ออยู่ระดับที่ต่ำ</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="22" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="22" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="23" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="23" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF18" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG18" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C18" s="22" t="inlineStr"/>
+      <c r="D18" s="22" t="inlineStr"/>
+      <c r="E18" s="22" t="inlineStr"/>
+      <c r="F18" s="22" t="inlineStr"/>
+      <c r="G18" s="22" t="inlineStr"/>
+      <c r="H18" s="22" t="inlineStr"/>
+      <c r="I18" s="22" t="inlineStr"/>
+      <c r="J18" s="22" t="inlineStr"/>
+      <c r="K18" s="22" t="inlineStr"/>
+      <c r="L18" s="22" t="inlineStr"/>
+      <c r="M18" s="22" t="inlineStr"/>
+      <c r="N18" s="22" t="inlineStr"/>
+      <c r="O18" s="22" t="inlineStr"/>
+      <c r="P18" s="22" t="inlineStr"/>
+      <c r="Q18" s="22" t="inlineStr"/>
+      <c r="R18" s="22" t="inlineStr"/>
+      <c r="S18" s="22" t="inlineStr"/>
+      <c r="T18" s="22" t="inlineStr"/>
+      <c r="U18" s="22" t="inlineStr"/>
+      <c r="V18" s="22" t="inlineStr"/>
+      <c r="W18" s="22" t="inlineStr"/>
+      <c r="X18" s="22" t="inlineStr"/>
+      <c r="Y18" s="23" t="inlineStr"/>
+      <c r="Z18" s="22" t="inlineStr"/>
+      <c r="AA18" s="23" t="inlineStr"/>
+      <c r="AB18" s="22" t="inlineStr"/>
+      <c r="AC18" s="22" t="inlineStr"/>
+      <c r="AD18" s="22" t="inlineStr"/>
+      <c r="AE18" s="23" t="inlineStr"/>
+      <c r="AF18" s="23" t="inlineStr"/>
+      <c r="AG18" s="23" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="14" t="n">
@@ -2493,49 +2337,37 @@
           <t>ความสะอาดทั่วไปของเครื่องจักรโดยรวม</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="22" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="23" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="23" t="n"/>
-      <c r="AB19" s="22" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF19" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG19" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C19" s="22" t="inlineStr"/>
+      <c r="D19" s="22" t="inlineStr"/>
+      <c r="E19" s="22" t="inlineStr"/>
+      <c r="F19" s="22" t="inlineStr"/>
+      <c r="G19" s="22" t="inlineStr"/>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="22" t="inlineStr"/>
+      <c r="J19" s="22" t="inlineStr"/>
+      <c r="K19" s="22" t="inlineStr"/>
+      <c r="L19" s="22" t="inlineStr"/>
+      <c r="M19" s="22" t="inlineStr"/>
+      <c r="N19" s="22" t="inlineStr"/>
+      <c r="O19" s="22" t="inlineStr"/>
+      <c r="P19" s="22" t="inlineStr"/>
+      <c r="Q19" s="22" t="inlineStr"/>
+      <c r="R19" s="22" t="inlineStr"/>
+      <c r="S19" s="22" t="inlineStr"/>
+      <c r="T19" s="22" t="inlineStr"/>
+      <c r="U19" s="22" t="inlineStr"/>
+      <c r="V19" s="22" t="inlineStr"/>
+      <c r="W19" s="22" t="inlineStr"/>
+      <c r="X19" s="22" t="inlineStr"/>
+      <c r="Y19" s="23" t="inlineStr"/>
+      <c r="Z19" s="22" t="inlineStr"/>
+      <c r="AA19" s="23" t="inlineStr"/>
+      <c r="AB19" s="22" t="inlineStr"/>
+      <c r="AC19" s="22" t="inlineStr"/>
+      <c r="AD19" s="22" t="inlineStr"/>
+      <c r="AE19" s="23" t="inlineStr"/>
+      <c r="AF19" s="23" t="inlineStr"/>
+      <c r="AG19" s="23" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="14" t="n">
@@ -2546,49 +2378,37 @@
           <t>ตรวจสอบความพร้อมสภาพโดยรวม(ฟังด้วยหู ดูด้วยตา)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="22" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="22" t="n"/>
-      <c r="Y20" s="23" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="23" t="n"/>
-      <c r="AB20" s="22" t="n"/>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="22" t="n"/>
-      <c r="AE20" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF20" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG20" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C20" s="22" t="inlineStr"/>
+      <c r="D20" s="22" t="inlineStr"/>
+      <c r="E20" s="22" t="inlineStr"/>
+      <c r="F20" s="22" t="inlineStr"/>
+      <c r="G20" s="22" t="inlineStr"/>
+      <c r="H20" s="22" t="inlineStr"/>
+      <c r="I20" s="22" t="inlineStr"/>
+      <c r="J20" s="22" t="inlineStr"/>
+      <c r="K20" s="22" t="inlineStr"/>
+      <c r="L20" s="22" t="inlineStr"/>
+      <c r="M20" s="22" t="inlineStr"/>
+      <c r="N20" s="22" t="inlineStr"/>
+      <c r="O20" s="22" t="inlineStr"/>
+      <c r="P20" s="22" t="inlineStr"/>
+      <c r="Q20" s="22" t="inlineStr"/>
+      <c r="R20" s="22" t="inlineStr"/>
+      <c r="S20" s="22" t="inlineStr"/>
+      <c r="T20" s="22" t="inlineStr"/>
+      <c r="U20" s="22" t="inlineStr"/>
+      <c r="V20" s="22" t="inlineStr"/>
+      <c r="W20" s="22" t="inlineStr"/>
+      <c r="X20" s="22" t="inlineStr"/>
+      <c r="Y20" s="23" t="inlineStr"/>
+      <c r="Z20" s="22" t="inlineStr"/>
+      <c r="AA20" s="23" t="inlineStr"/>
+      <c r="AB20" s="22" t="inlineStr"/>
+      <c r="AC20" s="22" t="inlineStr"/>
+      <c r="AD20" s="22" t="inlineStr"/>
+      <c r="AE20" s="23" t="inlineStr"/>
+      <c r="AF20" s="23" t="inlineStr"/>
+      <c r="AG20" s="23" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="n">
@@ -2599,96 +2419,72 @@
           <t>ตรวจสอบสายไฮโดรลิกส์ และสายลม</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="22" t="n"/>
-      <c r="P21" s="22" t="n"/>
-      <c r="Q21" s="22" t="n"/>
-      <c r="R21" s="22" t="n"/>
-      <c r="S21" s="22" t="n"/>
-      <c r="T21" s="22" t="n"/>
-      <c r="U21" s="22" t="n"/>
-      <c r="V21" s="22" t="n"/>
-      <c r="W21" s="22" t="n"/>
-      <c r="X21" s="22" t="n"/>
-      <c r="Y21" s="23" t="n"/>
-      <c r="Z21" s="22" t="n"/>
-      <c r="AA21" s="23" t="n"/>
-      <c r="AB21" s="22" t="n"/>
-      <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="22" t="n"/>
-      <c r="AE21" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF21" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG21" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C21" s="22" t="inlineStr"/>
+      <c r="D21" s="22" t="inlineStr"/>
+      <c r="E21" s="22" t="inlineStr"/>
+      <c r="F21" s="22" t="inlineStr"/>
+      <c r="G21" s="22" t="inlineStr"/>
+      <c r="H21" s="22" t="inlineStr"/>
+      <c r="I21" s="22" t="inlineStr"/>
+      <c r="J21" s="22" t="inlineStr"/>
+      <c r="K21" s="22" t="inlineStr"/>
+      <c r="L21" s="22" t="inlineStr"/>
+      <c r="M21" s="22" t="inlineStr"/>
+      <c r="N21" s="22" t="inlineStr"/>
+      <c r="O21" s="22" t="inlineStr"/>
+      <c r="P21" s="22" t="inlineStr"/>
+      <c r="Q21" s="22" t="inlineStr"/>
+      <c r="R21" s="22" t="inlineStr"/>
+      <c r="S21" s="22" t="inlineStr"/>
+      <c r="T21" s="22" t="inlineStr"/>
+      <c r="U21" s="22" t="inlineStr"/>
+      <c r="V21" s="22" t="inlineStr"/>
+      <c r="W21" s="22" t="inlineStr"/>
+      <c r="X21" s="22" t="inlineStr"/>
+      <c r="Y21" s="23" t="inlineStr"/>
+      <c r="Z21" s="22" t="inlineStr"/>
+      <c r="AA21" s="23" t="inlineStr"/>
+      <c r="AB21" s="22" t="inlineStr"/>
+      <c r="AC21" s="22" t="inlineStr"/>
+      <c r="AD21" s="22" t="inlineStr"/>
+      <c r="AE21" s="23" t="inlineStr"/>
+      <c r="AF21" s="23" t="inlineStr"/>
+      <c r="AG21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="28" t="n"/>
-      <c r="J22" s="28" t="n"/>
-      <c r="K22" s="28" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="28" t="n"/>
-      <c r="N22" s="28" t="n"/>
-      <c r="O22" s="28" t="n"/>
-      <c r="P22" s="28" t="n"/>
-      <c r="Q22" s="28" t="n"/>
-      <c r="R22" s="28" t="n"/>
-      <c r="S22" s="28" t="n"/>
-      <c r="T22" s="28" t="n"/>
-      <c r="U22" s="28" t="n"/>
-      <c r="V22" s="28" t="n"/>
-      <c r="W22" s="28" t="n"/>
-      <c r="X22" s="33" t="n"/>
-      <c r="Y22" s="33" t="n"/>
-      <c r="Z22" s="28" t="n"/>
-      <c r="AA22" s="33" t="n"/>
-      <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="28" t="n"/>
-      <c r="AD22" s="28" t="n"/>
-      <c r="AE22" s="33" t="inlineStr">
-        <is>
-          <t>พงศกร มลวัง</t>
-        </is>
-      </c>
-      <c r="AF22" s="33" t="inlineStr">
-        <is>
-          <t>พงศกร มลวัง</t>
-        </is>
-      </c>
-      <c r="AG22" s="33" t="inlineStr">
-        <is>
-          <t>พงศกร มลวัง</t>
-        </is>
-      </c>
+      <c r="C22" s="28" t="inlineStr"/>
+      <c r="D22" s="28" t="inlineStr"/>
+      <c r="E22" s="28" t="inlineStr"/>
+      <c r="F22" s="28" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
+      <c r="H22" s="28" t="inlineStr"/>
+      <c r="I22" s="28" t="inlineStr"/>
+      <c r="J22" s="28" t="inlineStr"/>
+      <c r="K22" s="28" t="inlineStr"/>
+      <c r="L22" s="28" t="inlineStr"/>
+      <c r="M22" s="28" t="inlineStr"/>
+      <c r="N22" s="28" t="inlineStr"/>
+      <c r="O22" s="28" t="inlineStr"/>
+      <c r="P22" s="28" t="inlineStr"/>
+      <c r="Q22" s="28" t="inlineStr"/>
+      <c r="R22" s="28" t="inlineStr"/>
+      <c r="S22" s="28" t="inlineStr"/>
+      <c r="T22" s="28" t="inlineStr"/>
+      <c r="U22" s="28" t="inlineStr"/>
+      <c r="V22" s="28" t="inlineStr"/>
+      <c r="W22" s="28" t="inlineStr"/>
+      <c r="X22" s="33" t="inlineStr"/>
+      <c r="Y22" s="33" t="inlineStr"/>
+      <c r="Z22" s="28" t="inlineStr"/>
+      <c r="AA22" s="33" t="inlineStr"/>
+      <c r="AB22" s="28" t="inlineStr"/>
+      <c r="AC22" s="28" t="inlineStr"/>
+      <c r="AD22" s="28" t="inlineStr"/>
+      <c r="AE22" s="33" t="inlineStr"/>
+      <c r="AF22" s="33" t="inlineStr"/>
+      <c r="AG22" s="33" t="inlineStr"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="B23" s="9" t="n"/>
@@ -2726,37 +2522,37 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="B24" s="9" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-      <c r="I24" s="30" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="30" t="n"/>
-      <c r="M24" s="30" t="n"/>
-      <c r="N24" s="30" t="n"/>
-      <c r="O24" s="30" t="n"/>
-      <c r="P24" s="30" t="n"/>
-      <c r="Q24" s="30" t="n"/>
-      <c r="R24" s="30" t="n"/>
-      <c r="S24" s="30" t="n"/>
-      <c r="T24" s="30" t="n"/>
-      <c r="U24" s="30" t="n"/>
-      <c r="V24" s="30" t="n"/>
-      <c r="W24" s="30" t="n"/>
-      <c r="X24" s="44" t="n"/>
-      <c r="Y24" s="44" t="n"/>
-      <c r="Z24" s="30" t="n"/>
-      <c r="AA24" s="44" t="n"/>
-      <c r="AB24" s="30" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="30" t="n"/>
-      <c r="AE24" s="30" t="n"/>
-      <c r="AF24" s="30" t="n"/>
-      <c r="AG24" s="30" t="n"/>
+      <c r="C24" s="30" t="inlineStr"/>
+      <c r="D24" s="30" t="inlineStr"/>
+      <c r="E24" s="30" t="inlineStr"/>
+      <c r="F24" s="30" t="inlineStr"/>
+      <c r="G24" s="30" t="inlineStr"/>
+      <c r="H24" s="30" t="inlineStr"/>
+      <c r="I24" s="30" t="inlineStr"/>
+      <c r="J24" s="30" t="inlineStr"/>
+      <c r="K24" s="30" t="inlineStr"/>
+      <c r="L24" s="30" t="inlineStr"/>
+      <c r="M24" s="30" t="inlineStr"/>
+      <c r="N24" s="30" t="inlineStr"/>
+      <c r="O24" s="30" t="inlineStr"/>
+      <c r="P24" s="30" t="inlineStr"/>
+      <c r="Q24" s="30" t="inlineStr"/>
+      <c r="R24" s="30" t="inlineStr"/>
+      <c r="S24" s="30" t="inlineStr"/>
+      <c r="T24" s="30" t="inlineStr"/>
+      <c r="U24" s="30" t="inlineStr"/>
+      <c r="V24" s="30" t="inlineStr"/>
+      <c r="W24" s="30" t="inlineStr"/>
+      <c r="X24" s="44" t="inlineStr"/>
+      <c r="Y24" s="44" t="inlineStr"/>
+      <c r="Z24" s="30" t="inlineStr"/>
+      <c r="AA24" s="44" t="inlineStr"/>
+      <c r="AB24" s="30" t="inlineStr"/>
+      <c r="AC24" s="30" t="inlineStr"/>
+      <c r="AD24" s="30" t="inlineStr"/>
+      <c r="AE24" s="30" t="inlineStr"/>
+      <c r="AF24" s="30" t="inlineStr"/>
+      <c r="AG24" s="30" t="inlineStr"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="B25" s="9" t="n"/>
@@ -2803,11 +2599,7 @@
       <c r="Y27" s="21" t="n"/>
     </row>
     <row r="28" ht="173.25" customHeight="1">
-      <c r="B28" s="46" t="inlineStr">
-        <is>
-          <t>[วันที่ 29]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 30]: น้ำใม่ไหล, มีน้ำมันไหล,  [วันที่ 31]: น้ำใม่ไหล, มีน้ำมันไหล</t>
-        </is>
-      </c>
+      <c r="B28" s="46" t="inlineStr"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="AA29" s="19" t="n"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -1809,7 +1809,11 @@
       <c r="E6" s="22" t="inlineStr"/>
       <c r="F6" s="22" t="inlineStr"/>
       <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="22" t="inlineStr"/>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
@@ -1850,7 +1854,11 @@
       <c r="E7" s="22" t="inlineStr"/>
       <c r="F7" s="22" t="inlineStr"/>
       <c r="G7" s="22" t="inlineStr"/>
-      <c r="H7" s="22" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="22" t="inlineStr"/>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
@@ -1891,7 +1899,11 @@
       <c r="E8" s="22" t="inlineStr"/>
       <c r="F8" s="22" t="inlineStr"/>
       <c r="G8" s="22" t="inlineStr"/>
-      <c r="H8" s="22" t="inlineStr"/>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="22" t="inlineStr"/>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
@@ -1932,7 +1944,11 @@
       <c r="E9" s="22" t="inlineStr"/>
       <c r="F9" s="22" t="inlineStr"/>
       <c r="G9" s="22" t="inlineStr"/>
-      <c r="H9" s="22" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="22" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
@@ -1973,7 +1989,11 @@
       <c r="E10" s="22" t="inlineStr"/>
       <c r="F10" s="22" t="inlineStr"/>
       <c r="G10" s="22" t="inlineStr"/>
-      <c r="H10" s="22" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="22" t="inlineStr"/>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
@@ -2014,7 +2034,11 @@
       <c r="E11" s="22" t="inlineStr"/>
       <c r="F11" s="22" t="inlineStr"/>
       <c r="G11" s="22" t="inlineStr"/>
-      <c r="H11" s="22" t="inlineStr"/>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I11" s="22" t="inlineStr"/>
       <c r="J11" s="22" t="inlineStr"/>
       <c r="K11" s="22" t="inlineStr"/>
@@ -2055,7 +2079,11 @@
       <c r="E12" s="22" t="inlineStr"/>
       <c r="F12" s="22" t="inlineStr"/>
       <c r="G12" s="22" t="inlineStr"/>
-      <c r="H12" s="22" t="inlineStr"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="22" t="inlineStr"/>
       <c r="J12" s="22" t="inlineStr"/>
       <c r="K12" s="22" t="inlineStr"/>
@@ -2096,7 +2124,11 @@
       <c r="E13" s="22" t="inlineStr"/>
       <c r="F13" s="22" t="inlineStr"/>
       <c r="G13" s="22" t="inlineStr"/>
-      <c r="H13" s="22" t="inlineStr"/>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="22" t="inlineStr"/>
       <c r="J13" s="22" t="inlineStr"/>
       <c r="K13" s="22" t="inlineStr"/>
@@ -2137,7 +2169,11 @@
       <c r="E14" s="22" t="inlineStr"/>
       <c r="F14" s="22" t="inlineStr"/>
       <c r="G14" s="22" t="inlineStr"/>
-      <c r="H14" s="22" t="inlineStr"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I14" s="22" t="inlineStr"/>
       <c r="J14" s="22" t="inlineStr"/>
       <c r="K14" s="22" t="inlineStr"/>
@@ -2178,7 +2214,11 @@
       <c r="E15" s="22" t="inlineStr"/>
       <c r="F15" s="22" t="inlineStr"/>
       <c r="G15" s="22" t="inlineStr"/>
-      <c r="H15" s="22" t="inlineStr"/>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I15" s="22" t="inlineStr"/>
       <c r="J15" s="22" t="inlineStr"/>
       <c r="K15" s="22" t="inlineStr"/>
@@ -2219,7 +2259,11 @@
       <c r="E16" s="22" t="inlineStr"/>
       <c r="F16" s="22" t="inlineStr"/>
       <c r="G16" s="22" t="inlineStr"/>
-      <c r="H16" s="22" t="inlineStr"/>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I16" s="22" t="inlineStr"/>
       <c r="J16" s="22" t="inlineStr"/>
       <c r="K16" s="22" t="inlineStr"/>
@@ -2260,7 +2304,11 @@
       <c r="E17" s="22" t="inlineStr"/>
       <c r="F17" s="22" t="inlineStr"/>
       <c r="G17" s="22" t="inlineStr"/>
-      <c r="H17" s="22" t="inlineStr"/>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I17" s="22" t="inlineStr"/>
       <c r="J17" s="22" t="inlineStr"/>
       <c r="K17" s="22" t="inlineStr"/>
@@ -2301,7 +2349,11 @@
       <c r="E18" s="22" t="inlineStr"/>
       <c r="F18" s="22" t="inlineStr"/>
       <c r="G18" s="22" t="inlineStr"/>
-      <c r="H18" s="22" t="inlineStr"/>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I18" s="22" t="inlineStr"/>
       <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr"/>
@@ -2342,7 +2394,11 @@
       <c r="E19" s="22" t="inlineStr"/>
       <c r="F19" s="22" t="inlineStr"/>
       <c r="G19" s="22" t="inlineStr"/>
-      <c r="H19" s="22" t="inlineStr"/>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I19" s="22" t="inlineStr"/>
       <c r="J19" s="22" t="inlineStr"/>
       <c r="K19" s="22" t="inlineStr"/>
@@ -2383,7 +2439,11 @@
       <c r="E20" s="22" t="inlineStr"/>
       <c r="F20" s="22" t="inlineStr"/>
       <c r="G20" s="22" t="inlineStr"/>
-      <c r="H20" s="22" t="inlineStr"/>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I20" s="22" t="inlineStr"/>
       <c r="J20" s="22" t="inlineStr"/>
       <c r="K20" s="22" t="inlineStr"/>
@@ -2424,7 +2484,11 @@
       <c r="E21" s="22" t="inlineStr"/>
       <c r="F21" s="22" t="inlineStr"/>
       <c r="G21" s="22" t="inlineStr"/>
-      <c r="H21" s="22" t="inlineStr"/>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I21" s="22" t="inlineStr"/>
       <c r="J21" s="22" t="inlineStr"/>
       <c r="K21" s="22" t="inlineStr"/>
@@ -2459,7 +2523,11 @@
       <c r="E22" s="28" t="inlineStr"/>
       <c r="F22" s="28" t="inlineStr"/>
       <c r="G22" s="28" t="inlineStr"/>
-      <c r="H22" s="28" t="inlineStr"/>
+      <c r="H22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
       <c r="I22" s="28" t="inlineStr"/>
       <c r="J22" s="28" t="inlineStr"/>
       <c r="K22" s="28" t="inlineStr"/>
@@ -2599,7 +2667,11 @@
       <c r="Y27" s="21" t="n"/>
     </row>
     <row r="28" ht="173.25" customHeight="1">
-      <c r="B28" s="46" t="inlineStr"/>
+      <c r="B28" s="46" t="inlineStr">
+        <is>
+          <t>[วันที่ 6]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีมันไหลออกจากหัว</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="AA29" s="19" t="n"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -2595,7 +2595,11 @@
       <c r="E24" s="30" t="inlineStr"/>
       <c r="F24" s="30" t="inlineStr"/>
       <c r="G24" s="30" t="inlineStr"/>
-      <c r="H24" s="30" t="inlineStr"/>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>สมศักดิ์</t>
+        </is>
+      </c>
       <c r="I24" s="30" t="inlineStr"/>
       <c r="J24" s="30" t="inlineStr"/>
       <c r="K24" s="30" t="inlineStr"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -2595,11 +2595,7 @@
       <c r="E24" s="30" t="inlineStr"/>
       <c r="F24" s="30" t="inlineStr"/>
       <c r="G24" s="30" t="inlineStr"/>
-      <c r="H24" s="44" t="inlineStr">
-        <is>
-          <t>สมศักดิ์</t>
-        </is>
-      </c>
+      <c r="H24" s="44" t="inlineStr"/>
       <c r="I24" s="30" t="inlineStr"/>
       <c r="J24" s="30" t="inlineStr"/>
       <c r="K24" s="30" t="inlineStr"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -2595,7 +2595,11 @@
       <c r="E24" s="30" t="inlineStr"/>
       <c r="F24" s="30" t="inlineStr"/>
       <c r="G24" s="30" t="inlineStr"/>
-      <c r="H24" s="44" t="inlineStr"/>
+      <c r="H24" s="44" t="inlineStr">
+        <is>
+          <t>รัชพล</t>
+        </is>
+      </c>
       <c r="I24" s="30" t="inlineStr"/>
       <c r="J24" s="30" t="inlineStr"/>
       <c r="K24" s="30" t="inlineStr"/>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -1814,7 +1814,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
       <c r="L6" s="22" t="inlineStr"/>
@@ -1859,7 +1863,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
       <c r="L7" s="22" t="inlineStr"/>
@@ -1904,7 +1912,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
       <c r="L8" s="22" t="inlineStr"/>
@@ -1949,7 +1961,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr"/>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
       <c r="L9" s="22" t="inlineStr"/>
@@ -1994,7 +2010,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr"/>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
       <c r="L10" s="22" t="inlineStr"/>
@@ -2039,7 +2059,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr"/>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J11" s="22" t="inlineStr"/>
       <c r="K11" s="22" t="inlineStr"/>
       <c r="L11" s="22" t="inlineStr"/>
@@ -2084,7 +2108,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr"/>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="22" t="inlineStr"/>
       <c r="K12" s="22" t="inlineStr"/>
       <c r="L12" s="22" t="inlineStr"/>
@@ -2129,7 +2157,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr"/>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="22" t="inlineStr"/>
       <c r="K13" s="22" t="inlineStr"/>
       <c r="L13" s="22" t="inlineStr"/>
@@ -2174,7 +2206,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr"/>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J14" s="22" t="inlineStr"/>
       <c r="K14" s="22" t="inlineStr"/>
       <c r="L14" s="22" t="inlineStr"/>
@@ -2219,7 +2255,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr"/>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J15" s="22" t="inlineStr"/>
       <c r="K15" s="22" t="inlineStr"/>
       <c r="L15" s="22" t="inlineStr"/>
@@ -2264,7 +2304,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J16" s="22" t="inlineStr"/>
       <c r="K16" s="22" t="inlineStr"/>
       <c r="L16" s="22" t="inlineStr"/>
@@ -2309,7 +2353,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr"/>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J17" s="22" t="inlineStr"/>
       <c r="K17" s="22" t="inlineStr"/>
       <c r="L17" s="22" t="inlineStr"/>
@@ -2354,7 +2402,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr"/>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr"/>
       <c r="L18" s="22" t="inlineStr"/>
@@ -2399,7 +2451,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr"/>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J19" s="22" t="inlineStr"/>
       <c r="K19" s="22" t="inlineStr"/>
       <c r="L19" s="22" t="inlineStr"/>
@@ -2444,7 +2500,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr"/>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J20" s="22" t="inlineStr"/>
       <c r="K20" s="22" t="inlineStr"/>
       <c r="L20" s="22" t="inlineStr"/>
@@ -2489,7 +2549,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr"/>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J21" s="22" t="inlineStr"/>
       <c r="K21" s="22" t="inlineStr"/>
       <c r="L21" s="22" t="inlineStr"/>
@@ -2528,7 +2592,11 @@
           <t>พงศกร มลวัง</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr"/>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
       <c r="J22" s="28" t="inlineStr"/>
       <c r="K22" s="28" t="inlineStr"/>
       <c r="L22" s="28" t="inlineStr"/>
@@ -2673,7 +2741,7 @@
     <row r="28" ht="173.25" customHeight="1">
       <c r="B28" s="46" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีมันไหลออกจากหัว</t>
+          <t>[วันที่ 6]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีมันไหลออกจากหัว,  [วันที่ 7]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีน้ำมันไหลออกจากหัว</t>
         </is>
       </c>
     </row>

--- a/FM-MN-07_CNC3X-02.xlsx
+++ b/FM-MN-07_CNC3X-02.xlsx
@@ -1821,7 +1821,11 @@
       </c>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="22" t="inlineStr"/>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="22" t="inlineStr"/>
       <c r="N6" s="22" t="inlineStr"/>
       <c r="O6" s="22" t="inlineStr"/>
@@ -1870,7 +1874,11 @@
       </c>
       <c r="J7" s="22" t="inlineStr"/>
       <c r="K7" s="22" t="inlineStr"/>
-      <c r="L7" s="22" t="inlineStr"/>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="22" t="inlineStr"/>
       <c r="N7" s="22" t="inlineStr"/>
       <c r="O7" s="22" t="inlineStr"/>
@@ -1919,7 +1927,11 @@
       </c>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="22" t="inlineStr"/>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="22" t="inlineStr"/>
       <c r="N8" s="22" t="inlineStr"/>
       <c r="O8" s="22" t="inlineStr"/>
@@ -1968,7 +1980,11 @@
       </c>
       <c r="J9" s="22" t="inlineStr"/>
       <c r="K9" s="22" t="inlineStr"/>
-      <c r="L9" s="22" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="22" t="inlineStr"/>
       <c r="N9" s="22" t="inlineStr"/>
       <c r="O9" s="22" t="inlineStr"/>
@@ -2017,7 +2033,11 @@
       </c>
       <c r="J10" s="22" t="inlineStr"/>
       <c r="K10" s="22" t="inlineStr"/>
-      <c r="L10" s="22" t="inlineStr"/>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="22" t="inlineStr"/>
       <c r="N10" s="22" t="inlineStr"/>
       <c r="O10" s="22" t="inlineStr"/>
@@ -2066,7 +2086,11 @@
       </c>
       <c r="J11" s="22" t="inlineStr"/>
       <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="22" t="inlineStr"/>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M11" s="22" t="inlineStr"/>
       <c r="N11" s="22" t="inlineStr"/>
       <c r="O11" s="22" t="inlineStr"/>
@@ -2115,7 +2139,11 @@
       </c>
       <c r="J12" s="22" t="inlineStr"/>
       <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="22" t="inlineStr"/>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="22" t="inlineStr"/>
       <c r="N12" s="22" t="inlineStr"/>
       <c r="O12" s="22" t="inlineStr"/>
@@ -2164,7 +2192,11 @@
       </c>
       <c r="J13" s="22" t="inlineStr"/>
       <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="22" t="inlineStr"/>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="22" t="inlineStr"/>
       <c r="N13" s="22" t="inlineStr"/>
       <c r="O13" s="22" t="inlineStr"/>
@@ -2213,7 +2245,11 @@
       </c>
       <c r="J14" s="22" t="inlineStr"/>
       <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="22" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M14" s="22" t="inlineStr"/>
       <c r="N14" s="22" t="inlineStr"/>
       <c r="O14" s="22" t="inlineStr"/>
@@ -2262,7 +2298,11 @@
       </c>
       <c r="J15" s="22" t="inlineStr"/>
       <c r="K15" s="22" t="inlineStr"/>
-      <c r="L15" s="22" t="inlineStr"/>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M15" s="22" t="inlineStr"/>
       <c r="N15" s="22" t="inlineStr"/>
       <c r="O15" s="22" t="inlineStr"/>
@@ -2311,7 +2351,11 @@
       </c>
       <c r="J16" s="22" t="inlineStr"/>
       <c r="K16" s="22" t="inlineStr"/>
-      <c r="L16" s="22" t="inlineStr"/>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M16" s="22" t="inlineStr"/>
       <c r="N16" s="22" t="inlineStr"/>
       <c r="O16" s="22" t="inlineStr"/>
@@ -2360,7 +2404,11 @@
       </c>
       <c r="J17" s="22" t="inlineStr"/>
       <c r="K17" s="22" t="inlineStr"/>
-      <c r="L17" s="22" t="inlineStr"/>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M17" s="22" t="inlineStr"/>
       <c r="N17" s="22" t="inlineStr"/>
       <c r="O17" s="22" t="inlineStr"/>
@@ -2409,7 +2457,11 @@
       </c>
       <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr"/>
-      <c r="L18" s="22" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M18" s="22" t="inlineStr"/>
       <c r="N18" s="22" t="inlineStr"/>
       <c r="O18" s="22" t="inlineStr"/>
@@ -2458,7 +2510,11 @@
       </c>
       <c r="J19" s="22" t="inlineStr"/>
       <c r="K19" s="22" t="inlineStr"/>
-      <c r="L19" s="22" t="inlineStr"/>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M19" s="22" t="inlineStr"/>
       <c r="N19" s="22" t="inlineStr"/>
       <c r="O19" s="22" t="inlineStr"/>
@@ -2507,7 +2563,11 @@
       </c>
       <c r="J20" s="22" t="inlineStr"/>
       <c r="K20" s="22" t="inlineStr"/>
-      <c r="L20" s="22" t="inlineStr"/>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M20" s="22" t="inlineStr"/>
       <c r="N20" s="22" t="inlineStr"/>
       <c r="O20" s="22" t="inlineStr"/>
@@ -2556,7 +2616,11 @@
       </c>
       <c r="J21" s="22" t="inlineStr"/>
       <c r="K21" s="22" t="inlineStr"/>
-      <c r="L21" s="22" t="inlineStr"/>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M21" s="22" t="inlineStr"/>
       <c r="N21" s="22" t="inlineStr"/>
       <c r="O21" s="22" t="inlineStr"/>
@@ -2599,7 +2663,11 @@
       </c>
       <c r="J22" s="28" t="inlineStr"/>
       <c r="K22" s="28" t="inlineStr"/>
-      <c r="L22" s="28" t="inlineStr"/>
+      <c r="L22" s="33" t="inlineStr">
+        <is>
+          <t>พงศกร มลวัง</t>
+        </is>
+      </c>
       <c r="M22" s="28" t="inlineStr"/>
       <c r="N22" s="28" t="inlineStr"/>
       <c r="O22" s="28" t="inlineStr"/>
@@ -2741,7 +2809,7 @@
     <row r="28" ht="173.25" customHeight="1">
       <c r="B28" s="46" t="inlineStr">
         <is>
-          <t>[วันที่ 6]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีมันไหลออกจากหัว,  [วันที่ 7]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีน้ำมันไหลออกจากหัว</t>
+          <t>[วันที่ 6]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีมันไหลออกจากหัว,  [วันที่ 7]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีน้ำมันไหลออกจากหัว,  [วันที่ 10]: ข้อ 9: น้ำคูลแลนใม่ไหล, ข้อ 11: มีน้ำมันไหลออกจากหัว</t>
         </is>
       </c>
     </row>
